--- a/backend/templates/ResumenFinal_Template.xlsx
+++ b/backend/templates/ResumenFinal_Template.xlsx
@@ -18,6 +18,6202 @@
     <sheet name="4to Año" sheetId="3" r:id="rId3"/>
     <sheet name="5to Año" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="inst_period" localSheetId="0">'1er Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="0">'1er Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="0">'1er Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="0">'1er Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="0">'1er Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="0">'1er Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="0">'1er Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="0">'1er Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="0">'1er Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="0">'1er Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="0">'1er Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="0">'1er Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="0">'1er Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="0">'1er Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="0">'1er Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="0">'1er Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="0">'1er Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="0">'1er Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="0">'1er Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="0">'1er Año'!$V$15</definedName>
+    <definedName name="std_num_1" localSheetId="0">'1er Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="0">'1er Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="0">'1er Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="0">'1er Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="0">'1er Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="0">'1er Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="0">'1er Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="0">'1er Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="0">'1er Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="0">'1er Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="0">'1er Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="0">'1er Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="0">'1er Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="0">'1er Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="0">'1er Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="0">'1er Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="0">'1er Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="0">'1er Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="0">'1er Año'!$V$16</definedName>
+    <definedName name="std_part_1" localSheetId="0">'1er Año'!$W$16</definedName>
+    <definedName name="std_num_2" localSheetId="0">'1er Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="0">'1er Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="0">'1er Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="0">'1er Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="0">'1er Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="0">'1er Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="0">'1er Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="0">'1er Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="0">'1er Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="0">'1er Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="0">'1er Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="0">'1er Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="0">'1er Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="0">'1er Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="0">'1er Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="0">'1er Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="0">'1er Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="0">'1er Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="0">'1er Año'!$V$17</definedName>
+    <definedName name="std_part_2" localSheetId="0">'1er Año'!$W$17</definedName>
+    <definedName name="std_num_3" localSheetId="0">'1er Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="0">'1er Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="0">'1er Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="0">'1er Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="0">'1er Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="0">'1er Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="0">'1er Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="0">'1er Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="0">'1er Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="0">'1er Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="0">'1er Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="0">'1er Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="0">'1er Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="0">'1er Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="0">'1er Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="0">'1er Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="0">'1er Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="0">'1er Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="0">'1er Año'!$V$18</definedName>
+    <definedName name="std_part_3" localSheetId="0">'1er Año'!$W$18</definedName>
+    <definedName name="std_num_4" localSheetId="0">'1er Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="0">'1er Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="0">'1er Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="0">'1er Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="0">'1er Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="0">'1er Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="0">'1er Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="0">'1er Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="0">'1er Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="0">'1er Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="0">'1er Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="0">'1er Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="0">'1er Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="0">'1er Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="0">'1er Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="0">'1er Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="0">'1er Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="0">'1er Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="0">'1er Año'!$V$19</definedName>
+    <definedName name="std_part_4" localSheetId="0">'1er Año'!$W$19</definedName>
+    <definedName name="std_num_5" localSheetId="0">'1er Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="0">'1er Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="0">'1er Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="0">'1er Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="0">'1er Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="0">'1er Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="0">'1er Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="0">'1er Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="0">'1er Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="0">'1er Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="0">'1er Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="0">'1er Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="0">'1er Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="0">'1er Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="0">'1er Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="0">'1er Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="0">'1er Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="0">'1er Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="0">'1er Año'!$V$20</definedName>
+    <definedName name="std_part_5" localSheetId="0">'1er Año'!$W$20</definedName>
+    <definedName name="std_num_6" localSheetId="0">'1er Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="0">'1er Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="0">'1er Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="0">'1er Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="0">'1er Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="0">'1er Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="0">'1er Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="0">'1er Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="0">'1er Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="0">'1er Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="0">'1er Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="0">'1er Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="0">'1er Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="0">'1er Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="0">'1er Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="0">'1er Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="0">'1er Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="0">'1er Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="0">'1er Año'!$V$21</definedName>
+    <definedName name="std_part_6" localSheetId="0">'1er Año'!$W$21</definedName>
+    <definedName name="std_num_7" localSheetId="0">'1er Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="0">'1er Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="0">'1er Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="0">'1er Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="0">'1er Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="0">'1er Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="0">'1er Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="0">'1er Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="0">'1er Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="0">'1er Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="0">'1er Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="0">'1er Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="0">'1er Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="0">'1er Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="0">'1er Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="0">'1er Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="0">'1er Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="0">'1er Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="0">'1er Año'!$V$22</definedName>
+    <definedName name="std_part_7" localSheetId="0">'1er Año'!$W$22</definedName>
+    <definedName name="std_num_8" localSheetId="0">'1er Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="0">'1er Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="0">'1er Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="0">'1er Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="0">'1er Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="0">'1er Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="0">'1er Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="0">'1er Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="0">'1er Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="0">'1er Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="0">'1er Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="0">'1er Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="0">'1er Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="0">'1er Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="0">'1er Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="0">'1er Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="0">'1er Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="0">'1er Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="0">'1er Año'!$V$23</definedName>
+    <definedName name="std_part_8" localSheetId="0">'1er Año'!$W$23</definedName>
+    <definedName name="std_num_9" localSheetId="0">'1er Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="0">'1er Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="0">'1er Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="0">'1er Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="0">'1er Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="0">'1er Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="0">'1er Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="0">'1er Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="0">'1er Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="0">'1er Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="0">'1er Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="0">'1er Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="0">'1er Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="0">'1er Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="0">'1er Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="0">'1er Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="0">'1er Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="0">'1er Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="0">'1er Año'!$V$24</definedName>
+    <definedName name="std_part_9" localSheetId="0">'1er Año'!$W$24</definedName>
+    <definedName name="std_num_10" localSheetId="0">'1er Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="0">'1er Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="0">'1er Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="0">'1er Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="0">'1er Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="0">'1er Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="0">'1er Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="0">'1er Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="0">'1er Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="0">'1er Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="0">'1er Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="0">'1er Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="0">'1er Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="0">'1er Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="0">'1er Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="0">'1er Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="0">'1er Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="0">'1er Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="0">'1er Año'!$V$25</definedName>
+    <definedName name="std_part_10" localSheetId="0">'1er Año'!$W$25</definedName>
+    <definedName name="std_num_11" localSheetId="0">'1er Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="0">'1er Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="0">'1er Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="0">'1er Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="0">'1er Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="0">'1er Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="0">'1er Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="0">'1er Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="0">'1er Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="0">'1er Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="0">'1er Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="0">'1er Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="0">'1er Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="0">'1er Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="0">'1er Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="0">'1er Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="0">'1er Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="0">'1er Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="0">'1er Año'!$V$26</definedName>
+    <definedName name="std_part_11" localSheetId="0">'1er Año'!$W$26</definedName>
+    <definedName name="std_num_12" localSheetId="0">'1er Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="0">'1er Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="0">'1er Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="0">'1er Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="0">'1er Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="0">'1er Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="0">'1er Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="0">'1er Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="0">'1er Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="0">'1er Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="0">'1er Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="0">'1er Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="0">'1er Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="0">'1er Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="0">'1er Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="0">'1er Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="0">'1er Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="0">'1er Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="0">'1er Año'!$V$27</definedName>
+    <definedName name="std_part_12" localSheetId="0">'1er Año'!$W$27</definedName>
+    <definedName name="std_num_13" localSheetId="0">'1er Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="0">'1er Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="0">'1er Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="0">'1er Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="0">'1er Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="0">'1er Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="0">'1er Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="0">'1er Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="0">'1er Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="0">'1er Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="0">'1er Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="0">'1er Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="0">'1er Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="0">'1er Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="0">'1er Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="0">'1er Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="0">'1er Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="0">'1er Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="0">'1er Año'!$V$28</definedName>
+    <definedName name="std_part_13" localSheetId="0">'1er Año'!$W$28</definedName>
+    <definedName name="std_num_14" localSheetId="0">'1er Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="0">'1er Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="0">'1er Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="0">'1er Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="0">'1er Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="0">'1er Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="0">'1er Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="0">'1er Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="0">'1er Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="0">'1er Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="0">'1er Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="0">'1er Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="0">'1er Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="0">'1er Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="0">'1er Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="0">'1er Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="0">'1er Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="0">'1er Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="0">'1er Año'!$V$29</definedName>
+    <definedName name="std_part_14" localSheetId="0">'1er Año'!$W$29</definedName>
+    <definedName name="std_num_15" localSheetId="0">'1er Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="0">'1er Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="0">'1er Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="0">'1er Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="0">'1er Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="0">'1er Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="0">'1er Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="0">'1er Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="0">'1er Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="0">'1er Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="0">'1er Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="0">'1er Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="0">'1er Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="0">'1er Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="0">'1er Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="0">'1er Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="0">'1er Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="0">'1er Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="0">'1er Año'!$V$30</definedName>
+    <definedName name="std_part_15" localSheetId="0">'1er Año'!$W$30</definedName>
+    <definedName name="std_num_16" localSheetId="0">'1er Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="0">'1er Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="0">'1er Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="0">'1er Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="0">'1er Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="0">'1er Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="0">'1er Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="0">'1er Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="0">'1er Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="0">'1er Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="0">'1er Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="0">'1er Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="0">'1er Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="0">'1er Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="0">'1er Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="0">'1er Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="0">'1er Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="0">'1er Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="0">'1er Año'!$V$31</definedName>
+    <definedName name="std_part_16" localSheetId="0">'1er Año'!$W$31</definedName>
+    <definedName name="std_num_17" localSheetId="0">'1er Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="0">'1er Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="0">'1er Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="0">'1er Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="0">'1er Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="0">'1er Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="0">'1er Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="0">'1er Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="0">'1er Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="0">'1er Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="0">'1er Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="0">'1er Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="0">'1er Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="0">'1er Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="0">'1er Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="0">'1er Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="0">'1er Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="0">'1er Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="0">'1er Año'!$V$32</definedName>
+    <definedName name="std_part_17" localSheetId="0">'1er Año'!$W$32</definedName>
+    <definedName name="std_num_18" localSheetId="0">'1er Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="0">'1er Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="0">'1er Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="0">'1er Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="0">'1er Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="0">'1er Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="0">'1er Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="0">'1er Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="0">'1er Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="0">'1er Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="0">'1er Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="0">'1er Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="0">'1er Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="0">'1er Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="0">'1er Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="0">'1er Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="0">'1er Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="0">'1er Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="0">'1er Año'!$V$33</definedName>
+    <definedName name="std_part_18" localSheetId="0">'1er Año'!$W$33</definedName>
+    <definedName name="std_num_19" localSheetId="0">'1er Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="0">'1er Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="0">'1er Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="0">'1er Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="0">'1er Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="0">'1er Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="0">'1er Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="0">'1er Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="0">'1er Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="0">'1er Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="0">'1er Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="0">'1er Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="0">'1er Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="0">'1er Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="0">'1er Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="0">'1er Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="0">'1er Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="0">'1er Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="0">'1er Año'!$V$34</definedName>
+    <definedName name="std_part_19" localSheetId="0">'1er Año'!$W$34</definedName>
+    <definedName name="std_num_20" localSheetId="0">'1er Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="0">'1er Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="0">'1er Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="0">'1er Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="0">'1er Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="0">'1er Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="0">'1er Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="0">'1er Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="0">'1er Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="0">'1er Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="0">'1er Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="0">'1er Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="0">'1er Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="0">'1er Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="0">'1er Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="0">'1er Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="0">'1er Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="0">'1er Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="0">'1er Año'!$V$35</definedName>
+    <definedName name="std_part_20" localSheetId="0">'1er Año'!$W$35</definedName>
+    <definedName name="std_num_21" localSheetId="0">'1er Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="0">'1er Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="0">'1er Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="0">'1er Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="0">'1er Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="0">'1er Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="0">'1er Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="0">'1er Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="0">'1er Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="0">'1er Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="0">'1er Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="0">'1er Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="0">'1er Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="0">'1er Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="0">'1er Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="0">'1er Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="0">'1er Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="0">'1er Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="0">'1er Año'!$V$36</definedName>
+    <definedName name="std_part_21" localSheetId="0">'1er Año'!$W$36</definedName>
+    <definedName name="std_num_22" localSheetId="0">'1er Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="0">'1er Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="0">'1er Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="0">'1er Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="0">'1er Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="0">'1er Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="0">'1er Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="0">'1er Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="0">'1er Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="0">'1er Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="0">'1er Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="0">'1er Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="0">'1er Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="0">'1er Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="0">'1er Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="0">'1er Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="0">'1er Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="0">'1er Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="0">'1er Año'!$V$37</definedName>
+    <definedName name="std_part_22" localSheetId="0">'1er Año'!$W$37</definedName>
+    <definedName name="std_num_23" localSheetId="0">'1er Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="0">'1er Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="0">'1er Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="0">'1er Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="0">'1er Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="0">'1er Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="0">'1er Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="0">'1er Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="0">'1er Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="0">'1er Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="0">'1er Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="0">'1er Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="0">'1er Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="0">'1er Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="0">'1er Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="0">'1er Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="0">'1er Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="0">'1er Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="0">'1er Año'!$V$38</definedName>
+    <definedName name="std_part_23" localSheetId="0">'1er Año'!$W$38</definedName>
+    <definedName name="std_num_24" localSheetId="0">'1er Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="0">'1er Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="0">'1er Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="0">'1er Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="0">'1er Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="0">'1er Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="0">'1er Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="0">'1er Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="0">'1er Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="0">'1er Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="0">'1er Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="0">'1er Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="0">'1er Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="0">'1er Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="0">'1er Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="0">'1er Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="0">'1er Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="0">'1er Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="0">'1er Año'!$V$39</definedName>
+    <definedName name="std_part_24" localSheetId="0">'1er Año'!$W$39</definedName>
+    <definedName name="std_num_25" localSheetId="0">'1er Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="0">'1er Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="0">'1er Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="0">'1er Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="0">'1er Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="0">'1er Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="0">'1er Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="0">'1er Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="0">'1er Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="0">'1er Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="0">'1er Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="0">'1er Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="0">'1er Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="0">'1er Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="0">'1er Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="0">'1er Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="0">'1er Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="0">'1er Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="0">'1er Año'!$V$40</definedName>
+    <definedName name="std_part_25" localSheetId="0">'1er Año'!$W$40</definedName>
+    <definedName name="std_num_26" localSheetId="0">'1er Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="0">'1er Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="0">'1er Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="0">'1er Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="0">'1er Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="0">'1er Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="0">'1er Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="0">'1er Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="0">'1er Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="0">'1er Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="0">'1er Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="0">'1er Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="0">'1er Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="0">'1er Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="0">'1er Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="0">'1er Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="0">'1er Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="0">'1er Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="0">'1er Año'!$V$41</definedName>
+    <definedName name="std_part_26" localSheetId="0">'1er Año'!$W$41</definedName>
+    <definedName name="std_num_27" localSheetId="0">'1er Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="0">'1er Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="0">'1er Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="0">'1er Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="0">'1er Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="0">'1er Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="0">'1er Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="0">'1er Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="0">'1er Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="0">'1er Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="0">'1er Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="0">'1er Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="0">'1er Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="0">'1er Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="0">'1er Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="0">'1er Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="0">'1er Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="0">'1er Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="0">'1er Año'!$V$42</definedName>
+    <definedName name="std_part_27" localSheetId="0">'1er Año'!$W$42</definedName>
+    <definedName name="std_num_28" localSheetId="0">'1er Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="0">'1er Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="0">'1er Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="0">'1er Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="0">'1er Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="0">'1er Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="0">'1er Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="0">'1er Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="0">'1er Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="0">'1er Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="0">'1er Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="0">'1er Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="0">'1er Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="0">'1er Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="0">'1er Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="0">'1er Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="0">'1er Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="0">'1er Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="0">'1er Año'!$V$43</definedName>
+    <definedName name="std_part_28" localSheetId="0">'1er Año'!$W$43</definedName>
+    <definedName name="std_num_29" localSheetId="0">'1er Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="0">'1er Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="0">'1er Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="0">'1er Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="0">'1er Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="0">'1er Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="0">'1er Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="0">'1er Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="0">'1er Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="0">'1er Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="0">'1er Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="0">'1er Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="0">'1er Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="0">'1er Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="0">'1er Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="0">'1er Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="0">'1er Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="0">'1er Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="0">'1er Año'!$V$44</definedName>
+    <definedName name="std_part_29" localSheetId="0">'1er Año'!$W$44</definedName>
+    <definedName name="std_num_30" localSheetId="0">'1er Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="0">'1er Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="0">'1er Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="0">'1er Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="0">'1er Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="0">'1er Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="0">'1er Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="0">'1er Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="0">'1er Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="0">'1er Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="0">'1er Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="0">'1er Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="0">'1er Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="0">'1er Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="0">'1er Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="0">'1er Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="0">'1er Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="0">'1er Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="0">'1er Año'!$V$45</definedName>
+    <definedName name="std_part_30" localSheetId="0">'1er Año'!$W$45</definedName>
+    <definedName name="std_num_31" localSheetId="0">'1er Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="0">'1er Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="0">'1er Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="0">'1er Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="0">'1er Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="0">'1er Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="0">'1er Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="0">'1er Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="0">'1er Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="0">'1er Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="0">'1er Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="0">'1er Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="0">'1er Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="0">'1er Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="0">'1er Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="0">'1er Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="0">'1er Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="0">'1er Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="0">'1er Año'!$V$46</definedName>
+    <definedName name="std_part_31" localSheetId="0">'1er Año'!$W$46</definedName>
+    <definedName name="std_num_32" localSheetId="0">'1er Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="0">'1er Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="0">'1er Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="0">'1er Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="0">'1er Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="0">'1er Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="0">'1er Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="0">'1er Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="0">'1er Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="0">'1er Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="0">'1er Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="0">'1er Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="0">'1er Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="0">'1er Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="0">'1er Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="0">'1er Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="0">'1er Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="0">'1er Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="0">'1er Año'!$V$47</definedName>
+    <definedName name="std_part_32" localSheetId="0">'1er Año'!$W$47</definedName>
+    <definedName name="std_num_33" localSheetId="0">'1er Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="0">'1er Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="0">'1er Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="0">'1er Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="0">'1er Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="0">'1er Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="0">'1er Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="0">'1er Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="0">'1er Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="0">'1er Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="0">'1er Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="0">'1er Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="0">'1er Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="0">'1er Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="0">'1er Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="0">'1er Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="0">'1er Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="0">'1er Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="0">'1er Año'!$V$48</definedName>
+    <definedName name="std_part_33" localSheetId="0">'1er Año'!$W$48</definedName>
+    <definedName name="std_num_34" localSheetId="0">'1er Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="0">'1er Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="0">'1er Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="0">'1er Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="0">'1er Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="0">'1er Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="0">'1er Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="0">'1er Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="0">'1er Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="0">'1er Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="0">'1er Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="0">'1er Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="0">'1er Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="0">'1er Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="0">'1er Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="0">'1er Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="0">'1er Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="0">'1er Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="0">'1er Año'!$V$49</definedName>
+    <definedName name="std_part_34" localSheetId="0">'1er Año'!$W$49</definedName>
+    <definedName name="std_num_35" localSheetId="0">'1er Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="0">'1er Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="0">'1er Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="0">'1er Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="0">'1er Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="0">'1er Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="0">'1er Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="0">'1er Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="0">'1er Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="0">'1er Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="0">'1er Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="0">'1er Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="0">'1er Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="0">'1er Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="0">'1er Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="0">'1er Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="0">'1er Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="0">'1er Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="0">'1er Año'!$V$50</definedName>
+    <definedName name="std_part_35" localSheetId="0">'1er Año'!$W$50</definedName>
+    <definedName name="inst_period" localSheetId="1">'3er Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="1">'3er Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="1">'3er Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="1">'3er Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="1">'3er Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="1">'3er Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="1">'3er Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="1">'3er Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="1">'3er Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="1">'3er Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="1">'3er Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="1">'3er Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="1">'3er Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="1">'3er Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="1">'3er Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="1">'3er Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="1">'3er Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="1">'3er Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="1">'3er Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="1">'3er Año'!$V$15</definedName>
+    <definedName name="subj_10" localSheetId="1">'3er Año'!$W$15</definedName>
+    <definedName name="std_num_1" localSheetId="1">'3er Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="1">'3er Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="1">'3er Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="1">'3er Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="1">'3er Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="1">'3er Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="1">'3er Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="1">'3er Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="1">'3er Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="1">'3er Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="1">'3er Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="1">'3er Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="1">'3er Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="1">'3er Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="1">'3er Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="1">'3er Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="1">'3er Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="1">'3er Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="1">'3er Año'!$V$16</definedName>
+    <definedName name="grade_10_1" localSheetId="1">'3er Año'!$W$16</definedName>
+    <definedName name="std_part_1" localSheetId="1">'3er Año'!$X$16</definedName>
+    <definedName name="std_num_2" localSheetId="1">'3er Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="1">'3er Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="1">'3er Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="1">'3er Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="1">'3er Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="1">'3er Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="1">'3er Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="1">'3er Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="1">'3er Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="1">'3er Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="1">'3er Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="1">'3er Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="1">'3er Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="1">'3er Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="1">'3er Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="1">'3er Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="1">'3er Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="1">'3er Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="1">'3er Año'!$V$17</definedName>
+    <definedName name="grade_10_2" localSheetId="1">'3er Año'!$W$17</definedName>
+    <definedName name="std_part_2" localSheetId="1">'3er Año'!$X$17</definedName>
+    <definedName name="std_num_3" localSheetId="1">'3er Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="1">'3er Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="1">'3er Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="1">'3er Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="1">'3er Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="1">'3er Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="1">'3er Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="1">'3er Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="1">'3er Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="1">'3er Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="1">'3er Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="1">'3er Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="1">'3er Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="1">'3er Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="1">'3er Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="1">'3er Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="1">'3er Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="1">'3er Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="1">'3er Año'!$V$18</definedName>
+    <definedName name="grade_10_3" localSheetId="1">'3er Año'!$W$18</definedName>
+    <definedName name="std_part_3" localSheetId="1">'3er Año'!$X$18</definedName>
+    <definedName name="std_num_4" localSheetId="1">'3er Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="1">'3er Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="1">'3er Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="1">'3er Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="1">'3er Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="1">'3er Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="1">'3er Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="1">'3er Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="1">'3er Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="1">'3er Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="1">'3er Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="1">'3er Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="1">'3er Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="1">'3er Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="1">'3er Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="1">'3er Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="1">'3er Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="1">'3er Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="1">'3er Año'!$V$19</definedName>
+    <definedName name="grade_10_4" localSheetId="1">'3er Año'!$W$19</definedName>
+    <definedName name="std_part_4" localSheetId="1">'3er Año'!$X$19</definedName>
+    <definedName name="std_num_5" localSheetId="1">'3er Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="1">'3er Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="1">'3er Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="1">'3er Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="1">'3er Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="1">'3er Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="1">'3er Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="1">'3er Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="1">'3er Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="1">'3er Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="1">'3er Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="1">'3er Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="1">'3er Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="1">'3er Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="1">'3er Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="1">'3er Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="1">'3er Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="1">'3er Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="1">'3er Año'!$V$20</definedName>
+    <definedName name="grade_10_5" localSheetId="1">'3er Año'!$W$20</definedName>
+    <definedName name="std_part_5" localSheetId="1">'3er Año'!$X$20</definedName>
+    <definedName name="std_num_6" localSheetId="1">'3er Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="1">'3er Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="1">'3er Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="1">'3er Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="1">'3er Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="1">'3er Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="1">'3er Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="1">'3er Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="1">'3er Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="1">'3er Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="1">'3er Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="1">'3er Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="1">'3er Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="1">'3er Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="1">'3er Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="1">'3er Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="1">'3er Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="1">'3er Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="1">'3er Año'!$V$21</definedName>
+    <definedName name="grade_10_6" localSheetId="1">'3er Año'!$W$21</definedName>
+    <definedName name="std_part_6" localSheetId="1">'3er Año'!$X$21</definedName>
+    <definedName name="std_num_7" localSheetId="1">'3er Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="1">'3er Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="1">'3er Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="1">'3er Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="1">'3er Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="1">'3er Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="1">'3er Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="1">'3er Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="1">'3er Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="1">'3er Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="1">'3er Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="1">'3er Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="1">'3er Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="1">'3er Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="1">'3er Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="1">'3er Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="1">'3er Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="1">'3er Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="1">'3er Año'!$V$22</definedName>
+    <definedName name="grade_10_7" localSheetId="1">'3er Año'!$W$22</definedName>
+    <definedName name="std_part_7" localSheetId="1">'3er Año'!$X$22</definedName>
+    <definedName name="std_num_8" localSheetId="1">'3er Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="1">'3er Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="1">'3er Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="1">'3er Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="1">'3er Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="1">'3er Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="1">'3er Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="1">'3er Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="1">'3er Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="1">'3er Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="1">'3er Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="1">'3er Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="1">'3er Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="1">'3er Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="1">'3er Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="1">'3er Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="1">'3er Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="1">'3er Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="1">'3er Año'!$V$23</definedName>
+    <definedName name="grade_10_8" localSheetId="1">'3er Año'!$W$23</definedName>
+    <definedName name="std_part_8" localSheetId="1">'3er Año'!$X$23</definedName>
+    <definedName name="std_num_9" localSheetId="1">'3er Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="1">'3er Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="1">'3er Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="1">'3er Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="1">'3er Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="1">'3er Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="1">'3er Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="1">'3er Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="1">'3er Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="1">'3er Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="1">'3er Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="1">'3er Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="1">'3er Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="1">'3er Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="1">'3er Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="1">'3er Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="1">'3er Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="1">'3er Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="1">'3er Año'!$V$24</definedName>
+    <definedName name="grade_10_9" localSheetId="1">'3er Año'!$W$24</definedName>
+    <definedName name="std_part_9" localSheetId="1">'3er Año'!$X$24</definedName>
+    <definedName name="std_num_10" localSheetId="1">'3er Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="1">'3er Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="1">'3er Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="1">'3er Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="1">'3er Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="1">'3er Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="1">'3er Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="1">'3er Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="1">'3er Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="1">'3er Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="1">'3er Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="1">'3er Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="1">'3er Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="1">'3er Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="1">'3er Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="1">'3er Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="1">'3er Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="1">'3er Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="1">'3er Año'!$V$25</definedName>
+    <definedName name="grade_10_10" localSheetId="1">'3er Año'!$W$25</definedName>
+    <definedName name="std_part_10" localSheetId="1">'3er Año'!$X$25</definedName>
+    <definedName name="std_num_11" localSheetId="1">'3er Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="1">'3er Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="1">'3er Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="1">'3er Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="1">'3er Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="1">'3er Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="1">'3er Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="1">'3er Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="1">'3er Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="1">'3er Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="1">'3er Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="1">'3er Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="1">'3er Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="1">'3er Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="1">'3er Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="1">'3er Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="1">'3er Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="1">'3er Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="1">'3er Año'!$V$26</definedName>
+    <definedName name="grade_10_11" localSheetId="1">'3er Año'!$W$26</definedName>
+    <definedName name="std_part_11" localSheetId="1">'3er Año'!$X$26</definedName>
+    <definedName name="std_num_12" localSheetId="1">'3er Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="1">'3er Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="1">'3er Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="1">'3er Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="1">'3er Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="1">'3er Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="1">'3er Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="1">'3er Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="1">'3er Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="1">'3er Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="1">'3er Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="1">'3er Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="1">'3er Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="1">'3er Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="1">'3er Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="1">'3er Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="1">'3er Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="1">'3er Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="1">'3er Año'!$V$27</definedName>
+    <definedName name="grade_10_12" localSheetId="1">'3er Año'!$W$27</definedName>
+    <definedName name="std_part_12" localSheetId="1">'3er Año'!$X$27</definedName>
+    <definedName name="std_num_13" localSheetId="1">'3er Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="1">'3er Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="1">'3er Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="1">'3er Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="1">'3er Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="1">'3er Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="1">'3er Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="1">'3er Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="1">'3er Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="1">'3er Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="1">'3er Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="1">'3er Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="1">'3er Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="1">'3er Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="1">'3er Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="1">'3er Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="1">'3er Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="1">'3er Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="1">'3er Año'!$V$28</definedName>
+    <definedName name="grade_10_13" localSheetId="1">'3er Año'!$W$28</definedName>
+    <definedName name="std_part_13" localSheetId="1">'3er Año'!$X$28</definedName>
+    <definedName name="std_num_14" localSheetId="1">'3er Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="1">'3er Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="1">'3er Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="1">'3er Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="1">'3er Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="1">'3er Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="1">'3er Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="1">'3er Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="1">'3er Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="1">'3er Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="1">'3er Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="1">'3er Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="1">'3er Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="1">'3er Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="1">'3er Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="1">'3er Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="1">'3er Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="1">'3er Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="1">'3er Año'!$V$29</definedName>
+    <definedName name="grade_10_14" localSheetId="1">'3er Año'!$W$29</definedName>
+    <definedName name="std_part_14" localSheetId="1">'3er Año'!$X$29</definedName>
+    <definedName name="std_num_15" localSheetId="1">'3er Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="1">'3er Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="1">'3er Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="1">'3er Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="1">'3er Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="1">'3er Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="1">'3er Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="1">'3er Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="1">'3er Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="1">'3er Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="1">'3er Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="1">'3er Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="1">'3er Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="1">'3er Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="1">'3er Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="1">'3er Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="1">'3er Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="1">'3er Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="1">'3er Año'!$V$30</definedName>
+    <definedName name="grade_10_15" localSheetId="1">'3er Año'!$W$30</definedName>
+    <definedName name="std_part_15" localSheetId="1">'3er Año'!$X$30</definedName>
+    <definedName name="std_num_16" localSheetId="1">'3er Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="1">'3er Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="1">'3er Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="1">'3er Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="1">'3er Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="1">'3er Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="1">'3er Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="1">'3er Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="1">'3er Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="1">'3er Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="1">'3er Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="1">'3er Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="1">'3er Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="1">'3er Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="1">'3er Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="1">'3er Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="1">'3er Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="1">'3er Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="1">'3er Año'!$V$31</definedName>
+    <definedName name="grade_10_16" localSheetId="1">'3er Año'!$W$31</definedName>
+    <definedName name="std_part_16" localSheetId="1">'3er Año'!$X$31</definedName>
+    <definedName name="std_num_17" localSheetId="1">'3er Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="1">'3er Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="1">'3er Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="1">'3er Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="1">'3er Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="1">'3er Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="1">'3er Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="1">'3er Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="1">'3er Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="1">'3er Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="1">'3er Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="1">'3er Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="1">'3er Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="1">'3er Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="1">'3er Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="1">'3er Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="1">'3er Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="1">'3er Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="1">'3er Año'!$V$32</definedName>
+    <definedName name="grade_10_17" localSheetId="1">'3er Año'!$W$32</definedName>
+    <definedName name="std_part_17" localSheetId="1">'3er Año'!$X$32</definedName>
+    <definedName name="std_num_18" localSheetId="1">'3er Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="1">'3er Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="1">'3er Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="1">'3er Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="1">'3er Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="1">'3er Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="1">'3er Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="1">'3er Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="1">'3er Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="1">'3er Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="1">'3er Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="1">'3er Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="1">'3er Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="1">'3er Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="1">'3er Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="1">'3er Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="1">'3er Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="1">'3er Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="1">'3er Año'!$V$33</definedName>
+    <definedName name="grade_10_18" localSheetId="1">'3er Año'!$W$33</definedName>
+    <definedName name="std_part_18" localSheetId="1">'3er Año'!$X$33</definedName>
+    <definedName name="std_num_19" localSheetId="1">'3er Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="1">'3er Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="1">'3er Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="1">'3er Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="1">'3er Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="1">'3er Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="1">'3er Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="1">'3er Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="1">'3er Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="1">'3er Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="1">'3er Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="1">'3er Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="1">'3er Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="1">'3er Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="1">'3er Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="1">'3er Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="1">'3er Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="1">'3er Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="1">'3er Año'!$V$34</definedName>
+    <definedName name="grade_10_19" localSheetId="1">'3er Año'!$W$34</definedName>
+    <definedName name="std_part_19" localSheetId="1">'3er Año'!$X$34</definedName>
+    <definedName name="std_num_20" localSheetId="1">'3er Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="1">'3er Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="1">'3er Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="1">'3er Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="1">'3er Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="1">'3er Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="1">'3er Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="1">'3er Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="1">'3er Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="1">'3er Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="1">'3er Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="1">'3er Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="1">'3er Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="1">'3er Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="1">'3er Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="1">'3er Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="1">'3er Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="1">'3er Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="1">'3er Año'!$V$35</definedName>
+    <definedName name="grade_10_20" localSheetId="1">'3er Año'!$W$35</definedName>
+    <definedName name="std_part_20" localSheetId="1">'3er Año'!$X$35</definedName>
+    <definedName name="std_num_21" localSheetId="1">'3er Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="1">'3er Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="1">'3er Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="1">'3er Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="1">'3er Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="1">'3er Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="1">'3er Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="1">'3er Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="1">'3er Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="1">'3er Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="1">'3er Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="1">'3er Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="1">'3er Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="1">'3er Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="1">'3er Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="1">'3er Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="1">'3er Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="1">'3er Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="1">'3er Año'!$V$36</definedName>
+    <definedName name="grade_10_21" localSheetId="1">'3er Año'!$W$36</definedName>
+    <definedName name="std_part_21" localSheetId="1">'3er Año'!$X$36</definedName>
+    <definedName name="std_num_22" localSheetId="1">'3er Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="1">'3er Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="1">'3er Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="1">'3er Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="1">'3er Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="1">'3er Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="1">'3er Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="1">'3er Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="1">'3er Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="1">'3er Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="1">'3er Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="1">'3er Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="1">'3er Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="1">'3er Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="1">'3er Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="1">'3er Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="1">'3er Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="1">'3er Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="1">'3er Año'!$V$37</definedName>
+    <definedName name="grade_10_22" localSheetId="1">'3er Año'!$W$37</definedName>
+    <definedName name="std_part_22" localSheetId="1">'3er Año'!$X$37</definedName>
+    <definedName name="std_num_23" localSheetId="1">'3er Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="1">'3er Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="1">'3er Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="1">'3er Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="1">'3er Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="1">'3er Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="1">'3er Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="1">'3er Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="1">'3er Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="1">'3er Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="1">'3er Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="1">'3er Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="1">'3er Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="1">'3er Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="1">'3er Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="1">'3er Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="1">'3er Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="1">'3er Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="1">'3er Año'!$V$38</definedName>
+    <definedName name="grade_10_23" localSheetId="1">'3er Año'!$W$38</definedName>
+    <definedName name="std_part_23" localSheetId="1">'3er Año'!$X$38</definedName>
+    <definedName name="std_num_24" localSheetId="1">'3er Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="1">'3er Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="1">'3er Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="1">'3er Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="1">'3er Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="1">'3er Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="1">'3er Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="1">'3er Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="1">'3er Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="1">'3er Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="1">'3er Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="1">'3er Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="1">'3er Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="1">'3er Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="1">'3er Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="1">'3er Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="1">'3er Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="1">'3er Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="1">'3er Año'!$V$39</definedName>
+    <definedName name="grade_10_24" localSheetId="1">'3er Año'!$W$39</definedName>
+    <definedName name="std_part_24" localSheetId="1">'3er Año'!$X$39</definedName>
+    <definedName name="std_num_25" localSheetId="1">'3er Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="1">'3er Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="1">'3er Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="1">'3er Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="1">'3er Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="1">'3er Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="1">'3er Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="1">'3er Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="1">'3er Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="1">'3er Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="1">'3er Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="1">'3er Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="1">'3er Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="1">'3er Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="1">'3er Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="1">'3er Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="1">'3er Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="1">'3er Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="1">'3er Año'!$V$40</definedName>
+    <definedName name="grade_10_25" localSheetId="1">'3er Año'!$W$40</definedName>
+    <definedName name="std_part_25" localSheetId="1">'3er Año'!$X$40</definedName>
+    <definedName name="std_num_26" localSheetId="1">'3er Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="1">'3er Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="1">'3er Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="1">'3er Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="1">'3er Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="1">'3er Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="1">'3er Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="1">'3er Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="1">'3er Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="1">'3er Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="1">'3er Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="1">'3er Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="1">'3er Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="1">'3er Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="1">'3er Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="1">'3er Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="1">'3er Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="1">'3er Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="1">'3er Año'!$V$41</definedName>
+    <definedName name="grade_10_26" localSheetId="1">'3er Año'!$W$41</definedName>
+    <definedName name="std_part_26" localSheetId="1">'3er Año'!$X$41</definedName>
+    <definedName name="std_num_27" localSheetId="1">'3er Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="1">'3er Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="1">'3er Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="1">'3er Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="1">'3er Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="1">'3er Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="1">'3er Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="1">'3er Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="1">'3er Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="1">'3er Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="1">'3er Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="1">'3er Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="1">'3er Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="1">'3er Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="1">'3er Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="1">'3er Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="1">'3er Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="1">'3er Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="1">'3er Año'!$V$42</definedName>
+    <definedName name="grade_10_27" localSheetId="1">'3er Año'!$W$42</definedName>
+    <definedName name="std_part_27" localSheetId="1">'3er Año'!$X$42</definedName>
+    <definedName name="std_num_28" localSheetId="1">'3er Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="1">'3er Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="1">'3er Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="1">'3er Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="1">'3er Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="1">'3er Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="1">'3er Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="1">'3er Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="1">'3er Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="1">'3er Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="1">'3er Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="1">'3er Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="1">'3er Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="1">'3er Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="1">'3er Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="1">'3er Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="1">'3er Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="1">'3er Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="1">'3er Año'!$V$43</definedName>
+    <definedName name="grade_10_28" localSheetId="1">'3er Año'!$W$43</definedName>
+    <definedName name="std_part_28" localSheetId="1">'3er Año'!$X$43</definedName>
+    <definedName name="std_num_29" localSheetId="1">'3er Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="1">'3er Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="1">'3er Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="1">'3er Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="1">'3er Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="1">'3er Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="1">'3er Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="1">'3er Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="1">'3er Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="1">'3er Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="1">'3er Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="1">'3er Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="1">'3er Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="1">'3er Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="1">'3er Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="1">'3er Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="1">'3er Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="1">'3er Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="1">'3er Año'!$V$44</definedName>
+    <definedName name="grade_10_29" localSheetId="1">'3er Año'!$W$44</definedName>
+    <definedName name="std_part_29" localSheetId="1">'3er Año'!$X$44</definedName>
+    <definedName name="std_num_30" localSheetId="1">'3er Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="1">'3er Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="1">'3er Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="1">'3er Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="1">'3er Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="1">'3er Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="1">'3er Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="1">'3er Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="1">'3er Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="1">'3er Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="1">'3er Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="1">'3er Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="1">'3er Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="1">'3er Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="1">'3er Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="1">'3er Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="1">'3er Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="1">'3er Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="1">'3er Año'!$V$45</definedName>
+    <definedName name="grade_10_30" localSheetId="1">'3er Año'!$W$45</definedName>
+    <definedName name="std_part_30" localSheetId="1">'3er Año'!$X$45</definedName>
+    <definedName name="std_num_31" localSheetId="1">'3er Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="1">'3er Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="1">'3er Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="1">'3er Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="1">'3er Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="1">'3er Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="1">'3er Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="1">'3er Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="1">'3er Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="1">'3er Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="1">'3er Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="1">'3er Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="1">'3er Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="1">'3er Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="1">'3er Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="1">'3er Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="1">'3er Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="1">'3er Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="1">'3er Año'!$V$46</definedName>
+    <definedName name="grade_10_31" localSheetId="1">'3er Año'!$W$46</definedName>
+    <definedName name="std_part_31" localSheetId="1">'3er Año'!$X$46</definedName>
+    <definedName name="std_num_32" localSheetId="1">'3er Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="1">'3er Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="1">'3er Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="1">'3er Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="1">'3er Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="1">'3er Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="1">'3er Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="1">'3er Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="1">'3er Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="1">'3er Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="1">'3er Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="1">'3er Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="1">'3er Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="1">'3er Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="1">'3er Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="1">'3er Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="1">'3er Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="1">'3er Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="1">'3er Año'!$V$47</definedName>
+    <definedName name="grade_10_32" localSheetId="1">'3er Año'!$W$47</definedName>
+    <definedName name="std_part_32" localSheetId="1">'3er Año'!$X$47</definedName>
+    <definedName name="std_num_33" localSheetId="1">'3er Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="1">'3er Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="1">'3er Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="1">'3er Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="1">'3er Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="1">'3er Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="1">'3er Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="1">'3er Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="1">'3er Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="1">'3er Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="1">'3er Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="1">'3er Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="1">'3er Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="1">'3er Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="1">'3er Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="1">'3er Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="1">'3er Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="1">'3er Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="1">'3er Año'!$V$48</definedName>
+    <definedName name="grade_10_33" localSheetId="1">'3er Año'!$W$48</definedName>
+    <definedName name="std_part_33" localSheetId="1">'3er Año'!$X$48</definedName>
+    <definedName name="std_num_34" localSheetId="1">'3er Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="1">'3er Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="1">'3er Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="1">'3er Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="1">'3er Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="1">'3er Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="1">'3er Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="1">'3er Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="1">'3er Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="1">'3er Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="1">'3er Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="1">'3er Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="1">'3er Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="1">'3er Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="1">'3er Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="1">'3er Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="1">'3er Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="1">'3er Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="1">'3er Año'!$V$49</definedName>
+    <definedName name="grade_10_34" localSheetId="1">'3er Año'!$W$49</definedName>
+    <definedName name="std_part_34" localSheetId="1">'3er Año'!$X$49</definedName>
+    <definedName name="std_num_35" localSheetId="1">'3er Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="1">'3er Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="1">'3er Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="1">'3er Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="1">'3er Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="1">'3er Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="1">'3er Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="1">'3er Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="1">'3er Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="1">'3er Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="1">'3er Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="1">'3er Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="1">'3er Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="1">'3er Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="1">'3er Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="1">'3er Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="1">'3er Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="1">'3er Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="1">'3er Año'!$V$50</definedName>
+    <definedName name="grade_10_35" localSheetId="1">'3er Año'!$W$50</definedName>
+    <definedName name="std_part_35" localSheetId="1">'3er Año'!$X$50</definedName>
+    <definedName name="inst_period" localSheetId="2">'4to Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="2">'4to Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="2">'4to Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="2">'4to Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="2">'4to Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="2">'4to Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="2">'4to Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="2">'4to Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="2">'4to Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="2">'4to Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="2">'4to Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="2">'4to Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="2">'4to Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="2">'4to Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="2">'4to Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="2">'4to Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="2">'4to Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="2">'4to Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="2">'4to Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="2">'4to Año'!$V$15</definedName>
+    <definedName name="subj_10" localSheetId="2">'4to Año'!$W$15</definedName>
+    <definedName name="subj_11" localSheetId="2">'4to Año'!$X$15</definedName>
+    <definedName name="std_num_1" localSheetId="2">'4to Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="2">'4to Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="2">'4to Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="2">'4to Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="2">'4to Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="2">'4to Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="2">'4to Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="2">'4to Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="2">'4to Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="2">'4to Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="2">'4to Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="2">'4to Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="2">'4to Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="2">'4to Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="2">'4to Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="2">'4to Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="2">'4to Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="2">'4to Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="2">'4to Año'!$V$16</definedName>
+    <definedName name="grade_10_1" localSheetId="2">'4to Año'!$W$16</definedName>
+    <definedName name="grade_11_1" localSheetId="2">'4to Año'!$X$16</definedName>
+    <definedName name="std_part_1" localSheetId="2">'4to Año'!$Y$16</definedName>
+    <definedName name="std_num_2" localSheetId="2">'4to Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="2">'4to Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="2">'4to Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="2">'4to Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="2">'4to Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="2">'4to Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="2">'4to Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="2">'4to Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="2">'4to Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="2">'4to Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="2">'4to Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="2">'4to Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="2">'4to Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="2">'4to Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="2">'4to Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="2">'4to Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="2">'4to Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="2">'4to Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="2">'4to Año'!$V$17</definedName>
+    <definedName name="grade_10_2" localSheetId="2">'4to Año'!$W$17</definedName>
+    <definedName name="grade_11_2" localSheetId="2">'4to Año'!$X$17</definedName>
+    <definedName name="std_part_2" localSheetId="2">'4to Año'!$Y$17</definedName>
+    <definedName name="std_num_3" localSheetId="2">'4to Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="2">'4to Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="2">'4to Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="2">'4to Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="2">'4to Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="2">'4to Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="2">'4to Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="2">'4to Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="2">'4to Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="2">'4to Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="2">'4to Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="2">'4to Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="2">'4to Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="2">'4to Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="2">'4to Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="2">'4to Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="2">'4to Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="2">'4to Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="2">'4to Año'!$V$18</definedName>
+    <definedName name="grade_10_3" localSheetId="2">'4to Año'!$W$18</definedName>
+    <definedName name="grade_11_3" localSheetId="2">'4to Año'!$X$18</definedName>
+    <definedName name="std_part_3" localSheetId="2">'4to Año'!$Y$18</definedName>
+    <definedName name="std_num_4" localSheetId="2">'4to Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="2">'4to Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="2">'4to Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="2">'4to Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="2">'4to Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="2">'4to Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="2">'4to Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="2">'4to Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="2">'4to Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="2">'4to Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="2">'4to Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="2">'4to Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="2">'4to Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="2">'4to Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="2">'4to Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="2">'4to Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="2">'4to Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="2">'4to Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="2">'4to Año'!$V$19</definedName>
+    <definedName name="grade_10_4" localSheetId="2">'4to Año'!$W$19</definedName>
+    <definedName name="grade_11_4" localSheetId="2">'4to Año'!$X$19</definedName>
+    <definedName name="std_part_4" localSheetId="2">'4to Año'!$Y$19</definedName>
+    <definedName name="std_num_5" localSheetId="2">'4to Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="2">'4to Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="2">'4to Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="2">'4to Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="2">'4to Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="2">'4to Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="2">'4to Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="2">'4to Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="2">'4to Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="2">'4to Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="2">'4to Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="2">'4to Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="2">'4to Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="2">'4to Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="2">'4to Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="2">'4to Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="2">'4to Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="2">'4to Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="2">'4to Año'!$V$20</definedName>
+    <definedName name="grade_10_5" localSheetId="2">'4to Año'!$W$20</definedName>
+    <definedName name="grade_11_5" localSheetId="2">'4to Año'!$X$20</definedName>
+    <definedName name="std_part_5" localSheetId="2">'4to Año'!$Y$20</definedName>
+    <definedName name="std_num_6" localSheetId="2">'4to Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="2">'4to Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="2">'4to Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="2">'4to Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="2">'4to Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="2">'4to Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="2">'4to Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="2">'4to Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="2">'4to Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="2">'4to Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="2">'4to Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="2">'4to Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="2">'4to Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="2">'4to Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="2">'4to Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="2">'4to Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="2">'4to Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="2">'4to Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="2">'4to Año'!$V$21</definedName>
+    <definedName name="grade_10_6" localSheetId="2">'4to Año'!$W$21</definedName>
+    <definedName name="grade_11_6" localSheetId="2">'4to Año'!$X$21</definedName>
+    <definedName name="std_part_6" localSheetId="2">'4to Año'!$Y$21</definedName>
+    <definedName name="std_num_7" localSheetId="2">'4to Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="2">'4to Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="2">'4to Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="2">'4to Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="2">'4to Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="2">'4to Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="2">'4to Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="2">'4to Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="2">'4to Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="2">'4to Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="2">'4to Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="2">'4to Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="2">'4to Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="2">'4to Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="2">'4to Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="2">'4to Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="2">'4to Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="2">'4to Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="2">'4to Año'!$V$22</definedName>
+    <definedName name="grade_10_7" localSheetId="2">'4to Año'!$W$22</definedName>
+    <definedName name="grade_11_7" localSheetId="2">'4to Año'!$X$22</definedName>
+    <definedName name="std_part_7" localSheetId="2">'4to Año'!$Y$22</definedName>
+    <definedName name="std_num_8" localSheetId="2">'4to Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="2">'4to Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="2">'4to Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="2">'4to Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="2">'4to Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="2">'4to Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="2">'4to Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="2">'4to Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="2">'4to Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="2">'4to Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="2">'4to Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="2">'4to Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="2">'4to Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="2">'4to Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="2">'4to Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="2">'4to Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="2">'4to Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="2">'4to Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="2">'4to Año'!$V$23</definedName>
+    <definedName name="grade_10_8" localSheetId="2">'4to Año'!$W$23</definedName>
+    <definedName name="grade_11_8" localSheetId="2">'4to Año'!$X$23</definedName>
+    <definedName name="std_part_8" localSheetId="2">'4to Año'!$Y$23</definedName>
+    <definedName name="std_num_9" localSheetId="2">'4to Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="2">'4to Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="2">'4to Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="2">'4to Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="2">'4to Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="2">'4to Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="2">'4to Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="2">'4to Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="2">'4to Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="2">'4to Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="2">'4to Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="2">'4to Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="2">'4to Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="2">'4to Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="2">'4to Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="2">'4to Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="2">'4to Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="2">'4to Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="2">'4to Año'!$V$24</definedName>
+    <definedName name="grade_10_9" localSheetId="2">'4to Año'!$W$24</definedName>
+    <definedName name="grade_11_9" localSheetId="2">'4to Año'!$X$24</definedName>
+    <definedName name="std_part_9" localSheetId="2">'4to Año'!$Y$24</definedName>
+    <definedName name="std_num_10" localSheetId="2">'4to Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="2">'4to Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="2">'4to Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="2">'4to Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="2">'4to Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="2">'4to Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="2">'4to Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="2">'4to Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="2">'4to Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="2">'4to Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="2">'4to Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="2">'4to Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="2">'4to Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="2">'4to Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="2">'4to Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="2">'4to Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="2">'4to Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="2">'4to Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="2">'4to Año'!$V$25</definedName>
+    <definedName name="grade_10_10" localSheetId="2">'4to Año'!$W$25</definedName>
+    <definedName name="grade_11_10" localSheetId="2">'4to Año'!$X$25</definedName>
+    <definedName name="std_part_10" localSheetId="2">'4to Año'!$Y$25</definedName>
+    <definedName name="std_num_11" localSheetId="2">'4to Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="2">'4to Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="2">'4to Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="2">'4to Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="2">'4to Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="2">'4to Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="2">'4to Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="2">'4to Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="2">'4to Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="2">'4to Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="2">'4to Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="2">'4to Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="2">'4to Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="2">'4to Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="2">'4to Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="2">'4to Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="2">'4to Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="2">'4to Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="2">'4to Año'!$V$26</definedName>
+    <definedName name="grade_10_11" localSheetId="2">'4to Año'!$W$26</definedName>
+    <definedName name="grade_11_11" localSheetId="2">'4to Año'!$X$26</definedName>
+    <definedName name="std_part_11" localSheetId="2">'4to Año'!$Y$26</definedName>
+    <definedName name="std_num_12" localSheetId="2">'4to Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="2">'4to Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="2">'4to Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="2">'4to Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="2">'4to Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="2">'4to Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="2">'4to Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="2">'4to Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="2">'4to Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="2">'4to Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="2">'4to Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="2">'4to Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="2">'4to Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="2">'4to Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="2">'4to Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="2">'4to Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="2">'4to Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="2">'4to Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="2">'4to Año'!$V$27</definedName>
+    <definedName name="grade_10_12" localSheetId="2">'4to Año'!$W$27</definedName>
+    <definedName name="grade_11_12" localSheetId="2">'4to Año'!$X$27</definedName>
+    <definedName name="std_part_12" localSheetId="2">'4to Año'!$Y$27</definedName>
+    <definedName name="std_num_13" localSheetId="2">'4to Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="2">'4to Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="2">'4to Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="2">'4to Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="2">'4to Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="2">'4to Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="2">'4to Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="2">'4to Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="2">'4to Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="2">'4to Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="2">'4to Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="2">'4to Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="2">'4to Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="2">'4to Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="2">'4to Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="2">'4to Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="2">'4to Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="2">'4to Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="2">'4to Año'!$V$28</definedName>
+    <definedName name="grade_10_13" localSheetId="2">'4to Año'!$W$28</definedName>
+    <definedName name="grade_11_13" localSheetId="2">'4to Año'!$X$28</definedName>
+    <definedName name="std_part_13" localSheetId="2">'4to Año'!$Y$28</definedName>
+    <definedName name="std_num_14" localSheetId="2">'4to Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="2">'4to Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="2">'4to Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="2">'4to Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="2">'4to Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="2">'4to Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="2">'4to Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="2">'4to Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="2">'4to Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="2">'4to Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="2">'4to Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="2">'4to Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="2">'4to Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="2">'4to Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="2">'4to Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="2">'4to Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="2">'4to Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="2">'4to Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="2">'4to Año'!$V$29</definedName>
+    <definedName name="grade_10_14" localSheetId="2">'4to Año'!$W$29</definedName>
+    <definedName name="grade_11_14" localSheetId="2">'4to Año'!$X$29</definedName>
+    <definedName name="std_part_14" localSheetId="2">'4to Año'!$Y$29</definedName>
+    <definedName name="std_num_15" localSheetId="2">'4to Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="2">'4to Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="2">'4to Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="2">'4to Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="2">'4to Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="2">'4to Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="2">'4to Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="2">'4to Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="2">'4to Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="2">'4to Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="2">'4to Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="2">'4to Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="2">'4to Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="2">'4to Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="2">'4to Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="2">'4to Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="2">'4to Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="2">'4to Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="2">'4to Año'!$V$30</definedName>
+    <definedName name="grade_10_15" localSheetId="2">'4to Año'!$W$30</definedName>
+    <definedName name="grade_11_15" localSheetId="2">'4to Año'!$X$30</definedName>
+    <definedName name="std_part_15" localSheetId="2">'4to Año'!$Y$30</definedName>
+    <definedName name="std_num_16" localSheetId="2">'4to Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="2">'4to Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="2">'4to Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="2">'4to Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="2">'4to Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="2">'4to Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="2">'4to Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="2">'4to Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="2">'4to Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="2">'4to Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="2">'4to Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="2">'4to Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="2">'4to Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="2">'4to Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="2">'4to Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="2">'4to Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="2">'4to Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="2">'4to Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="2">'4to Año'!$V$31</definedName>
+    <definedName name="grade_10_16" localSheetId="2">'4to Año'!$W$31</definedName>
+    <definedName name="grade_11_16" localSheetId="2">'4to Año'!$X$31</definedName>
+    <definedName name="std_part_16" localSheetId="2">'4to Año'!$Y$31</definedName>
+    <definedName name="std_num_17" localSheetId="2">'4to Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="2">'4to Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="2">'4to Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="2">'4to Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="2">'4to Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="2">'4to Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="2">'4to Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="2">'4to Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="2">'4to Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="2">'4to Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="2">'4to Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="2">'4to Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="2">'4to Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="2">'4to Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="2">'4to Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="2">'4to Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="2">'4to Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="2">'4to Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="2">'4to Año'!$V$32</definedName>
+    <definedName name="grade_10_17" localSheetId="2">'4to Año'!$W$32</definedName>
+    <definedName name="grade_11_17" localSheetId="2">'4to Año'!$X$32</definedName>
+    <definedName name="std_part_17" localSheetId="2">'4to Año'!$Y$32</definedName>
+    <definedName name="std_num_18" localSheetId="2">'4to Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="2">'4to Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="2">'4to Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="2">'4to Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="2">'4to Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="2">'4to Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="2">'4to Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="2">'4to Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="2">'4to Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="2">'4to Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="2">'4to Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="2">'4to Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="2">'4to Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="2">'4to Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="2">'4to Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="2">'4to Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="2">'4to Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="2">'4to Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="2">'4to Año'!$V$33</definedName>
+    <definedName name="grade_10_18" localSheetId="2">'4to Año'!$W$33</definedName>
+    <definedName name="grade_11_18" localSheetId="2">'4to Año'!$X$33</definedName>
+    <definedName name="std_part_18" localSheetId="2">'4to Año'!$Y$33</definedName>
+    <definedName name="std_num_19" localSheetId="2">'4to Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="2">'4to Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="2">'4to Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="2">'4to Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="2">'4to Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="2">'4to Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="2">'4to Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="2">'4to Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="2">'4to Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="2">'4to Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="2">'4to Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="2">'4to Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="2">'4to Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="2">'4to Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="2">'4to Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="2">'4to Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="2">'4to Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="2">'4to Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="2">'4to Año'!$V$34</definedName>
+    <definedName name="grade_10_19" localSheetId="2">'4to Año'!$W$34</definedName>
+    <definedName name="grade_11_19" localSheetId="2">'4to Año'!$X$34</definedName>
+    <definedName name="std_part_19" localSheetId="2">'4to Año'!$Y$34</definedName>
+    <definedName name="std_num_20" localSheetId="2">'4to Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="2">'4to Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="2">'4to Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="2">'4to Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="2">'4to Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="2">'4to Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="2">'4to Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="2">'4to Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="2">'4to Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="2">'4to Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="2">'4to Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="2">'4to Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="2">'4to Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="2">'4to Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="2">'4to Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="2">'4to Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="2">'4to Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="2">'4to Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="2">'4to Año'!$V$35</definedName>
+    <definedName name="grade_10_20" localSheetId="2">'4to Año'!$W$35</definedName>
+    <definedName name="grade_11_20" localSheetId="2">'4to Año'!$X$35</definedName>
+    <definedName name="std_part_20" localSheetId="2">'4to Año'!$Y$35</definedName>
+    <definedName name="std_num_21" localSheetId="2">'4to Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="2">'4to Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="2">'4to Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="2">'4to Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="2">'4to Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="2">'4to Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="2">'4to Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="2">'4to Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="2">'4to Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="2">'4to Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="2">'4to Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="2">'4to Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="2">'4to Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="2">'4to Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="2">'4to Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="2">'4to Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="2">'4to Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="2">'4to Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="2">'4to Año'!$V$36</definedName>
+    <definedName name="grade_10_21" localSheetId="2">'4to Año'!$W$36</definedName>
+    <definedName name="grade_11_21" localSheetId="2">'4to Año'!$X$36</definedName>
+    <definedName name="std_part_21" localSheetId="2">'4to Año'!$Y$36</definedName>
+    <definedName name="std_num_22" localSheetId="2">'4to Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="2">'4to Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="2">'4to Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="2">'4to Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="2">'4to Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="2">'4to Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="2">'4to Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="2">'4to Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="2">'4to Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="2">'4to Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="2">'4to Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="2">'4to Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="2">'4to Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="2">'4to Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="2">'4to Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="2">'4to Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="2">'4to Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="2">'4to Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="2">'4to Año'!$V$37</definedName>
+    <definedName name="grade_10_22" localSheetId="2">'4to Año'!$W$37</definedName>
+    <definedName name="grade_11_22" localSheetId="2">'4to Año'!$X$37</definedName>
+    <definedName name="std_part_22" localSheetId="2">'4to Año'!$Y$37</definedName>
+    <definedName name="std_num_23" localSheetId="2">'4to Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="2">'4to Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="2">'4to Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="2">'4to Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="2">'4to Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="2">'4to Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="2">'4to Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="2">'4to Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="2">'4to Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="2">'4to Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="2">'4to Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="2">'4to Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="2">'4to Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="2">'4to Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="2">'4to Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="2">'4to Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="2">'4to Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="2">'4to Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="2">'4to Año'!$V$38</definedName>
+    <definedName name="grade_10_23" localSheetId="2">'4to Año'!$W$38</definedName>
+    <definedName name="grade_11_23" localSheetId="2">'4to Año'!$X$38</definedName>
+    <definedName name="std_part_23" localSheetId="2">'4to Año'!$Y$38</definedName>
+    <definedName name="std_num_24" localSheetId="2">'4to Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="2">'4to Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="2">'4to Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="2">'4to Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="2">'4to Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="2">'4to Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="2">'4to Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="2">'4to Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="2">'4to Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="2">'4to Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="2">'4to Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="2">'4to Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="2">'4to Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="2">'4to Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="2">'4to Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="2">'4to Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="2">'4to Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="2">'4to Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="2">'4to Año'!$V$39</definedName>
+    <definedName name="grade_10_24" localSheetId="2">'4to Año'!$W$39</definedName>
+    <definedName name="grade_11_24" localSheetId="2">'4to Año'!$X$39</definedName>
+    <definedName name="std_part_24" localSheetId="2">'4to Año'!$Y$39</definedName>
+    <definedName name="std_num_25" localSheetId="2">'4to Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="2">'4to Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="2">'4to Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="2">'4to Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="2">'4to Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="2">'4to Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="2">'4to Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="2">'4to Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="2">'4to Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="2">'4to Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="2">'4to Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="2">'4to Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="2">'4to Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="2">'4to Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="2">'4to Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="2">'4to Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="2">'4to Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="2">'4to Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="2">'4to Año'!$V$40</definedName>
+    <definedName name="grade_10_25" localSheetId="2">'4to Año'!$W$40</definedName>
+    <definedName name="grade_11_25" localSheetId="2">'4to Año'!$X$40</definedName>
+    <definedName name="std_part_25" localSheetId="2">'4to Año'!$Y$40</definedName>
+    <definedName name="std_num_26" localSheetId="2">'4to Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="2">'4to Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="2">'4to Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="2">'4to Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="2">'4to Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="2">'4to Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="2">'4to Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="2">'4to Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="2">'4to Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="2">'4to Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="2">'4to Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="2">'4to Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="2">'4to Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="2">'4to Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="2">'4to Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="2">'4to Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="2">'4to Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="2">'4to Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="2">'4to Año'!$V$41</definedName>
+    <definedName name="grade_10_26" localSheetId="2">'4to Año'!$W$41</definedName>
+    <definedName name="grade_11_26" localSheetId="2">'4to Año'!$X$41</definedName>
+    <definedName name="std_part_26" localSheetId="2">'4to Año'!$Y$41</definedName>
+    <definedName name="std_num_27" localSheetId="2">'4to Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="2">'4to Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="2">'4to Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="2">'4to Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="2">'4to Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="2">'4to Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="2">'4to Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="2">'4to Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="2">'4to Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="2">'4to Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="2">'4to Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="2">'4to Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="2">'4to Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="2">'4to Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="2">'4to Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="2">'4to Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="2">'4to Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="2">'4to Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="2">'4to Año'!$V$42</definedName>
+    <definedName name="grade_10_27" localSheetId="2">'4to Año'!$W$42</definedName>
+    <definedName name="grade_11_27" localSheetId="2">'4to Año'!$X$42</definedName>
+    <definedName name="std_part_27" localSheetId="2">'4to Año'!$Y$42</definedName>
+    <definedName name="std_num_28" localSheetId="2">'4to Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="2">'4to Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="2">'4to Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="2">'4to Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="2">'4to Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="2">'4to Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="2">'4to Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="2">'4to Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="2">'4to Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="2">'4to Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="2">'4to Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="2">'4to Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="2">'4to Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="2">'4to Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="2">'4to Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="2">'4to Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="2">'4to Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="2">'4to Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="2">'4to Año'!$V$43</definedName>
+    <definedName name="grade_10_28" localSheetId="2">'4to Año'!$W$43</definedName>
+    <definedName name="grade_11_28" localSheetId="2">'4to Año'!$X$43</definedName>
+    <definedName name="std_part_28" localSheetId="2">'4to Año'!$Y$43</definedName>
+    <definedName name="std_num_29" localSheetId="2">'4to Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="2">'4to Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="2">'4to Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="2">'4to Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="2">'4to Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="2">'4to Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="2">'4to Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="2">'4to Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="2">'4to Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="2">'4to Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="2">'4to Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="2">'4to Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="2">'4to Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="2">'4to Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="2">'4to Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="2">'4to Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="2">'4to Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="2">'4to Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="2">'4to Año'!$V$44</definedName>
+    <definedName name="grade_10_29" localSheetId="2">'4to Año'!$W$44</definedName>
+    <definedName name="grade_11_29" localSheetId="2">'4to Año'!$X$44</definedName>
+    <definedName name="std_part_29" localSheetId="2">'4to Año'!$Y$44</definedName>
+    <definedName name="std_num_30" localSheetId="2">'4to Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="2">'4to Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="2">'4to Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="2">'4to Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="2">'4to Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="2">'4to Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="2">'4to Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="2">'4to Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="2">'4to Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="2">'4to Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="2">'4to Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="2">'4to Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="2">'4to Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="2">'4to Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="2">'4to Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="2">'4to Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="2">'4to Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="2">'4to Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="2">'4to Año'!$V$45</definedName>
+    <definedName name="grade_10_30" localSheetId="2">'4to Año'!$W$45</definedName>
+    <definedName name="grade_11_30" localSheetId="2">'4to Año'!$X$45</definedName>
+    <definedName name="std_part_30" localSheetId="2">'4to Año'!$Y$45</definedName>
+    <definedName name="std_num_31" localSheetId="2">'4to Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="2">'4to Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="2">'4to Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="2">'4to Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="2">'4to Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="2">'4to Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="2">'4to Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="2">'4to Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="2">'4to Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="2">'4to Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="2">'4to Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="2">'4to Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="2">'4to Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="2">'4to Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="2">'4to Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="2">'4to Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="2">'4to Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="2">'4to Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="2">'4to Año'!$V$46</definedName>
+    <definedName name="grade_10_31" localSheetId="2">'4to Año'!$W$46</definedName>
+    <definedName name="grade_11_31" localSheetId="2">'4to Año'!$X$46</definedName>
+    <definedName name="std_part_31" localSheetId="2">'4to Año'!$Y$46</definedName>
+    <definedName name="std_num_32" localSheetId="2">'4to Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="2">'4to Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="2">'4to Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="2">'4to Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="2">'4to Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="2">'4to Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="2">'4to Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="2">'4to Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="2">'4to Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="2">'4to Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="2">'4to Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="2">'4to Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="2">'4to Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="2">'4to Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="2">'4to Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="2">'4to Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="2">'4to Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="2">'4to Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="2">'4to Año'!$V$47</definedName>
+    <definedName name="grade_10_32" localSheetId="2">'4to Año'!$W$47</definedName>
+    <definedName name="grade_11_32" localSheetId="2">'4to Año'!$X$47</definedName>
+    <definedName name="std_part_32" localSheetId="2">'4to Año'!$Y$47</definedName>
+    <definedName name="std_num_33" localSheetId="2">'4to Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="2">'4to Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="2">'4to Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="2">'4to Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="2">'4to Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="2">'4to Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="2">'4to Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="2">'4to Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="2">'4to Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="2">'4to Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="2">'4to Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="2">'4to Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="2">'4to Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="2">'4to Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="2">'4to Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="2">'4to Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="2">'4to Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="2">'4to Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="2">'4to Año'!$V$48</definedName>
+    <definedName name="grade_10_33" localSheetId="2">'4to Año'!$W$48</definedName>
+    <definedName name="grade_11_33" localSheetId="2">'4to Año'!$X$48</definedName>
+    <definedName name="std_part_33" localSheetId="2">'4to Año'!$Y$48</definedName>
+    <definedName name="std_num_34" localSheetId="2">'4to Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="2">'4to Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="2">'4to Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="2">'4to Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="2">'4to Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="2">'4to Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="2">'4to Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="2">'4to Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="2">'4to Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="2">'4to Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="2">'4to Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="2">'4to Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="2">'4to Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="2">'4to Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="2">'4to Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="2">'4to Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="2">'4to Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="2">'4to Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="2">'4to Año'!$V$49</definedName>
+    <definedName name="grade_10_34" localSheetId="2">'4to Año'!$W$49</definedName>
+    <definedName name="grade_11_34" localSheetId="2">'4to Año'!$X$49</definedName>
+    <definedName name="std_part_34" localSheetId="2">'4to Año'!$Y$49</definedName>
+    <definedName name="std_num_35" localSheetId="2">'4to Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="2">'4to Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="2">'4to Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="2">'4to Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="2">'4to Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="2">'4to Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="2">'4to Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="2">'4to Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="2">'4to Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="2">'4to Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="2">'4to Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="2">'4to Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="2">'4to Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="2">'4to Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="2">'4to Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="2">'4to Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="2">'4to Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="2">'4to Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="2">'4to Año'!$V$50</definedName>
+    <definedName name="grade_10_35" localSheetId="2">'4to Año'!$W$50</definedName>
+    <definedName name="grade_11_35" localSheetId="2">'4to Año'!$X$50</definedName>
+    <definedName name="std_part_35" localSheetId="2">'4to Año'!$Y$50</definedName>
+    <definedName name="inst_period" localSheetId="3">'5to Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="3">'5to Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="3">'5to Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="3">'5to Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="3">'5to Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="3">'5to Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="3">'5to Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="3">'5to Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="3">'5to Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="3">'5to Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="3">'5to Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="3">'5to Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="3">'5to Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="3">'5to Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="3">'5to Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="3">'5to Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="3">'5to Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="3">'5to Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="3">'5to Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="3">'5to Año'!$V$15</definedName>
+    <definedName name="subj_10" localSheetId="3">'5to Año'!$W$15</definedName>
+    <definedName name="subj_11" localSheetId="3">'5to Año'!$X$15</definedName>
+    <definedName name="subj_12" localSheetId="3">'5to Año'!$Y$15</definedName>
+    <definedName name="std_num_1" localSheetId="3">'5to Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="3">'5to Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="3">'5to Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="3">'5to Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="3">'5to Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="3">'5to Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="3">'5to Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="3">'5to Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="3">'5to Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="3">'5to Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="3">'5to Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="3">'5to Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="3">'5to Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="3">'5to Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="3">'5to Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="3">'5to Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="3">'5to Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="3">'5to Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="3">'5to Año'!$V$16</definedName>
+    <definedName name="grade_10_1" localSheetId="3">'5to Año'!$W$16</definedName>
+    <definedName name="grade_11_1" localSheetId="3">'5to Año'!$X$16</definedName>
+    <definedName name="grade_12_1" localSheetId="3">'5to Año'!$Y$16</definedName>
+    <definedName name="std_part_1" localSheetId="3">'5to Año'!$Z$16</definedName>
+    <definedName name="std_num_2" localSheetId="3">'5to Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="3">'5to Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="3">'5to Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="3">'5to Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="3">'5to Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="3">'5to Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="3">'5to Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="3">'5to Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="3">'5to Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="3">'5to Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="3">'5to Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="3">'5to Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="3">'5to Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="3">'5to Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="3">'5to Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="3">'5to Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="3">'5to Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="3">'5to Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="3">'5to Año'!$V$17</definedName>
+    <definedName name="grade_10_2" localSheetId="3">'5to Año'!$W$17</definedName>
+    <definedName name="grade_11_2" localSheetId="3">'5to Año'!$X$17</definedName>
+    <definedName name="grade_12_2" localSheetId="3">'5to Año'!$Y$17</definedName>
+    <definedName name="std_part_2" localSheetId="3">'5to Año'!$Z$17</definedName>
+    <definedName name="std_num_3" localSheetId="3">'5to Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="3">'5to Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="3">'5to Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="3">'5to Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="3">'5to Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="3">'5to Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="3">'5to Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="3">'5to Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="3">'5to Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="3">'5to Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="3">'5to Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="3">'5to Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="3">'5to Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="3">'5to Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="3">'5to Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="3">'5to Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="3">'5to Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="3">'5to Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="3">'5to Año'!$V$18</definedName>
+    <definedName name="grade_10_3" localSheetId="3">'5to Año'!$W$18</definedName>
+    <definedName name="grade_11_3" localSheetId="3">'5to Año'!$X$18</definedName>
+    <definedName name="grade_12_3" localSheetId="3">'5to Año'!$Y$18</definedName>
+    <definedName name="std_part_3" localSheetId="3">'5to Año'!$Z$18</definedName>
+    <definedName name="std_num_4" localSheetId="3">'5to Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="3">'5to Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="3">'5to Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="3">'5to Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="3">'5to Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="3">'5to Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="3">'5to Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="3">'5to Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="3">'5to Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="3">'5to Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="3">'5to Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="3">'5to Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="3">'5to Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="3">'5to Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="3">'5to Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="3">'5to Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="3">'5to Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="3">'5to Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="3">'5to Año'!$V$19</definedName>
+    <definedName name="grade_10_4" localSheetId="3">'5to Año'!$W$19</definedName>
+    <definedName name="grade_11_4" localSheetId="3">'5to Año'!$X$19</definedName>
+    <definedName name="grade_12_4" localSheetId="3">'5to Año'!$Y$19</definedName>
+    <definedName name="std_part_4" localSheetId="3">'5to Año'!$Z$19</definedName>
+    <definedName name="std_num_5" localSheetId="3">'5to Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="3">'5to Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="3">'5to Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="3">'5to Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="3">'5to Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="3">'5to Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="3">'5to Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="3">'5to Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="3">'5to Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="3">'5to Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="3">'5to Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="3">'5to Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="3">'5to Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="3">'5to Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="3">'5to Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="3">'5to Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="3">'5to Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="3">'5to Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="3">'5to Año'!$V$20</definedName>
+    <definedName name="grade_10_5" localSheetId="3">'5to Año'!$W$20</definedName>
+    <definedName name="grade_11_5" localSheetId="3">'5to Año'!$X$20</definedName>
+    <definedName name="grade_12_5" localSheetId="3">'5to Año'!$Y$20</definedName>
+    <definedName name="std_part_5" localSheetId="3">'5to Año'!$Z$20</definedName>
+    <definedName name="std_num_6" localSheetId="3">'5to Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="3">'5to Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="3">'5to Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="3">'5to Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="3">'5to Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="3">'5to Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="3">'5to Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="3">'5to Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="3">'5to Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="3">'5to Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="3">'5to Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="3">'5to Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="3">'5to Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="3">'5to Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="3">'5to Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="3">'5to Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="3">'5to Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="3">'5to Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="3">'5to Año'!$V$21</definedName>
+    <definedName name="grade_10_6" localSheetId="3">'5to Año'!$W$21</definedName>
+    <definedName name="grade_11_6" localSheetId="3">'5to Año'!$X$21</definedName>
+    <definedName name="grade_12_6" localSheetId="3">'5to Año'!$Y$21</definedName>
+    <definedName name="std_part_6" localSheetId="3">'5to Año'!$Z$21</definedName>
+    <definedName name="std_num_7" localSheetId="3">'5to Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="3">'5to Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="3">'5to Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="3">'5to Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="3">'5to Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="3">'5to Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="3">'5to Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="3">'5to Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="3">'5to Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="3">'5to Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="3">'5to Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="3">'5to Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="3">'5to Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="3">'5to Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="3">'5to Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="3">'5to Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="3">'5to Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="3">'5to Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="3">'5to Año'!$V$22</definedName>
+    <definedName name="grade_10_7" localSheetId="3">'5to Año'!$W$22</definedName>
+    <definedName name="grade_11_7" localSheetId="3">'5to Año'!$X$22</definedName>
+    <definedName name="grade_12_7" localSheetId="3">'5to Año'!$Y$22</definedName>
+    <definedName name="std_part_7" localSheetId="3">'5to Año'!$Z$22</definedName>
+    <definedName name="std_num_8" localSheetId="3">'5to Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="3">'5to Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="3">'5to Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="3">'5to Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="3">'5to Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="3">'5to Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="3">'5to Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="3">'5to Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="3">'5to Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="3">'5to Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="3">'5to Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="3">'5to Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="3">'5to Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="3">'5to Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="3">'5to Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="3">'5to Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="3">'5to Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="3">'5to Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="3">'5to Año'!$V$23</definedName>
+    <definedName name="grade_10_8" localSheetId="3">'5to Año'!$W$23</definedName>
+    <definedName name="grade_11_8" localSheetId="3">'5to Año'!$X$23</definedName>
+    <definedName name="grade_12_8" localSheetId="3">'5to Año'!$Y$23</definedName>
+    <definedName name="std_part_8" localSheetId="3">'5to Año'!$Z$23</definedName>
+    <definedName name="std_num_9" localSheetId="3">'5to Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="3">'5to Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="3">'5to Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="3">'5to Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="3">'5to Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="3">'5to Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="3">'5to Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="3">'5to Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="3">'5to Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="3">'5to Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="3">'5to Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="3">'5to Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="3">'5to Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="3">'5to Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="3">'5to Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="3">'5to Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="3">'5to Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="3">'5to Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="3">'5to Año'!$V$24</definedName>
+    <definedName name="grade_10_9" localSheetId="3">'5to Año'!$W$24</definedName>
+    <definedName name="grade_11_9" localSheetId="3">'5to Año'!$X$24</definedName>
+    <definedName name="grade_12_9" localSheetId="3">'5to Año'!$Y$24</definedName>
+    <definedName name="std_part_9" localSheetId="3">'5to Año'!$Z$24</definedName>
+    <definedName name="std_num_10" localSheetId="3">'5to Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="3">'5to Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="3">'5to Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="3">'5to Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="3">'5to Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="3">'5to Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="3">'5to Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="3">'5to Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="3">'5to Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="3">'5to Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="3">'5to Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="3">'5to Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="3">'5to Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="3">'5to Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="3">'5to Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="3">'5to Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="3">'5to Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="3">'5to Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="3">'5to Año'!$V$25</definedName>
+    <definedName name="grade_10_10" localSheetId="3">'5to Año'!$W$25</definedName>
+    <definedName name="grade_11_10" localSheetId="3">'5to Año'!$X$25</definedName>
+    <definedName name="grade_12_10" localSheetId="3">'5to Año'!$Y$25</definedName>
+    <definedName name="std_part_10" localSheetId="3">'5to Año'!$Z$25</definedName>
+    <definedName name="std_num_11" localSheetId="3">'5to Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="3">'5to Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="3">'5to Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="3">'5to Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="3">'5to Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="3">'5to Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="3">'5to Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="3">'5to Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="3">'5to Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="3">'5to Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="3">'5to Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="3">'5to Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="3">'5to Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="3">'5to Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="3">'5to Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="3">'5to Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="3">'5to Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="3">'5to Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="3">'5to Año'!$V$26</definedName>
+    <definedName name="grade_10_11" localSheetId="3">'5to Año'!$W$26</definedName>
+    <definedName name="grade_11_11" localSheetId="3">'5to Año'!$X$26</definedName>
+    <definedName name="grade_12_11" localSheetId="3">'5to Año'!$Y$26</definedName>
+    <definedName name="std_part_11" localSheetId="3">'5to Año'!$Z$26</definedName>
+    <definedName name="std_num_12" localSheetId="3">'5to Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="3">'5to Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="3">'5to Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="3">'5to Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="3">'5to Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="3">'5to Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="3">'5to Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="3">'5to Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="3">'5to Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="3">'5to Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="3">'5to Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="3">'5to Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="3">'5to Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="3">'5to Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="3">'5to Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="3">'5to Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="3">'5to Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="3">'5to Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="3">'5to Año'!$V$27</definedName>
+    <definedName name="grade_10_12" localSheetId="3">'5to Año'!$W$27</definedName>
+    <definedName name="grade_11_12" localSheetId="3">'5to Año'!$X$27</definedName>
+    <definedName name="grade_12_12" localSheetId="3">'5to Año'!$Y$27</definedName>
+    <definedName name="std_part_12" localSheetId="3">'5to Año'!$Z$27</definedName>
+    <definedName name="std_num_13" localSheetId="3">'5to Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="3">'5to Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="3">'5to Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="3">'5to Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="3">'5to Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="3">'5to Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="3">'5to Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="3">'5to Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="3">'5to Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="3">'5to Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="3">'5to Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="3">'5to Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="3">'5to Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="3">'5to Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="3">'5to Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="3">'5to Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="3">'5to Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="3">'5to Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="3">'5to Año'!$V$28</definedName>
+    <definedName name="grade_10_13" localSheetId="3">'5to Año'!$W$28</definedName>
+    <definedName name="grade_11_13" localSheetId="3">'5to Año'!$X$28</definedName>
+    <definedName name="grade_12_13" localSheetId="3">'5to Año'!$Y$28</definedName>
+    <definedName name="std_part_13" localSheetId="3">'5to Año'!$Z$28</definedName>
+    <definedName name="std_num_14" localSheetId="3">'5to Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="3">'5to Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="3">'5to Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="3">'5to Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="3">'5to Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="3">'5to Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="3">'5to Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="3">'5to Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="3">'5to Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="3">'5to Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="3">'5to Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="3">'5to Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="3">'5to Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="3">'5to Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="3">'5to Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="3">'5to Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="3">'5to Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="3">'5to Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="3">'5to Año'!$V$29</definedName>
+    <definedName name="grade_10_14" localSheetId="3">'5to Año'!$W$29</definedName>
+    <definedName name="grade_11_14" localSheetId="3">'5to Año'!$X$29</definedName>
+    <definedName name="grade_12_14" localSheetId="3">'5to Año'!$Y$29</definedName>
+    <definedName name="std_part_14" localSheetId="3">'5to Año'!$Z$29</definedName>
+    <definedName name="std_num_15" localSheetId="3">'5to Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="3">'5to Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="3">'5to Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="3">'5to Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="3">'5to Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="3">'5to Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="3">'5to Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="3">'5to Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="3">'5to Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="3">'5to Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="3">'5to Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="3">'5to Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="3">'5to Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="3">'5to Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="3">'5to Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="3">'5to Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="3">'5to Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="3">'5to Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="3">'5to Año'!$V$30</definedName>
+    <definedName name="grade_10_15" localSheetId="3">'5to Año'!$W$30</definedName>
+    <definedName name="grade_11_15" localSheetId="3">'5to Año'!$X$30</definedName>
+    <definedName name="grade_12_15" localSheetId="3">'5to Año'!$Y$30</definedName>
+    <definedName name="std_part_15" localSheetId="3">'5to Año'!$Z$30</definedName>
+    <definedName name="std_num_16" localSheetId="3">'5to Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="3">'5to Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="3">'5to Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="3">'5to Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="3">'5to Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="3">'5to Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="3">'5to Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="3">'5to Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="3">'5to Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="3">'5to Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="3">'5to Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="3">'5to Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="3">'5to Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="3">'5to Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="3">'5to Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="3">'5to Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="3">'5to Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="3">'5to Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="3">'5to Año'!$V$31</definedName>
+    <definedName name="grade_10_16" localSheetId="3">'5to Año'!$W$31</definedName>
+    <definedName name="grade_11_16" localSheetId="3">'5to Año'!$X$31</definedName>
+    <definedName name="grade_12_16" localSheetId="3">'5to Año'!$Y$31</definedName>
+    <definedName name="std_part_16" localSheetId="3">'5to Año'!$Z$31</definedName>
+    <definedName name="std_num_17" localSheetId="3">'5to Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="3">'5to Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="3">'5to Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="3">'5to Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="3">'5to Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="3">'5to Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="3">'5to Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="3">'5to Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="3">'5to Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="3">'5to Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="3">'5to Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="3">'5to Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="3">'5to Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="3">'5to Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="3">'5to Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="3">'5to Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="3">'5to Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="3">'5to Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="3">'5to Año'!$V$32</definedName>
+    <definedName name="grade_10_17" localSheetId="3">'5to Año'!$W$32</definedName>
+    <definedName name="grade_11_17" localSheetId="3">'5to Año'!$X$32</definedName>
+    <definedName name="grade_12_17" localSheetId="3">'5to Año'!$Y$32</definedName>
+    <definedName name="std_part_17" localSheetId="3">'5to Año'!$Z$32</definedName>
+    <definedName name="std_num_18" localSheetId="3">'5to Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="3">'5to Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="3">'5to Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="3">'5to Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="3">'5to Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="3">'5to Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="3">'5to Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="3">'5to Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="3">'5to Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="3">'5to Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="3">'5to Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="3">'5to Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="3">'5to Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="3">'5to Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="3">'5to Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="3">'5to Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="3">'5to Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="3">'5to Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="3">'5to Año'!$V$33</definedName>
+    <definedName name="grade_10_18" localSheetId="3">'5to Año'!$W$33</definedName>
+    <definedName name="grade_11_18" localSheetId="3">'5to Año'!$X$33</definedName>
+    <definedName name="grade_12_18" localSheetId="3">'5to Año'!$Y$33</definedName>
+    <definedName name="std_part_18" localSheetId="3">'5to Año'!$Z$33</definedName>
+    <definedName name="std_num_19" localSheetId="3">'5to Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="3">'5to Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="3">'5to Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="3">'5to Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="3">'5to Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="3">'5to Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="3">'5to Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="3">'5to Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="3">'5to Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="3">'5to Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="3">'5to Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="3">'5to Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="3">'5to Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="3">'5to Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="3">'5to Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="3">'5to Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="3">'5to Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="3">'5to Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="3">'5to Año'!$V$34</definedName>
+    <definedName name="grade_10_19" localSheetId="3">'5to Año'!$W$34</definedName>
+    <definedName name="grade_11_19" localSheetId="3">'5to Año'!$X$34</definedName>
+    <definedName name="grade_12_19" localSheetId="3">'5to Año'!$Y$34</definedName>
+    <definedName name="std_part_19" localSheetId="3">'5to Año'!$Z$34</definedName>
+    <definedName name="std_num_20" localSheetId="3">'5to Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="3">'5to Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="3">'5to Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="3">'5to Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="3">'5to Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="3">'5to Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="3">'5to Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="3">'5to Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="3">'5to Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="3">'5to Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="3">'5to Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="3">'5to Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="3">'5to Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="3">'5to Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="3">'5to Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="3">'5to Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="3">'5to Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="3">'5to Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="3">'5to Año'!$V$35</definedName>
+    <definedName name="grade_10_20" localSheetId="3">'5to Año'!$W$35</definedName>
+    <definedName name="grade_11_20" localSheetId="3">'5to Año'!$X$35</definedName>
+    <definedName name="grade_12_20" localSheetId="3">'5to Año'!$Y$35</definedName>
+    <definedName name="std_part_20" localSheetId="3">'5to Año'!$Z$35</definedName>
+    <definedName name="std_num_21" localSheetId="3">'5to Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="3">'5to Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="3">'5to Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="3">'5to Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="3">'5to Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="3">'5to Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="3">'5to Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="3">'5to Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="3">'5to Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="3">'5to Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="3">'5to Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="3">'5to Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="3">'5to Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="3">'5to Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="3">'5to Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="3">'5to Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="3">'5to Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="3">'5to Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="3">'5to Año'!$V$36</definedName>
+    <definedName name="grade_10_21" localSheetId="3">'5to Año'!$W$36</definedName>
+    <definedName name="grade_11_21" localSheetId="3">'5to Año'!$X$36</definedName>
+    <definedName name="grade_12_21" localSheetId="3">'5to Año'!$Y$36</definedName>
+    <definedName name="std_part_21" localSheetId="3">'5to Año'!$Z$36</definedName>
+    <definedName name="std_num_22" localSheetId="3">'5to Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="3">'5to Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="3">'5to Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="3">'5to Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="3">'5to Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="3">'5to Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="3">'5to Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="3">'5to Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="3">'5to Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="3">'5to Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="3">'5to Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="3">'5to Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="3">'5to Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="3">'5to Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="3">'5to Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="3">'5to Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="3">'5to Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="3">'5to Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="3">'5to Año'!$V$37</definedName>
+    <definedName name="grade_10_22" localSheetId="3">'5to Año'!$W$37</definedName>
+    <definedName name="grade_11_22" localSheetId="3">'5to Año'!$X$37</definedName>
+    <definedName name="grade_12_22" localSheetId="3">'5to Año'!$Y$37</definedName>
+    <definedName name="std_part_22" localSheetId="3">'5to Año'!$Z$37</definedName>
+    <definedName name="std_num_23" localSheetId="3">'5to Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="3">'5to Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="3">'5to Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="3">'5to Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="3">'5to Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="3">'5to Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="3">'5to Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="3">'5to Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="3">'5to Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="3">'5to Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="3">'5to Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="3">'5to Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="3">'5to Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="3">'5to Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="3">'5to Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="3">'5to Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="3">'5to Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="3">'5to Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="3">'5to Año'!$V$38</definedName>
+    <definedName name="grade_10_23" localSheetId="3">'5to Año'!$W$38</definedName>
+    <definedName name="grade_11_23" localSheetId="3">'5to Año'!$X$38</definedName>
+    <definedName name="grade_12_23" localSheetId="3">'5to Año'!$Y$38</definedName>
+    <definedName name="std_part_23" localSheetId="3">'5to Año'!$Z$38</definedName>
+    <definedName name="std_num_24" localSheetId="3">'5to Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="3">'5to Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="3">'5to Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="3">'5to Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="3">'5to Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="3">'5to Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="3">'5to Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="3">'5to Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="3">'5to Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="3">'5to Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="3">'5to Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="3">'5to Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="3">'5to Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="3">'5to Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="3">'5to Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="3">'5to Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="3">'5to Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="3">'5to Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="3">'5to Año'!$V$39</definedName>
+    <definedName name="grade_10_24" localSheetId="3">'5to Año'!$W$39</definedName>
+    <definedName name="grade_11_24" localSheetId="3">'5to Año'!$X$39</definedName>
+    <definedName name="grade_12_24" localSheetId="3">'5to Año'!$Y$39</definedName>
+    <definedName name="std_part_24" localSheetId="3">'5to Año'!$Z$39</definedName>
+    <definedName name="std_num_25" localSheetId="3">'5to Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="3">'5to Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="3">'5to Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="3">'5to Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="3">'5to Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="3">'5to Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="3">'5to Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="3">'5to Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="3">'5to Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="3">'5to Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="3">'5to Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="3">'5to Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="3">'5to Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="3">'5to Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="3">'5to Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="3">'5to Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="3">'5to Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="3">'5to Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="3">'5to Año'!$V$40</definedName>
+    <definedName name="grade_10_25" localSheetId="3">'5to Año'!$W$40</definedName>
+    <definedName name="grade_11_25" localSheetId="3">'5to Año'!$X$40</definedName>
+    <definedName name="grade_12_25" localSheetId="3">'5to Año'!$Y$40</definedName>
+    <definedName name="std_part_25" localSheetId="3">'5to Año'!$Z$40</definedName>
+    <definedName name="std_num_26" localSheetId="3">'5to Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="3">'5to Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="3">'5to Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="3">'5to Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="3">'5to Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="3">'5to Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="3">'5to Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="3">'5to Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="3">'5to Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="3">'5to Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="3">'5to Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="3">'5to Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="3">'5to Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="3">'5to Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="3">'5to Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="3">'5to Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="3">'5to Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="3">'5to Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="3">'5to Año'!$V$41</definedName>
+    <definedName name="grade_10_26" localSheetId="3">'5to Año'!$W$41</definedName>
+    <definedName name="grade_11_26" localSheetId="3">'5to Año'!$X$41</definedName>
+    <definedName name="grade_12_26" localSheetId="3">'5to Año'!$Y$41</definedName>
+    <definedName name="std_part_26" localSheetId="3">'5to Año'!$Z$41</definedName>
+    <definedName name="std_num_27" localSheetId="3">'5to Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="3">'5to Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="3">'5to Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="3">'5to Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="3">'5to Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="3">'5to Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="3">'5to Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="3">'5to Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="3">'5to Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="3">'5to Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="3">'5to Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="3">'5to Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="3">'5to Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="3">'5to Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="3">'5to Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="3">'5to Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="3">'5to Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="3">'5to Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="3">'5to Año'!$V$42</definedName>
+    <definedName name="grade_10_27" localSheetId="3">'5to Año'!$W$42</definedName>
+    <definedName name="grade_11_27" localSheetId="3">'5to Año'!$X$42</definedName>
+    <definedName name="grade_12_27" localSheetId="3">'5to Año'!$Y$42</definedName>
+    <definedName name="std_part_27" localSheetId="3">'5to Año'!$Z$42</definedName>
+    <definedName name="std_num_28" localSheetId="3">'5to Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="3">'5to Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="3">'5to Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="3">'5to Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="3">'5to Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="3">'5to Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="3">'5to Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="3">'5to Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="3">'5to Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="3">'5to Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="3">'5to Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="3">'5to Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="3">'5to Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="3">'5to Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="3">'5to Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="3">'5to Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="3">'5to Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="3">'5to Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="3">'5to Año'!$V$43</definedName>
+    <definedName name="grade_10_28" localSheetId="3">'5to Año'!$W$43</definedName>
+    <definedName name="grade_11_28" localSheetId="3">'5to Año'!$X$43</definedName>
+    <definedName name="grade_12_28" localSheetId="3">'5to Año'!$Y$43</definedName>
+    <definedName name="std_part_28" localSheetId="3">'5to Año'!$Z$43</definedName>
+    <definedName name="std_num_29" localSheetId="3">'5to Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="3">'5to Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="3">'5to Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="3">'5to Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="3">'5to Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="3">'5to Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="3">'5to Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="3">'5to Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="3">'5to Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="3">'5to Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="3">'5to Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="3">'5to Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="3">'5to Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="3">'5to Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="3">'5to Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="3">'5to Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="3">'5to Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="3">'5to Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="3">'5to Año'!$V$44</definedName>
+    <definedName name="grade_10_29" localSheetId="3">'5to Año'!$W$44</definedName>
+    <definedName name="grade_11_29" localSheetId="3">'5to Año'!$X$44</definedName>
+    <definedName name="grade_12_29" localSheetId="3">'5to Año'!$Y$44</definedName>
+    <definedName name="std_part_29" localSheetId="3">'5to Año'!$Z$44</definedName>
+    <definedName name="std_num_30" localSheetId="3">'5to Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="3">'5to Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="3">'5to Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="3">'5to Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="3">'5to Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="3">'5to Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="3">'5to Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="3">'5to Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="3">'5to Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="3">'5to Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="3">'5to Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="3">'5to Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="3">'5to Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="3">'5to Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="3">'5to Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="3">'5to Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="3">'5to Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="3">'5to Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="3">'5to Año'!$V$45</definedName>
+    <definedName name="grade_10_30" localSheetId="3">'5to Año'!$W$45</definedName>
+    <definedName name="grade_11_30" localSheetId="3">'5to Año'!$X$45</definedName>
+    <definedName name="grade_12_30" localSheetId="3">'5to Año'!$Y$45</definedName>
+    <definedName name="std_part_30" localSheetId="3">'5to Año'!$Z$45</definedName>
+    <definedName name="std_num_31" localSheetId="3">'5to Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="3">'5to Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="3">'5to Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="3">'5to Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="3">'5to Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="3">'5to Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="3">'5to Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="3">'5to Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="3">'5to Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="3">'5to Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="3">'5to Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="3">'5to Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="3">'5to Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="3">'5to Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="3">'5to Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="3">'5to Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="3">'5to Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="3">'5to Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="3">'5to Año'!$V$46</definedName>
+    <definedName name="grade_10_31" localSheetId="3">'5to Año'!$W$46</definedName>
+    <definedName name="grade_11_31" localSheetId="3">'5to Año'!$X$46</definedName>
+    <definedName name="grade_12_31" localSheetId="3">'5to Año'!$Y$46</definedName>
+    <definedName name="std_part_31" localSheetId="3">'5to Año'!$Z$46</definedName>
+    <definedName name="std_num_32" localSheetId="3">'5to Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="3">'5to Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="3">'5to Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="3">'5to Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="3">'5to Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="3">'5to Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="3">'5to Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="3">'5to Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="3">'5to Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="3">'5to Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="3">'5to Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="3">'5to Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="3">'5to Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="3">'5to Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="3">'5to Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="3">'5to Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="3">'5to Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="3">'5to Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="3">'5to Año'!$V$47</definedName>
+    <definedName name="grade_10_32" localSheetId="3">'5to Año'!$W$47</definedName>
+    <definedName name="grade_11_32" localSheetId="3">'5to Año'!$X$47</definedName>
+    <definedName name="grade_12_32" localSheetId="3">'5to Año'!$Y$47</definedName>
+    <definedName name="std_part_32" localSheetId="3">'5to Año'!$Z$47</definedName>
+    <definedName name="std_num_33" localSheetId="3">'5to Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="3">'5to Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="3">'5to Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="3">'5to Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="3">'5to Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="3">'5to Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="3">'5to Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="3">'5to Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="3">'5to Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="3">'5to Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="3">'5to Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="3">'5to Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="3">'5to Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="3">'5to Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="3">'5to Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="3">'5to Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="3">'5to Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="3">'5to Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="3">'5to Año'!$V$48</definedName>
+    <definedName name="grade_10_33" localSheetId="3">'5to Año'!$W$48</definedName>
+    <definedName name="grade_11_33" localSheetId="3">'5to Año'!$X$48</definedName>
+    <definedName name="grade_12_33" localSheetId="3">'5to Año'!$Y$48</definedName>
+    <definedName name="std_part_33" localSheetId="3">'5to Año'!$Z$48</definedName>
+    <definedName name="std_num_34" localSheetId="3">'5to Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="3">'5to Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="3">'5to Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="3">'5to Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="3">'5to Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="3">'5to Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="3">'5to Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="3">'5to Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="3">'5to Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="3">'5to Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="3">'5to Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="3">'5to Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="3">'5to Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="3">'5to Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="3">'5to Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="3">'5to Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="3">'5to Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="3">'5to Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="3">'5to Año'!$V$49</definedName>
+    <definedName name="grade_10_34" localSheetId="3">'5to Año'!$W$49</definedName>
+    <definedName name="grade_11_34" localSheetId="3">'5to Año'!$X$49</definedName>
+    <definedName name="grade_12_34" localSheetId="3">'5to Año'!$Y$49</definedName>
+    <definedName name="std_part_34" localSheetId="3">'5to Año'!$Z$49</definedName>
+    <definedName name="std_num_35" localSheetId="3">'5to Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="3">'5to Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="3">'5to Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="3">'5to Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="3">'5to Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="3">'5to Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="3">'5to Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="3">'5to Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="3">'5to Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="3">'5to Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="3">'5to Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="3">'5to Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="3">'5to Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="3">'5to Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="3">'5to Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="3">'5to Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="3">'5to Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="3">'5to Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="3">'5to Año'!$V$50</definedName>
+    <definedName name="grade_10_35" localSheetId="3">'5to Año'!$W$50</definedName>
+    <definedName name="grade_11_35" localSheetId="3">'5to Año'!$X$50</definedName>
+    <definedName name="grade_12_35" localSheetId="3">'5to Año'!$Y$50</definedName>
+    <definedName name="std_part_35" localSheetId="3">'5to Año'!$Z$50</definedName>
+  </definedNames>
+  <definedNames>
+    <definedName name="inst_period" localSheetId="0">'1er Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="0">'1er Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="0">'1er Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="0">'1er Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="0">'1er Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="0">'1er Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="0">'1er Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="0">'1er Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="0">'1er Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="0">'1er Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="0">'1er Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="0">'1er Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="0">'1er Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="0">'1er Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="0">'1er Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="0">'1er Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="0">'1er Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="0">'1er Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="0">'1er Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="0">'1er Año'!$V$15</definedName>
+    <definedName name="std_num_1" localSheetId="0">'1er Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="0">'1er Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="0">'1er Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="0">'1er Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="0">'1er Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="0">'1er Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="0">'1er Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="0">'1er Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="0">'1er Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="0">'1er Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="0">'1er Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="0">'1er Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="0">'1er Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="0">'1er Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="0">'1er Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="0">'1er Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="0">'1er Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="0">'1er Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="0">'1er Año'!$V$16</definedName>
+    <definedName name="std_part_1" localSheetId="0">'1er Año'!$W$16</definedName>
+    <definedName name="std_num_2" localSheetId="0">'1er Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="0">'1er Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="0">'1er Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="0">'1er Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="0">'1er Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="0">'1er Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="0">'1er Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="0">'1er Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="0">'1er Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="0">'1er Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="0">'1er Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="0">'1er Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="0">'1er Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="0">'1er Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="0">'1er Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="0">'1er Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="0">'1er Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="0">'1er Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="0">'1er Año'!$V$17</definedName>
+    <definedName name="std_part_2" localSheetId="0">'1er Año'!$W$17</definedName>
+    <definedName name="std_num_3" localSheetId="0">'1er Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="0">'1er Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="0">'1er Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="0">'1er Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="0">'1er Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="0">'1er Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="0">'1er Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="0">'1er Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="0">'1er Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="0">'1er Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="0">'1er Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="0">'1er Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="0">'1er Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="0">'1er Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="0">'1er Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="0">'1er Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="0">'1er Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="0">'1er Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="0">'1er Año'!$V$18</definedName>
+    <definedName name="std_part_3" localSheetId="0">'1er Año'!$W$18</definedName>
+    <definedName name="std_num_4" localSheetId="0">'1er Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="0">'1er Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="0">'1er Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="0">'1er Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="0">'1er Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="0">'1er Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="0">'1er Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="0">'1er Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="0">'1er Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="0">'1er Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="0">'1er Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="0">'1er Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="0">'1er Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="0">'1er Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="0">'1er Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="0">'1er Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="0">'1er Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="0">'1er Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="0">'1er Año'!$V$19</definedName>
+    <definedName name="std_part_4" localSheetId="0">'1er Año'!$W$19</definedName>
+    <definedName name="std_num_5" localSheetId="0">'1er Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="0">'1er Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="0">'1er Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="0">'1er Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="0">'1er Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="0">'1er Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="0">'1er Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="0">'1er Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="0">'1er Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="0">'1er Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="0">'1er Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="0">'1er Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="0">'1er Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="0">'1er Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="0">'1er Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="0">'1er Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="0">'1er Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="0">'1er Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="0">'1er Año'!$V$20</definedName>
+    <definedName name="std_part_5" localSheetId="0">'1er Año'!$W$20</definedName>
+    <definedName name="std_num_6" localSheetId="0">'1er Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="0">'1er Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="0">'1er Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="0">'1er Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="0">'1er Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="0">'1er Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="0">'1er Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="0">'1er Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="0">'1er Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="0">'1er Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="0">'1er Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="0">'1er Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="0">'1er Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="0">'1er Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="0">'1er Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="0">'1er Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="0">'1er Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="0">'1er Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="0">'1er Año'!$V$21</definedName>
+    <definedName name="std_part_6" localSheetId="0">'1er Año'!$W$21</definedName>
+    <definedName name="std_num_7" localSheetId="0">'1er Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="0">'1er Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="0">'1er Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="0">'1er Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="0">'1er Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="0">'1er Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="0">'1er Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="0">'1er Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="0">'1er Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="0">'1er Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="0">'1er Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="0">'1er Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="0">'1er Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="0">'1er Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="0">'1er Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="0">'1er Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="0">'1er Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="0">'1er Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="0">'1er Año'!$V$22</definedName>
+    <definedName name="std_part_7" localSheetId="0">'1er Año'!$W$22</definedName>
+    <definedName name="std_num_8" localSheetId="0">'1er Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="0">'1er Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="0">'1er Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="0">'1er Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="0">'1er Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="0">'1er Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="0">'1er Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="0">'1er Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="0">'1er Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="0">'1er Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="0">'1er Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="0">'1er Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="0">'1er Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="0">'1er Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="0">'1er Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="0">'1er Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="0">'1er Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="0">'1er Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="0">'1er Año'!$V$23</definedName>
+    <definedName name="std_part_8" localSheetId="0">'1er Año'!$W$23</definedName>
+    <definedName name="std_num_9" localSheetId="0">'1er Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="0">'1er Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="0">'1er Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="0">'1er Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="0">'1er Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="0">'1er Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="0">'1er Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="0">'1er Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="0">'1er Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="0">'1er Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="0">'1er Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="0">'1er Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="0">'1er Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="0">'1er Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="0">'1er Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="0">'1er Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="0">'1er Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="0">'1er Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="0">'1er Año'!$V$24</definedName>
+    <definedName name="std_part_9" localSheetId="0">'1er Año'!$W$24</definedName>
+    <definedName name="std_num_10" localSheetId="0">'1er Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="0">'1er Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="0">'1er Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="0">'1er Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="0">'1er Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="0">'1er Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="0">'1er Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="0">'1er Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="0">'1er Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="0">'1er Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="0">'1er Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="0">'1er Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="0">'1er Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="0">'1er Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="0">'1er Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="0">'1er Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="0">'1er Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="0">'1er Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="0">'1er Año'!$V$25</definedName>
+    <definedName name="std_part_10" localSheetId="0">'1er Año'!$W$25</definedName>
+    <definedName name="std_num_11" localSheetId="0">'1er Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="0">'1er Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="0">'1er Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="0">'1er Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="0">'1er Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="0">'1er Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="0">'1er Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="0">'1er Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="0">'1er Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="0">'1er Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="0">'1er Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="0">'1er Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="0">'1er Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="0">'1er Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="0">'1er Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="0">'1er Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="0">'1er Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="0">'1er Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="0">'1er Año'!$V$26</definedName>
+    <definedName name="std_part_11" localSheetId="0">'1er Año'!$W$26</definedName>
+    <definedName name="std_num_12" localSheetId="0">'1er Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="0">'1er Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="0">'1er Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="0">'1er Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="0">'1er Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="0">'1er Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="0">'1er Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="0">'1er Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="0">'1er Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="0">'1er Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="0">'1er Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="0">'1er Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="0">'1er Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="0">'1er Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="0">'1er Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="0">'1er Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="0">'1er Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="0">'1er Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="0">'1er Año'!$V$27</definedName>
+    <definedName name="std_part_12" localSheetId="0">'1er Año'!$W$27</definedName>
+    <definedName name="std_num_13" localSheetId="0">'1er Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="0">'1er Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="0">'1er Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="0">'1er Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="0">'1er Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="0">'1er Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="0">'1er Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="0">'1er Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="0">'1er Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="0">'1er Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="0">'1er Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="0">'1er Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="0">'1er Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="0">'1er Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="0">'1er Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="0">'1er Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="0">'1er Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="0">'1er Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="0">'1er Año'!$V$28</definedName>
+    <definedName name="std_part_13" localSheetId="0">'1er Año'!$W$28</definedName>
+    <definedName name="std_num_14" localSheetId="0">'1er Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="0">'1er Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="0">'1er Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="0">'1er Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="0">'1er Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="0">'1er Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="0">'1er Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="0">'1er Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="0">'1er Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="0">'1er Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="0">'1er Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="0">'1er Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="0">'1er Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="0">'1er Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="0">'1er Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="0">'1er Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="0">'1er Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="0">'1er Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="0">'1er Año'!$V$29</definedName>
+    <definedName name="std_part_14" localSheetId="0">'1er Año'!$W$29</definedName>
+    <definedName name="std_num_15" localSheetId="0">'1er Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="0">'1er Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="0">'1er Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="0">'1er Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="0">'1er Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="0">'1er Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="0">'1er Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="0">'1er Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="0">'1er Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="0">'1er Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="0">'1er Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="0">'1er Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="0">'1er Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="0">'1er Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="0">'1er Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="0">'1er Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="0">'1er Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="0">'1er Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="0">'1er Año'!$V$30</definedName>
+    <definedName name="std_part_15" localSheetId="0">'1er Año'!$W$30</definedName>
+    <definedName name="std_num_16" localSheetId="0">'1er Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="0">'1er Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="0">'1er Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="0">'1er Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="0">'1er Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="0">'1er Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="0">'1er Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="0">'1er Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="0">'1er Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="0">'1er Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="0">'1er Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="0">'1er Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="0">'1er Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="0">'1er Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="0">'1er Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="0">'1er Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="0">'1er Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="0">'1er Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="0">'1er Año'!$V$31</definedName>
+    <definedName name="std_part_16" localSheetId="0">'1er Año'!$W$31</definedName>
+    <definedName name="std_num_17" localSheetId="0">'1er Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="0">'1er Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="0">'1er Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="0">'1er Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="0">'1er Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="0">'1er Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="0">'1er Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="0">'1er Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="0">'1er Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="0">'1er Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="0">'1er Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="0">'1er Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="0">'1er Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="0">'1er Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="0">'1er Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="0">'1er Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="0">'1er Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="0">'1er Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="0">'1er Año'!$V$32</definedName>
+    <definedName name="std_part_17" localSheetId="0">'1er Año'!$W$32</definedName>
+    <definedName name="std_num_18" localSheetId="0">'1er Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="0">'1er Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="0">'1er Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="0">'1er Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="0">'1er Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="0">'1er Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="0">'1er Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="0">'1er Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="0">'1er Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="0">'1er Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="0">'1er Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="0">'1er Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="0">'1er Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="0">'1er Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="0">'1er Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="0">'1er Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="0">'1er Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="0">'1er Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="0">'1er Año'!$V$33</definedName>
+    <definedName name="std_part_18" localSheetId="0">'1er Año'!$W$33</definedName>
+    <definedName name="std_num_19" localSheetId="0">'1er Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="0">'1er Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="0">'1er Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="0">'1er Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="0">'1er Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="0">'1er Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="0">'1er Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="0">'1er Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="0">'1er Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="0">'1er Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="0">'1er Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="0">'1er Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="0">'1er Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="0">'1er Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="0">'1er Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="0">'1er Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="0">'1er Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="0">'1er Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="0">'1er Año'!$V$34</definedName>
+    <definedName name="std_part_19" localSheetId="0">'1er Año'!$W$34</definedName>
+    <definedName name="std_num_20" localSheetId="0">'1er Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="0">'1er Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="0">'1er Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="0">'1er Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="0">'1er Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="0">'1er Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="0">'1er Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="0">'1er Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="0">'1er Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="0">'1er Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="0">'1er Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="0">'1er Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="0">'1er Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="0">'1er Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="0">'1er Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="0">'1er Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="0">'1er Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="0">'1er Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="0">'1er Año'!$V$35</definedName>
+    <definedName name="std_part_20" localSheetId="0">'1er Año'!$W$35</definedName>
+    <definedName name="std_num_21" localSheetId="0">'1er Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="0">'1er Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="0">'1er Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="0">'1er Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="0">'1er Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="0">'1er Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="0">'1er Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="0">'1er Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="0">'1er Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="0">'1er Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="0">'1er Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="0">'1er Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="0">'1er Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="0">'1er Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="0">'1er Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="0">'1er Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="0">'1er Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="0">'1er Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="0">'1er Año'!$V$36</definedName>
+    <definedName name="std_part_21" localSheetId="0">'1er Año'!$W$36</definedName>
+    <definedName name="std_num_22" localSheetId="0">'1er Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="0">'1er Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="0">'1er Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="0">'1er Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="0">'1er Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="0">'1er Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="0">'1er Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="0">'1er Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="0">'1er Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="0">'1er Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="0">'1er Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="0">'1er Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="0">'1er Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="0">'1er Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="0">'1er Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="0">'1er Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="0">'1er Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="0">'1er Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="0">'1er Año'!$V$37</definedName>
+    <definedName name="std_part_22" localSheetId="0">'1er Año'!$W$37</definedName>
+    <definedName name="std_num_23" localSheetId="0">'1er Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="0">'1er Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="0">'1er Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="0">'1er Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="0">'1er Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="0">'1er Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="0">'1er Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="0">'1er Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="0">'1er Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="0">'1er Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="0">'1er Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="0">'1er Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="0">'1er Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="0">'1er Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="0">'1er Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="0">'1er Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="0">'1er Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="0">'1er Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="0">'1er Año'!$V$38</definedName>
+    <definedName name="std_part_23" localSheetId="0">'1er Año'!$W$38</definedName>
+    <definedName name="std_num_24" localSheetId="0">'1er Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="0">'1er Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="0">'1er Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="0">'1er Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="0">'1er Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="0">'1er Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="0">'1er Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="0">'1er Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="0">'1er Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="0">'1er Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="0">'1er Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="0">'1er Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="0">'1er Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="0">'1er Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="0">'1er Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="0">'1er Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="0">'1er Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="0">'1er Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="0">'1er Año'!$V$39</definedName>
+    <definedName name="std_part_24" localSheetId="0">'1er Año'!$W$39</definedName>
+    <definedName name="std_num_25" localSheetId="0">'1er Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="0">'1er Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="0">'1er Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="0">'1er Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="0">'1er Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="0">'1er Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="0">'1er Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="0">'1er Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="0">'1er Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="0">'1er Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="0">'1er Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="0">'1er Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="0">'1er Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="0">'1er Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="0">'1er Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="0">'1er Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="0">'1er Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="0">'1er Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="0">'1er Año'!$V$40</definedName>
+    <definedName name="std_part_25" localSheetId="0">'1er Año'!$W$40</definedName>
+    <definedName name="std_num_26" localSheetId="0">'1er Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="0">'1er Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="0">'1er Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="0">'1er Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="0">'1er Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="0">'1er Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="0">'1er Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="0">'1er Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="0">'1er Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="0">'1er Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="0">'1er Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="0">'1er Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="0">'1er Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="0">'1er Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="0">'1er Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="0">'1er Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="0">'1er Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="0">'1er Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="0">'1er Año'!$V$41</definedName>
+    <definedName name="std_part_26" localSheetId="0">'1er Año'!$W$41</definedName>
+    <definedName name="std_num_27" localSheetId="0">'1er Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="0">'1er Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="0">'1er Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="0">'1er Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="0">'1er Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="0">'1er Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="0">'1er Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="0">'1er Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="0">'1er Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="0">'1er Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="0">'1er Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="0">'1er Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="0">'1er Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="0">'1er Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="0">'1er Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="0">'1er Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="0">'1er Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="0">'1er Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="0">'1er Año'!$V$42</definedName>
+    <definedName name="std_part_27" localSheetId="0">'1er Año'!$W$42</definedName>
+    <definedName name="std_num_28" localSheetId="0">'1er Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="0">'1er Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="0">'1er Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="0">'1er Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="0">'1er Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="0">'1er Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="0">'1er Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="0">'1er Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="0">'1er Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="0">'1er Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="0">'1er Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="0">'1er Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="0">'1er Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="0">'1er Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="0">'1er Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="0">'1er Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="0">'1er Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="0">'1er Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="0">'1er Año'!$V$43</definedName>
+    <definedName name="std_part_28" localSheetId="0">'1er Año'!$W$43</definedName>
+    <definedName name="std_num_29" localSheetId="0">'1er Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="0">'1er Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="0">'1er Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="0">'1er Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="0">'1er Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="0">'1er Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="0">'1er Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="0">'1er Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="0">'1er Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="0">'1er Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="0">'1er Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="0">'1er Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="0">'1er Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="0">'1er Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="0">'1er Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="0">'1er Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="0">'1er Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="0">'1er Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="0">'1er Año'!$V$44</definedName>
+    <definedName name="std_part_29" localSheetId="0">'1er Año'!$W$44</definedName>
+    <definedName name="std_num_30" localSheetId="0">'1er Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="0">'1er Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="0">'1er Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="0">'1er Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="0">'1er Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="0">'1er Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="0">'1er Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="0">'1er Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="0">'1er Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="0">'1er Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="0">'1er Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="0">'1er Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="0">'1er Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="0">'1er Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="0">'1er Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="0">'1er Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="0">'1er Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="0">'1er Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="0">'1er Año'!$V$45</definedName>
+    <definedName name="std_part_30" localSheetId="0">'1er Año'!$W$45</definedName>
+    <definedName name="std_num_31" localSheetId="0">'1er Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="0">'1er Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="0">'1er Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="0">'1er Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="0">'1er Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="0">'1er Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="0">'1er Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="0">'1er Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="0">'1er Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="0">'1er Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="0">'1er Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="0">'1er Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="0">'1er Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="0">'1er Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="0">'1er Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="0">'1er Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="0">'1er Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="0">'1er Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="0">'1er Año'!$V$46</definedName>
+    <definedName name="std_part_31" localSheetId="0">'1er Año'!$W$46</definedName>
+    <definedName name="std_num_32" localSheetId="0">'1er Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="0">'1er Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="0">'1er Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="0">'1er Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="0">'1er Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="0">'1er Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="0">'1er Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="0">'1er Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="0">'1er Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="0">'1er Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="0">'1er Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="0">'1er Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="0">'1er Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="0">'1er Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="0">'1er Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="0">'1er Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="0">'1er Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="0">'1er Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="0">'1er Año'!$V$47</definedName>
+    <definedName name="std_part_32" localSheetId="0">'1er Año'!$W$47</definedName>
+    <definedName name="std_num_33" localSheetId="0">'1er Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="0">'1er Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="0">'1er Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="0">'1er Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="0">'1er Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="0">'1er Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="0">'1er Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="0">'1er Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="0">'1er Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="0">'1er Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="0">'1er Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="0">'1er Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="0">'1er Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="0">'1er Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="0">'1er Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="0">'1er Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="0">'1er Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="0">'1er Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="0">'1er Año'!$V$48</definedName>
+    <definedName name="std_part_33" localSheetId="0">'1er Año'!$W$48</definedName>
+    <definedName name="std_num_34" localSheetId="0">'1er Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="0">'1er Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="0">'1er Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="0">'1er Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="0">'1er Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="0">'1er Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="0">'1er Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="0">'1er Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="0">'1er Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="0">'1er Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="0">'1er Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="0">'1er Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="0">'1er Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="0">'1er Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="0">'1er Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="0">'1er Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="0">'1er Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="0">'1er Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="0">'1er Año'!$V$49</definedName>
+    <definedName name="std_part_34" localSheetId="0">'1er Año'!$W$49</definedName>
+    <definedName name="std_num_35" localSheetId="0">'1er Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="0">'1er Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="0">'1er Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="0">'1er Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="0">'1er Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="0">'1er Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="0">'1er Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="0">'1er Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="0">'1er Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="0">'1er Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="0">'1er Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="0">'1er Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="0">'1er Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="0">'1er Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="0">'1er Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="0">'1er Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="0">'1er Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="0">'1er Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="0">'1er Año'!$V$50</definedName>
+    <definedName name="std_part_35" localSheetId="0">'1er Año'!$W$50</definedName>
+    <definedName name="inst_period" localSheetId="1">'3er Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="1">'3er Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="1">'3er Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="1">'3er Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="1">'3er Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="1">'3er Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="1">'3er Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="1">'3er Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="1">'3er Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="1">'3er Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="1">'3er Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="1">'3er Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="1">'3er Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="1">'3er Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="1">'3er Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="1">'3er Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="1">'3er Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="1">'3er Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="1">'3er Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="1">'3er Año'!$V$15</definedName>
+    <definedName name="subj_10" localSheetId="1">'3er Año'!$W$15</definedName>
+    <definedName name="std_num_1" localSheetId="1">'3er Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="1">'3er Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="1">'3er Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="1">'3er Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="1">'3er Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="1">'3er Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="1">'3er Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="1">'3er Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="1">'3er Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="1">'3er Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="1">'3er Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="1">'3er Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="1">'3er Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="1">'3er Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="1">'3er Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="1">'3er Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="1">'3er Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="1">'3er Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="1">'3er Año'!$V$16</definedName>
+    <definedName name="grade_10_1" localSheetId="1">'3er Año'!$W$16</definedName>
+    <definedName name="std_part_1" localSheetId="1">'3er Año'!$X$16</definedName>
+    <definedName name="std_num_2" localSheetId="1">'3er Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="1">'3er Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="1">'3er Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="1">'3er Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="1">'3er Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="1">'3er Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="1">'3er Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="1">'3er Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="1">'3er Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="1">'3er Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="1">'3er Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="1">'3er Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="1">'3er Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="1">'3er Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="1">'3er Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="1">'3er Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="1">'3er Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="1">'3er Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="1">'3er Año'!$V$17</definedName>
+    <definedName name="grade_10_2" localSheetId="1">'3er Año'!$W$17</definedName>
+    <definedName name="std_part_2" localSheetId="1">'3er Año'!$X$17</definedName>
+    <definedName name="std_num_3" localSheetId="1">'3er Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="1">'3er Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="1">'3er Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="1">'3er Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="1">'3er Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="1">'3er Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="1">'3er Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="1">'3er Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="1">'3er Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="1">'3er Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="1">'3er Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="1">'3er Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="1">'3er Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="1">'3er Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="1">'3er Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="1">'3er Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="1">'3er Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="1">'3er Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="1">'3er Año'!$V$18</definedName>
+    <definedName name="grade_10_3" localSheetId="1">'3er Año'!$W$18</definedName>
+    <definedName name="std_part_3" localSheetId="1">'3er Año'!$X$18</definedName>
+    <definedName name="std_num_4" localSheetId="1">'3er Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="1">'3er Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="1">'3er Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="1">'3er Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="1">'3er Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="1">'3er Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="1">'3er Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="1">'3er Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="1">'3er Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="1">'3er Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="1">'3er Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="1">'3er Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="1">'3er Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="1">'3er Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="1">'3er Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="1">'3er Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="1">'3er Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="1">'3er Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="1">'3er Año'!$V$19</definedName>
+    <definedName name="grade_10_4" localSheetId="1">'3er Año'!$W$19</definedName>
+    <definedName name="std_part_4" localSheetId="1">'3er Año'!$X$19</definedName>
+    <definedName name="std_num_5" localSheetId="1">'3er Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="1">'3er Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="1">'3er Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="1">'3er Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="1">'3er Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="1">'3er Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="1">'3er Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="1">'3er Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="1">'3er Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="1">'3er Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="1">'3er Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="1">'3er Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="1">'3er Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="1">'3er Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="1">'3er Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="1">'3er Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="1">'3er Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="1">'3er Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="1">'3er Año'!$V$20</definedName>
+    <definedName name="grade_10_5" localSheetId="1">'3er Año'!$W$20</definedName>
+    <definedName name="std_part_5" localSheetId="1">'3er Año'!$X$20</definedName>
+    <definedName name="std_num_6" localSheetId="1">'3er Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="1">'3er Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="1">'3er Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="1">'3er Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="1">'3er Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="1">'3er Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="1">'3er Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="1">'3er Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="1">'3er Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="1">'3er Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="1">'3er Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="1">'3er Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="1">'3er Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="1">'3er Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="1">'3er Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="1">'3er Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="1">'3er Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="1">'3er Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="1">'3er Año'!$V$21</definedName>
+    <definedName name="grade_10_6" localSheetId="1">'3er Año'!$W$21</definedName>
+    <definedName name="std_part_6" localSheetId="1">'3er Año'!$X$21</definedName>
+    <definedName name="std_num_7" localSheetId="1">'3er Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="1">'3er Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="1">'3er Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="1">'3er Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="1">'3er Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="1">'3er Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="1">'3er Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="1">'3er Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="1">'3er Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="1">'3er Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="1">'3er Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="1">'3er Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="1">'3er Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="1">'3er Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="1">'3er Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="1">'3er Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="1">'3er Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="1">'3er Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="1">'3er Año'!$V$22</definedName>
+    <definedName name="grade_10_7" localSheetId="1">'3er Año'!$W$22</definedName>
+    <definedName name="std_part_7" localSheetId="1">'3er Año'!$X$22</definedName>
+    <definedName name="std_num_8" localSheetId="1">'3er Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="1">'3er Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="1">'3er Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="1">'3er Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="1">'3er Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="1">'3er Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="1">'3er Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="1">'3er Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="1">'3er Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="1">'3er Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="1">'3er Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="1">'3er Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="1">'3er Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="1">'3er Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="1">'3er Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="1">'3er Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="1">'3er Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="1">'3er Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="1">'3er Año'!$V$23</definedName>
+    <definedName name="grade_10_8" localSheetId="1">'3er Año'!$W$23</definedName>
+    <definedName name="std_part_8" localSheetId="1">'3er Año'!$X$23</definedName>
+    <definedName name="std_num_9" localSheetId="1">'3er Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="1">'3er Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="1">'3er Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="1">'3er Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="1">'3er Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="1">'3er Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="1">'3er Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="1">'3er Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="1">'3er Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="1">'3er Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="1">'3er Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="1">'3er Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="1">'3er Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="1">'3er Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="1">'3er Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="1">'3er Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="1">'3er Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="1">'3er Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="1">'3er Año'!$V$24</definedName>
+    <definedName name="grade_10_9" localSheetId="1">'3er Año'!$W$24</definedName>
+    <definedName name="std_part_9" localSheetId="1">'3er Año'!$X$24</definedName>
+    <definedName name="std_num_10" localSheetId="1">'3er Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="1">'3er Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="1">'3er Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="1">'3er Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="1">'3er Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="1">'3er Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="1">'3er Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="1">'3er Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="1">'3er Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="1">'3er Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="1">'3er Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="1">'3er Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="1">'3er Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="1">'3er Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="1">'3er Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="1">'3er Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="1">'3er Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="1">'3er Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="1">'3er Año'!$V$25</definedName>
+    <definedName name="grade_10_10" localSheetId="1">'3er Año'!$W$25</definedName>
+    <definedName name="std_part_10" localSheetId="1">'3er Año'!$X$25</definedName>
+    <definedName name="std_num_11" localSheetId="1">'3er Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="1">'3er Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="1">'3er Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="1">'3er Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="1">'3er Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="1">'3er Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="1">'3er Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="1">'3er Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="1">'3er Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="1">'3er Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="1">'3er Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="1">'3er Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="1">'3er Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="1">'3er Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="1">'3er Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="1">'3er Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="1">'3er Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="1">'3er Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="1">'3er Año'!$V$26</definedName>
+    <definedName name="grade_10_11" localSheetId="1">'3er Año'!$W$26</definedName>
+    <definedName name="std_part_11" localSheetId="1">'3er Año'!$X$26</definedName>
+    <definedName name="std_num_12" localSheetId="1">'3er Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="1">'3er Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="1">'3er Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="1">'3er Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="1">'3er Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="1">'3er Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="1">'3er Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="1">'3er Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="1">'3er Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="1">'3er Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="1">'3er Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="1">'3er Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="1">'3er Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="1">'3er Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="1">'3er Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="1">'3er Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="1">'3er Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="1">'3er Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="1">'3er Año'!$V$27</definedName>
+    <definedName name="grade_10_12" localSheetId="1">'3er Año'!$W$27</definedName>
+    <definedName name="std_part_12" localSheetId="1">'3er Año'!$X$27</definedName>
+    <definedName name="std_num_13" localSheetId="1">'3er Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="1">'3er Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="1">'3er Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="1">'3er Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="1">'3er Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="1">'3er Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="1">'3er Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="1">'3er Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="1">'3er Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="1">'3er Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="1">'3er Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="1">'3er Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="1">'3er Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="1">'3er Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="1">'3er Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="1">'3er Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="1">'3er Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="1">'3er Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="1">'3er Año'!$V$28</definedName>
+    <definedName name="grade_10_13" localSheetId="1">'3er Año'!$W$28</definedName>
+    <definedName name="std_part_13" localSheetId="1">'3er Año'!$X$28</definedName>
+    <definedName name="std_num_14" localSheetId="1">'3er Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="1">'3er Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="1">'3er Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="1">'3er Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="1">'3er Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="1">'3er Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="1">'3er Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="1">'3er Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="1">'3er Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="1">'3er Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="1">'3er Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="1">'3er Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="1">'3er Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="1">'3er Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="1">'3er Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="1">'3er Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="1">'3er Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="1">'3er Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="1">'3er Año'!$V$29</definedName>
+    <definedName name="grade_10_14" localSheetId="1">'3er Año'!$W$29</definedName>
+    <definedName name="std_part_14" localSheetId="1">'3er Año'!$X$29</definedName>
+    <definedName name="std_num_15" localSheetId="1">'3er Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="1">'3er Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="1">'3er Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="1">'3er Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="1">'3er Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="1">'3er Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="1">'3er Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="1">'3er Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="1">'3er Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="1">'3er Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="1">'3er Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="1">'3er Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="1">'3er Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="1">'3er Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="1">'3er Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="1">'3er Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="1">'3er Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="1">'3er Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="1">'3er Año'!$V$30</definedName>
+    <definedName name="grade_10_15" localSheetId="1">'3er Año'!$W$30</definedName>
+    <definedName name="std_part_15" localSheetId="1">'3er Año'!$X$30</definedName>
+    <definedName name="std_num_16" localSheetId="1">'3er Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="1">'3er Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="1">'3er Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="1">'3er Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="1">'3er Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="1">'3er Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="1">'3er Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="1">'3er Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="1">'3er Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="1">'3er Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="1">'3er Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="1">'3er Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="1">'3er Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="1">'3er Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="1">'3er Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="1">'3er Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="1">'3er Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="1">'3er Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="1">'3er Año'!$V$31</definedName>
+    <definedName name="grade_10_16" localSheetId="1">'3er Año'!$W$31</definedName>
+    <definedName name="std_part_16" localSheetId="1">'3er Año'!$X$31</definedName>
+    <definedName name="std_num_17" localSheetId="1">'3er Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="1">'3er Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="1">'3er Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="1">'3er Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="1">'3er Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="1">'3er Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="1">'3er Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="1">'3er Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="1">'3er Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="1">'3er Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="1">'3er Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="1">'3er Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="1">'3er Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="1">'3er Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="1">'3er Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="1">'3er Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="1">'3er Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="1">'3er Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="1">'3er Año'!$V$32</definedName>
+    <definedName name="grade_10_17" localSheetId="1">'3er Año'!$W$32</definedName>
+    <definedName name="std_part_17" localSheetId="1">'3er Año'!$X$32</definedName>
+    <definedName name="std_num_18" localSheetId="1">'3er Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="1">'3er Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="1">'3er Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="1">'3er Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="1">'3er Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="1">'3er Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="1">'3er Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="1">'3er Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="1">'3er Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="1">'3er Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="1">'3er Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="1">'3er Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="1">'3er Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="1">'3er Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="1">'3er Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="1">'3er Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="1">'3er Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="1">'3er Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="1">'3er Año'!$V$33</definedName>
+    <definedName name="grade_10_18" localSheetId="1">'3er Año'!$W$33</definedName>
+    <definedName name="std_part_18" localSheetId="1">'3er Año'!$X$33</definedName>
+    <definedName name="std_num_19" localSheetId="1">'3er Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="1">'3er Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="1">'3er Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="1">'3er Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="1">'3er Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="1">'3er Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="1">'3er Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="1">'3er Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="1">'3er Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="1">'3er Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="1">'3er Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="1">'3er Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="1">'3er Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="1">'3er Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="1">'3er Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="1">'3er Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="1">'3er Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="1">'3er Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="1">'3er Año'!$V$34</definedName>
+    <definedName name="grade_10_19" localSheetId="1">'3er Año'!$W$34</definedName>
+    <definedName name="std_part_19" localSheetId="1">'3er Año'!$X$34</definedName>
+    <definedName name="std_num_20" localSheetId="1">'3er Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="1">'3er Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="1">'3er Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="1">'3er Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="1">'3er Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="1">'3er Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="1">'3er Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="1">'3er Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="1">'3er Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="1">'3er Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="1">'3er Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="1">'3er Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="1">'3er Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="1">'3er Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="1">'3er Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="1">'3er Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="1">'3er Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="1">'3er Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="1">'3er Año'!$V$35</definedName>
+    <definedName name="grade_10_20" localSheetId="1">'3er Año'!$W$35</definedName>
+    <definedName name="std_part_20" localSheetId="1">'3er Año'!$X$35</definedName>
+    <definedName name="std_num_21" localSheetId="1">'3er Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="1">'3er Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="1">'3er Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="1">'3er Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="1">'3er Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="1">'3er Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="1">'3er Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="1">'3er Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="1">'3er Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="1">'3er Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="1">'3er Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="1">'3er Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="1">'3er Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="1">'3er Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="1">'3er Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="1">'3er Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="1">'3er Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="1">'3er Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="1">'3er Año'!$V$36</definedName>
+    <definedName name="grade_10_21" localSheetId="1">'3er Año'!$W$36</definedName>
+    <definedName name="std_part_21" localSheetId="1">'3er Año'!$X$36</definedName>
+    <definedName name="std_num_22" localSheetId="1">'3er Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="1">'3er Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="1">'3er Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="1">'3er Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="1">'3er Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="1">'3er Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="1">'3er Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="1">'3er Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="1">'3er Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="1">'3er Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="1">'3er Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="1">'3er Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="1">'3er Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="1">'3er Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="1">'3er Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="1">'3er Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="1">'3er Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="1">'3er Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="1">'3er Año'!$V$37</definedName>
+    <definedName name="grade_10_22" localSheetId="1">'3er Año'!$W$37</definedName>
+    <definedName name="std_part_22" localSheetId="1">'3er Año'!$X$37</definedName>
+    <definedName name="std_num_23" localSheetId="1">'3er Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="1">'3er Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="1">'3er Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="1">'3er Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="1">'3er Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="1">'3er Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="1">'3er Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="1">'3er Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="1">'3er Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="1">'3er Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="1">'3er Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="1">'3er Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="1">'3er Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="1">'3er Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="1">'3er Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="1">'3er Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="1">'3er Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="1">'3er Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="1">'3er Año'!$V$38</definedName>
+    <definedName name="grade_10_23" localSheetId="1">'3er Año'!$W$38</definedName>
+    <definedName name="std_part_23" localSheetId="1">'3er Año'!$X$38</definedName>
+    <definedName name="std_num_24" localSheetId="1">'3er Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="1">'3er Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="1">'3er Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="1">'3er Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="1">'3er Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="1">'3er Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="1">'3er Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="1">'3er Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="1">'3er Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="1">'3er Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="1">'3er Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="1">'3er Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="1">'3er Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="1">'3er Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="1">'3er Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="1">'3er Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="1">'3er Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="1">'3er Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="1">'3er Año'!$V$39</definedName>
+    <definedName name="grade_10_24" localSheetId="1">'3er Año'!$W$39</definedName>
+    <definedName name="std_part_24" localSheetId="1">'3er Año'!$X$39</definedName>
+    <definedName name="std_num_25" localSheetId="1">'3er Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="1">'3er Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="1">'3er Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="1">'3er Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="1">'3er Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="1">'3er Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="1">'3er Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="1">'3er Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="1">'3er Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="1">'3er Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="1">'3er Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="1">'3er Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="1">'3er Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="1">'3er Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="1">'3er Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="1">'3er Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="1">'3er Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="1">'3er Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="1">'3er Año'!$V$40</definedName>
+    <definedName name="grade_10_25" localSheetId="1">'3er Año'!$W$40</definedName>
+    <definedName name="std_part_25" localSheetId="1">'3er Año'!$X$40</definedName>
+    <definedName name="std_num_26" localSheetId="1">'3er Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="1">'3er Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="1">'3er Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="1">'3er Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="1">'3er Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="1">'3er Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="1">'3er Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="1">'3er Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="1">'3er Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="1">'3er Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="1">'3er Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="1">'3er Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="1">'3er Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="1">'3er Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="1">'3er Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="1">'3er Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="1">'3er Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="1">'3er Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="1">'3er Año'!$V$41</definedName>
+    <definedName name="grade_10_26" localSheetId="1">'3er Año'!$W$41</definedName>
+    <definedName name="std_part_26" localSheetId="1">'3er Año'!$X$41</definedName>
+    <definedName name="std_num_27" localSheetId="1">'3er Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="1">'3er Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="1">'3er Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="1">'3er Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="1">'3er Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="1">'3er Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="1">'3er Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="1">'3er Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="1">'3er Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="1">'3er Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="1">'3er Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="1">'3er Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="1">'3er Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="1">'3er Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="1">'3er Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="1">'3er Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="1">'3er Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="1">'3er Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="1">'3er Año'!$V$42</definedName>
+    <definedName name="grade_10_27" localSheetId="1">'3er Año'!$W$42</definedName>
+    <definedName name="std_part_27" localSheetId="1">'3er Año'!$X$42</definedName>
+    <definedName name="std_num_28" localSheetId="1">'3er Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="1">'3er Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="1">'3er Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="1">'3er Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="1">'3er Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="1">'3er Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="1">'3er Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="1">'3er Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="1">'3er Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="1">'3er Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="1">'3er Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="1">'3er Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="1">'3er Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="1">'3er Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="1">'3er Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="1">'3er Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="1">'3er Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="1">'3er Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="1">'3er Año'!$V$43</definedName>
+    <definedName name="grade_10_28" localSheetId="1">'3er Año'!$W$43</definedName>
+    <definedName name="std_part_28" localSheetId="1">'3er Año'!$X$43</definedName>
+    <definedName name="std_num_29" localSheetId="1">'3er Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="1">'3er Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="1">'3er Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="1">'3er Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="1">'3er Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="1">'3er Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="1">'3er Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="1">'3er Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="1">'3er Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="1">'3er Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="1">'3er Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="1">'3er Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="1">'3er Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="1">'3er Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="1">'3er Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="1">'3er Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="1">'3er Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="1">'3er Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="1">'3er Año'!$V$44</definedName>
+    <definedName name="grade_10_29" localSheetId="1">'3er Año'!$W$44</definedName>
+    <definedName name="std_part_29" localSheetId="1">'3er Año'!$X$44</definedName>
+    <definedName name="std_num_30" localSheetId="1">'3er Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="1">'3er Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="1">'3er Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="1">'3er Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="1">'3er Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="1">'3er Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="1">'3er Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="1">'3er Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="1">'3er Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="1">'3er Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="1">'3er Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="1">'3er Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="1">'3er Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="1">'3er Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="1">'3er Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="1">'3er Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="1">'3er Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="1">'3er Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="1">'3er Año'!$V$45</definedName>
+    <definedName name="grade_10_30" localSheetId="1">'3er Año'!$W$45</definedName>
+    <definedName name="std_part_30" localSheetId="1">'3er Año'!$X$45</definedName>
+    <definedName name="std_num_31" localSheetId="1">'3er Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="1">'3er Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="1">'3er Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="1">'3er Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="1">'3er Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="1">'3er Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="1">'3er Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="1">'3er Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="1">'3er Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="1">'3er Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="1">'3er Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="1">'3er Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="1">'3er Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="1">'3er Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="1">'3er Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="1">'3er Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="1">'3er Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="1">'3er Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="1">'3er Año'!$V$46</definedName>
+    <definedName name="grade_10_31" localSheetId="1">'3er Año'!$W$46</definedName>
+    <definedName name="std_part_31" localSheetId="1">'3er Año'!$X$46</definedName>
+    <definedName name="std_num_32" localSheetId="1">'3er Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="1">'3er Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="1">'3er Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="1">'3er Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="1">'3er Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="1">'3er Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="1">'3er Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="1">'3er Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="1">'3er Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="1">'3er Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="1">'3er Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="1">'3er Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="1">'3er Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="1">'3er Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="1">'3er Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="1">'3er Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="1">'3er Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="1">'3er Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="1">'3er Año'!$V$47</definedName>
+    <definedName name="grade_10_32" localSheetId="1">'3er Año'!$W$47</definedName>
+    <definedName name="std_part_32" localSheetId="1">'3er Año'!$X$47</definedName>
+    <definedName name="std_num_33" localSheetId="1">'3er Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="1">'3er Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="1">'3er Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="1">'3er Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="1">'3er Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="1">'3er Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="1">'3er Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="1">'3er Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="1">'3er Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="1">'3er Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="1">'3er Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="1">'3er Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="1">'3er Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="1">'3er Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="1">'3er Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="1">'3er Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="1">'3er Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="1">'3er Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="1">'3er Año'!$V$48</definedName>
+    <definedName name="grade_10_33" localSheetId="1">'3er Año'!$W$48</definedName>
+    <definedName name="std_part_33" localSheetId="1">'3er Año'!$X$48</definedName>
+    <definedName name="std_num_34" localSheetId="1">'3er Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="1">'3er Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="1">'3er Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="1">'3er Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="1">'3er Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="1">'3er Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="1">'3er Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="1">'3er Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="1">'3er Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="1">'3er Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="1">'3er Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="1">'3er Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="1">'3er Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="1">'3er Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="1">'3er Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="1">'3er Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="1">'3er Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="1">'3er Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="1">'3er Año'!$V$49</definedName>
+    <definedName name="grade_10_34" localSheetId="1">'3er Año'!$W$49</definedName>
+    <definedName name="std_part_34" localSheetId="1">'3er Año'!$X$49</definedName>
+    <definedName name="std_num_35" localSheetId="1">'3er Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="1">'3er Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="1">'3er Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="1">'3er Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="1">'3er Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="1">'3er Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="1">'3er Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="1">'3er Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="1">'3er Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="1">'3er Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="1">'3er Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="1">'3er Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="1">'3er Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="1">'3er Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="1">'3er Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="1">'3er Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="1">'3er Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="1">'3er Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="1">'3er Año'!$V$50</definedName>
+    <definedName name="grade_10_35" localSheetId="1">'3er Año'!$W$50</definedName>
+    <definedName name="std_part_35" localSheetId="1">'3er Año'!$X$50</definedName>
+    <definedName name="inst_period" localSheetId="2">'4to Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="2">'4to Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="2">'4to Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="2">'4to Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="2">'4to Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="2">'4to Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="2">'4to Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="2">'4to Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="2">'4to Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="2">'4to Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="2">'4to Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="2">'4to Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="2">'4to Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="2">'4to Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="2">'4to Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="2">'4to Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="2">'4to Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="2">'4to Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="2">'4to Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="2">'4to Año'!$V$15</definedName>
+    <definedName name="subj_10" localSheetId="2">'4to Año'!$W$15</definedName>
+    <definedName name="subj_11" localSheetId="2">'4to Año'!$X$15</definedName>
+    <definedName name="std_num_1" localSheetId="2">'4to Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="2">'4to Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="2">'4to Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="2">'4to Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="2">'4to Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="2">'4to Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="2">'4to Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="2">'4to Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="2">'4to Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="2">'4to Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="2">'4to Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="2">'4to Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="2">'4to Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="2">'4to Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="2">'4to Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="2">'4to Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="2">'4to Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="2">'4to Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="2">'4to Año'!$V$16</definedName>
+    <definedName name="grade_10_1" localSheetId="2">'4to Año'!$W$16</definedName>
+    <definedName name="grade_11_1" localSheetId="2">'4to Año'!$X$16</definedName>
+    <definedName name="std_part_1" localSheetId="2">'4to Año'!$Y$16</definedName>
+    <definedName name="std_num_2" localSheetId="2">'4to Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="2">'4to Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="2">'4to Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="2">'4to Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="2">'4to Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="2">'4to Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="2">'4to Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="2">'4to Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="2">'4to Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="2">'4to Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="2">'4to Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="2">'4to Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="2">'4to Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="2">'4to Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="2">'4to Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="2">'4to Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="2">'4to Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="2">'4to Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="2">'4to Año'!$V$17</definedName>
+    <definedName name="grade_10_2" localSheetId="2">'4to Año'!$W$17</definedName>
+    <definedName name="grade_11_2" localSheetId="2">'4to Año'!$X$17</definedName>
+    <definedName name="std_part_2" localSheetId="2">'4to Año'!$Y$17</definedName>
+    <definedName name="std_num_3" localSheetId="2">'4to Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="2">'4to Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="2">'4to Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="2">'4to Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="2">'4to Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="2">'4to Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="2">'4to Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="2">'4to Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="2">'4to Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="2">'4to Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="2">'4to Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="2">'4to Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="2">'4to Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="2">'4to Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="2">'4to Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="2">'4to Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="2">'4to Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="2">'4to Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="2">'4to Año'!$V$18</definedName>
+    <definedName name="grade_10_3" localSheetId="2">'4to Año'!$W$18</definedName>
+    <definedName name="grade_11_3" localSheetId="2">'4to Año'!$X$18</definedName>
+    <definedName name="std_part_3" localSheetId="2">'4to Año'!$Y$18</definedName>
+    <definedName name="std_num_4" localSheetId="2">'4to Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="2">'4to Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="2">'4to Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="2">'4to Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="2">'4to Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="2">'4to Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="2">'4to Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="2">'4to Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="2">'4to Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="2">'4to Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="2">'4to Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="2">'4to Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="2">'4to Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="2">'4to Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="2">'4to Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="2">'4to Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="2">'4to Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="2">'4to Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="2">'4to Año'!$V$19</definedName>
+    <definedName name="grade_10_4" localSheetId="2">'4to Año'!$W$19</definedName>
+    <definedName name="grade_11_4" localSheetId="2">'4to Año'!$X$19</definedName>
+    <definedName name="std_part_4" localSheetId="2">'4to Año'!$Y$19</definedName>
+    <definedName name="std_num_5" localSheetId="2">'4to Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="2">'4to Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="2">'4to Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="2">'4to Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="2">'4to Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="2">'4to Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="2">'4to Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="2">'4to Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="2">'4to Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="2">'4to Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="2">'4to Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="2">'4to Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="2">'4to Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="2">'4to Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="2">'4to Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="2">'4to Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="2">'4to Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="2">'4to Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="2">'4to Año'!$V$20</definedName>
+    <definedName name="grade_10_5" localSheetId="2">'4to Año'!$W$20</definedName>
+    <definedName name="grade_11_5" localSheetId="2">'4to Año'!$X$20</definedName>
+    <definedName name="std_part_5" localSheetId="2">'4to Año'!$Y$20</definedName>
+    <definedName name="std_num_6" localSheetId="2">'4to Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="2">'4to Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="2">'4to Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="2">'4to Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="2">'4to Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="2">'4to Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="2">'4to Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="2">'4to Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="2">'4to Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="2">'4to Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="2">'4to Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="2">'4to Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="2">'4to Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="2">'4to Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="2">'4to Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="2">'4to Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="2">'4to Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="2">'4to Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="2">'4to Año'!$V$21</definedName>
+    <definedName name="grade_10_6" localSheetId="2">'4to Año'!$W$21</definedName>
+    <definedName name="grade_11_6" localSheetId="2">'4to Año'!$X$21</definedName>
+    <definedName name="std_part_6" localSheetId="2">'4to Año'!$Y$21</definedName>
+    <definedName name="std_num_7" localSheetId="2">'4to Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="2">'4to Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="2">'4to Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="2">'4to Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="2">'4to Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="2">'4to Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="2">'4to Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="2">'4to Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="2">'4to Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="2">'4to Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="2">'4to Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="2">'4to Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="2">'4to Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="2">'4to Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="2">'4to Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="2">'4to Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="2">'4to Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="2">'4to Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="2">'4to Año'!$V$22</definedName>
+    <definedName name="grade_10_7" localSheetId="2">'4to Año'!$W$22</definedName>
+    <definedName name="grade_11_7" localSheetId="2">'4to Año'!$X$22</definedName>
+    <definedName name="std_part_7" localSheetId="2">'4to Año'!$Y$22</definedName>
+    <definedName name="std_num_8" localSheetId="2">'4to Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="2">'4to Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="2">'4to Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="2">'4to Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="2">'4to Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="2">'4to Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="2">'4to Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="2">'4to Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="2">'4to Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="2">'4to Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="2">'4to Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="2">'4to Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="2">'4to Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="2">'4to Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="2">'4to Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="2">'4to Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="2">'4to Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="2">'4to Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="2">'4to Año'!$V$23</definedName>
+    <definedName name="grade_10_8" localSheetId="2">'4to Año'!$W$23</definedName>
+    <definedName name="grade_11_8" localSheetId="2">'4to Año'!$X$23</definedName>
+    <definedName name="std_part_8" localSheetId="2">'4to Año'!$Y$23</definedName>
+    <definedName name="std_num_9" localSheetId="2">'4to Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="2">'4to Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="2">'4to Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="2">'4to Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="2">'4to Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="2">'4to Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="2">'4to Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="2">'4to Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="2">'4to Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="2">'4to Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="2">'4to Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="2">'4to Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="2">'4to Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="2">'4to Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="2">'4to Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="2">'4to Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="2">'4to Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="2">'4to Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="2">'4to Año'!$V$24</definedName>
+    <definedName name="grade_10_9" localSheetId="2">'4to Año'!$W$24</definedName>
+    <definedName name="grade_11_9" localSheetId="2">'4to Año'!$X$24</definedName>
+    <definedName name="std_part_9" localSheetId="2">'4to Año'!$Y$24</definedName>
+    <definedName name="std_num_10" localSheetId="2">'4to Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="2">'4to Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="2">'4to Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="2">'4to Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="2">'4to Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="2">'4to Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="2">'4to Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="2">'4to Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="2">'4to Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="2">'4to Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="2">'4to Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="2">'4to Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="2">'4to Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="2">'4to Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="2">'4to Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="2">'4to Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="2">'4to Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="2">'4to Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="2">'4to Año'!$V$25</definedName>
+    <definedName name="grade_10_10" localSheetId="2">'4to Año'!$W$25</definedName>
+    <definedName name="grade_11_10" localSheetId="2">'4to Año'!$X$25</definedName>
+    <definedName name="std_part_10" localSheetId="2">'4to Año'!$Y$25</definedName>
+    <definedName name="std_num_11" localSheetId="2">'4to Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="2">'4to Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="2">'4to Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="2">'4to Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="2">'4to Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="2">'4to Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="2">'4to Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="2">'4to Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="2">'4to Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="2">'4to Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="2">'4to Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="2">'4to Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="2">'4to Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="2">'4to Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="2">'4to Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="2">'4to Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="2">'4to Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="2">'4to Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="2">'4to Año'!$V$26</definedName>
+    <definedName name="grade_10_11" localSheetId="2">'4to Año'!$W$26</definedName>
+    <definedName name="grade_11_11" localSheetId="2">'4to Año'!$X$26</definedName>
+    <definedName name="std_part_11" localSheetId="2">'4to Año'!$Y$26</definedName>
+    <definedName name="std_num_12" localSheetId="2">'4to Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="2">'4to Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="2">'4to Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="2">'4to Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="2">'4to Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="2">'4to Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="2">'4to Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="2">'4to Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="2">'4to Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="2">'4to Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="2">'4to Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="2">'4to Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="2">'4to Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="2">'4to Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="2">'4to Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="2">'4to Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="2">'4to Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="2">'4to Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="2">'4to Año'!$V$27</definedName>
+    <definedName name="grade_10_12" localSheetId="2">'4to Año'!$W$27</definedName>
+    <definedName name="grade_11_12" localSheetId="2">'4to Año'!$X$27</definedName>
+    <definedName name="std_part_12" localSheetId="2">'4to Año'!$Y$27</definedName>
+    <definedName name="std_num_13" localSheetId="2">'4to Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="2">'4to Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="2">'4to Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="2">'4to Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="2">'4to Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="2">'4to Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="2">'4to Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="2">'4to Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="2">'4to Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="2">'4to Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="2">'4to Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="2">'4to Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="2">'4to Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="2">'4to Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="2">'4to Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="2">'4to Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="2">'4to Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="2">'4to Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="2">'4to Año'!$V$28</definedName>
+    <definedName name="grade_10_13" localSheetId="2">'4to Año'!$W$28</definedName>
+    <definedName name="grade_11_13" localSheetId="2">'4to Año'!$X$28</definedName>
+    <definedName name="std_part_13" localSheetId="2">'4to Año'!$Y$28</definedName>
+    <definedName name="std_num_14" localSheetId="2">'4to Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="2">'4to Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="2">'4to Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="2">'4to Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="2">'4to Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="2">'4to Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="2">'4to Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="2">'4to Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="2">'4to Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="2">'4to Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="2">'4to Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="2">'4to Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="2">'4to Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="2">'4to Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="2">'4to Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="2">'4to Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="2">'4to Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="2">'4to Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="2">'4to Año'!$V$29</definedName>
+    <definedName name="grade_10_14" localSheetId="2">'4to Año'!$W$29</definedName>
+    <definedName name="grade_11_14" localSheetId="2">'4to Año'!$X$29</definedName>
+    <definedName name="std_part_14" localSheetId="2">'4to Año'!$Y$29</definedName>
+    <definedName name="std_num_15" localSheetId="2">'4to Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="2">'4to Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="2">'4to Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="2">'4to Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="2">'4to Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="2">'4to Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="2">'4to Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="2">'4to Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="2">'4to Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="2">'4to Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="2">'4to Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="2">'4to Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="2">'4to Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="2">'4to Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="2">'4to Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="2">'4to Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="2">'4to Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="2">'4to Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="2">'4to Año'!$V$30</definedName>
+    <definedName name="grade_10_15" localSheetId="2">'4to Año'!$W$30</definedName>
+    <definedName name="grade_11_15" localSheetId="2">'4to Año'!$X$30</definedName>
+    <definedName name="std_part_15" localSheetId="2">'4to Año'!$Y$30</definedName>
+    <definedName name="std_num_16" localSheetId="2">'4to Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="2">'4to Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="2">'4to Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="2">'4to Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="2">'4to Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="2">'4to Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="2">'4to Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="2">'4to Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="2">'4to Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="2">'4to Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="2">'4to Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="2">'4to Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="2">'4to Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="2">'4to Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="2">'4to Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="2">'4to Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="2">'4to Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="2">'4to Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="2">'4to Año'!$V$31</definedName>
+    <definedName name="grade_10_16" localSheetId="2">'4to Año'!$W$31</definedName>
+    <definedName name="grade_11_16" localSheetId="2">'4to Año'!$X$31</definedName>
+    <definedName name="std_part_16" localSheetId="2">'4to Año'!$Y$31</definedName>
+    <definedName name="std_num_17" localSheetId="2">'4to Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="2">'4to Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="2">'4to Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="2">'4to Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="2">'4to Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="2">'4to Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="2">'4to Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="2">'4to Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="2">'4to Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="2">'4to Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="2">'4to Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="2">'4to Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="2">'4to Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="2">'4to Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="2">'4to Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="2">'4to Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="2">'4to Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="2">'4to Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="2">'4to Año'!$V$32</definedName>
+    <definedName name="grade_10_17" localSheetId="2">'4to Año'!$W$32</definedName>
+    <definedName name="grade_11_17" localSheetId="2">'4to Año'!$X$32</definedName>
+    <definedName name="std_part_17" localSheetId="2">'4to Año'!$Y$32</definedName>
+    <definedName name="std_num_18" localSheetId="2">'4to Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="2">'4to Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="2">'4to Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="2">'4to Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="2">'4to Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="2">'4to Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="2">'4to Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="2">'4to Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="2">'4to Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="2">'4to Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="2">'4to Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="2">'4to Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="2">'4to Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="2">'4to Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="2">'4to Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="2">'4to Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="2">'4to Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="2">'4to Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="2">'4to Año'!$V$33</definedName>
+    <definedName name="grade_10_18" localSheetId="2">'4to Año'!$W$33</definedName>
+    <definedName name="grade_11_18" localSheetId="2">'4to Año'!$X$33</definedName>
+    <definedName name="std_part_18" localSheetId="2">'4to Año'!$Y$33</definedName>
+    <definedName name="std_num_19" localSheetId="2">'4to Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="2">'4to Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="2">'4to Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="2">'4to Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="2">'4to Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="2">'4to Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="2">'4to Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="2">'4to Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="2">'4to Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="2">'4to Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="2">'4to Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="2">'4to Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="2">'4to Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="2">'4to Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="2">'4to Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="2">'4to Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="2">'4to Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="2">'4to Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="2">'4to Año'!$V$34</definedName>
+    <definedName name="grade_10_19" localSheetId="2">'4to Año'!$W$34</definedName>
+    <definedName name="grade_11_19" localSheetId="2">'4to Año'!$X$34</definedName>
+    <definedName name="std_part_19" localSheetId="2">'4to Año'!$Y$34</definedName>
+    <definedName name="std_num_20" localSheetId="2">'4to Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="2">'4to Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="2">'4to Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="2">'4to Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="2">'4to Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="2">'4to Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="2">'4to Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="2">'4to Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="2">'4to Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="2">'4to Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="2">'4to Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="2">'4to Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="2">'4to Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="2">'4to Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="2">'4to Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="2">'4to Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="2">'4to Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="2">'4to Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="2">'4to Año'!$V$35</definedName>
+    <definedName name="grade_10_20" localSheetId="2">'4to Año'!$W$35</definedName>
+    <definedName name="grade_11_20" localSheetId="2">'4to Año'!$X$35</definedName>
+    <definedName name="std_part_20" localSheetId="2">'4to Año'!$Y$35</definedName>
+    <definedName name="std_num_21" localSheetId="2">'4to Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="2">'4to Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="2">'4to Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="2">'4to Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="2">'4to Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="2">'4to Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="2">'4to Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="2">'4to Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="2">'4to Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="2">'4to Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="2">'4to Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="2">'4to Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="2">'4to Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="2">'4to Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="2">'4to Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="2">'4to Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="2">'4to Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="2">'4to Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="2">'4to Año'!$V$36</definedName>
+    <definedName name="grade_10_21" localSheetId="2">'4to Año'!$W$36</definedName>
+    <definedName name="grade_11_21" localSheetId="2">'4to Año'!$X$36</definedName>
+    <definedName name="std_part_21" localSheetId="2">'4to Año'!$Y$36</definedName>
+    <definedName name="std_num_22" localSheetId="2">'4to Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="2">'4to Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="2">'4to Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="2">'4to Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="2">'4to Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="2">'4to Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="2">'4to Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="2">'4to Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="2">'4to Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="2">'4to Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="2">'4to Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="2">'4to Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="2">'4to Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="2">'4to Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="2">'4to Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="2">'4to Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="2">'4to Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="2">'4to Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="2">'4to Año'!$V$37</definedName>
+    <definedName name="grade_10_22" localSheetId="2">'4to Año'!$W$37</definedName>
+    <definedName name="grade_11_22" localSheetId="2">'4to Año'!$X$37</definedName>
+    <definedName name="std_part_22" localSheetId="2">'4to Año'!$Y$37</definedName>
+    <definedName name="std_num_23" localSheetId="2">'4to Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="2">'4to Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="2">'4to Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="2">'4to Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="2">'4to Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="2">'4to Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="2">'4to Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="2">'4to Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="2">'4to Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="2">'4to Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="2">'4to Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="2">'4to Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="2">'4to Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="2">'4to Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="2">'4to Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="2">'4to Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="2">'4to Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="2">'4to Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="2">'4to Año'!$V$38</definedName>
+    <definedName name="grade_10_23" localSheetId="2">'4to Año'!$W$38</definedName>
+    <definedName name="grade_11_23" localSheetId="2">'4to Año'!$X$38</definedName>
+    <definedName name="std_part_23" localSheetId="2">'4to Año'!$Y$38</definedName>
+    <definedName name="std_num_24" localSheetId="2">'4to Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="2">'4to Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="2">'4to Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="2">'4to Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="2">'4to Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="2">'4to Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="2">'4to Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="2">'4to Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="2">'4to Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="2">'4to Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="2">'4to Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="2">'4to Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="2">'4to Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="2">'4to Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="2">'4to Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="2">'4to Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="2">'4to Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="2">'4to Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="2">'4to Año'!$V$39</definedName>
+    <definedName name="grade_10_24" localSheetId="2">'4to Año'!$W$39</definedName>
+    <definedName name="grade_11_24" localSheetId="2">'4to Año'!$X$39</definedName>
+    <definedName name="std_part_24" localSheetId="2">'4to Año'!$Y$39</definedName>
+    <definedName name="std_num_25" localSheetId="2">'4to Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="2">'4to Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="2">'4to Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="2">'4to Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="2">'4to Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="2">'4to Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="2">'4to Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="2">'4to Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="2">'4to Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="2">'4to Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="2">'4to Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="2">'4to Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="2">'4to Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="2">'4to Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="2">'4to Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="2">'4to Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="2">'4to Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="2">'4to Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="2">'4to Año'!$V$40</definedName>
+    <definedName name="grade_10_25" localSheetId="2">'4to Año'!$W$40</definedName>
+    <definedName name="grade_11_25" localSheetId="2">'4to Año'!$X$40</definedName>
+    <definedName name="std_part_25" localSheetId="2">'4to Año'!$Y$40</definedName>
+    <definedName name="std_num_26" localSheetId="2">'4to Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="2">'4to Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="2">'4to Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="2">'4to Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="2">'4to Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="2">'4to Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="2">'4to Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="2">'4to Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="2">'4to Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="2">'4to Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="2">'4to Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="2">'4to Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="2">'4to Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="2">'4to Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="2">'4to Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="2">'4to Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="2">'4to Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="2">'4to Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="2">'4to Año'!$V$41</definedName>
+    <definedName name="grade_10_26" localSheetId="2">'4to Año'!$W$41</definedName>
+    <definedName name="grade_11_26" localSheetId="2">'4to Año'!$X$41</definedName>
+    <definedName name="std_part_26" localSheetId="2">'4to Año'!$Y$41</definedName>
+    <definedName name="std_num_27" localSheetId="2">'4to Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="2">'4to Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="2">'4to Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="2">'4to Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="2">'4to Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="2">'4to Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="2">'4to Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="2">'4to Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="2">'4to Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="2">'4to Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="2">'4to Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="2">'4to Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="2">'4to Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="2">'4to Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="2">'4to Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="2">'4to Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="2">'4to Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="2">'4to Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="2">'4to Año'!$V$42</definedName>
+    <definedName name="grade_10_27" localSheetId="2">'4to Año'!$W$42</definedName>
+    <definedName name="grade_11_27" localSheetId="2">'4to Año'!$X$42</definedName>
+    <definedName name="std_part_27" localSheetId="2">'4to Año'!$Y$42</definedName>
+    <definedName name="std_num_28" localSheetId="2">'4to Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="2">'4to Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="2">'4to Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="2">'4to Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="2">'4to Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="2">'4to Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="2">'4to Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="2">'4to Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="2">'4to Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="2">'4to Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="2">'4to Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="2">'4to Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="2">'4to Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="2">'4to Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="2">'4to Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="2">'4to Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="2">'4to Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="2">'4to Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="2">'4to Año'!$V$43</definedName>
+    <definedName name="grade_10_28" localSheetId="2">'4to Año'!$W$43</definedName>
+    <definedName name="grade_11_28" localSheetId="2">'4to Año'!$X$43</definedName>
+    <definedName name="std_part_28" localSheetId="2">'4to Año'!$Y$43</definedName>
+    <definedName name="std_num_29" localSheetId="2">'4to Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="2">'4to Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="2">'4to Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="2">'4to Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="2">'4to Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="2">'4to Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="2">'4to Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="2">'4to Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="2">'4to Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="2">'4to Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="2">'4to Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="2">'4to Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="2">'4to Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="2">'4to Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="2">'4to Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="2">'4to Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="2">'4to Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="2">'4to Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="2">'4to Año'!$V$44</definedName>
+    <definedName name="grade_10_29" localSheetId="2">'4to Año'!$W$44</definedName>
+    <definedName name="grade_11_29" localSheetId="2">'4to Año'!$X$44</definedName>
+    <definedName name="std_part_29" localSheetId="2">'4to Año'!$Y$44</definedName>
+    <definedName name="std_num_30" localSheetId="2">'4to Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="2">'4to Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="2">'4to Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="2">'4to Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="2">'4to Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="2">'4to Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="2">'4to Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="2">'4to Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="2">'4to Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="2">'4to Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="2">'4to Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="2">'4to Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="2">'4to Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="2">'4to Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="2">'4to Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="2">'4to Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="2">'4to Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="2">'4to Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="2">'4to Año'!$V$45</definedName>
+    <definedName name="grade_10_30" localSheetId="2">'4to Año'!$W$45</definedName>
+    <definedName name="grade_11_30" localSheetId="2">'4to Año'!$X$45</definedName>
+    <definedName name="std_part_30" localSheetId="2">'4to Año'!$Y$45</definedName>
+    <definedName name="std_num_31" localSheetId="2">'4to Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="2">'4to Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="2">'4to Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="2">'4to Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="2">'4to Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="2">'4to Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="2">'4to Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="2">'4to Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="2">'4to Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="2">'4to Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="2">'4to Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="2">'4to Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="2">'4to Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="2">'4to Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="2">'4to Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="2">'4to Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="2">'4to Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="2">'4to Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="2">'4to Año'!$V$46</definedName>
+    <definedName name="grade_10_31" localSheetId="2">'4to Año'!$W$46</definedName>
+    <definedName name="grade_11_31" localSheetId="2">'4to Año'!$X$46</definedName>
+    <definedName name="std_part_31" localSheetId="2">'4to Año'!$Y$46</definedName>
+    <definedName name="std_num_32" localSheetId="2">'4to Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="2">'4to Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="2">'4to Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="2">'4to Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="2">'4to Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="2">'4to Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="2">'4to Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="2">'4to Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="2">'4to Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="2">'4to Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="2">'4to Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="2">'4to Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="2">'4to Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="2">'4to Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="2">'4to Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="2">'4to Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="2">'4to Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="2">'4to Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="2">'4to Año'!$V$47</definedName>
+    <definedName name="grade_10_32" localSheetId="2">'4to Año'!$W$47</definedName>
+    <definedName name="grade_11_32" localSheetId="2">'4to Año'!$X$47</definedName>
+    <definedName name="std_part_32" localSheetId="2">'4to Año'!$Y$47</definedName>
+    <definedName name="std_num_33" localSheetId="2">'4to Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="2">'4to Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="2">'4to Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="2">'4to Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="2">'4to Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="2">'4to Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="2">'4to Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="2">'4to Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="2">'4to Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="2">'4to Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="2">'4to Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="2">'4to Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="2">'4to Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="2">'4to Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="2">'4to Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="2">'4to Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="2">'4to Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="2">'4to Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="2">'4to Año'!$V$48</definedName>
+    <definedName name="grade_10_33" localSheetId="2">'4to Año'!$W$48</definedName>
+    <definedName name="grade_11_33" localSheetId="2">'4to Año'!$X$48</definedName>
+    <definedName name="std_part_33" localSheetId="2">'4to Año'!$Y$48</definedName>
+    <definedName name="std_num_34" localSheetId="2">'4to Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="2">'4to Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="2">'4to Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="2">'4to Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="2">'4to Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="2">'4to Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="2">'4to Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="2">'4to Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="2">'4to Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="2">'4to Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="2">'4to Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="2">'4to Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="2">'4to Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="2">'4to Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="2">'4to Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="2">'4to Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="2">'4to Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="2">'4to Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="2">'4to Año'!$V$49</definedName>
+    <definedName name="grade_10_34" localSheetId="2">'4to Año'!$W$49</definedName>
+    <definedName name="grade_11_34" localSheetId="2">'4to Año'!$X$49</definedName>
+    <definedName name="std_part_34" localSheetId="2">'4to Año'!$Y$49</definedName>
+    <definedName name="std_num_35" localSheetId="2">'4to Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="2">'4to Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="2">'4to Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="2">'4to Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="2">'4to Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="2">'4to Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="2">'4to Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="2">'4to Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="2">'4to Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="2">'4to Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="2">'4to Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="2">'4to Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="2">'4to Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="2">'4to Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="2">'4to Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="2">'4to Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="2">'4to Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="2">'4to Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="2">'4to Año'!$V$50</definedName>
+    <definedName name="grade_10_35" localSheetId="2">'4to Año'!$W$50</definedName>
+    <definedName name="grade_11_35" localSheetId="2">'4to Año'!$X$50</definedName>
+    <definedName name="std_part_35" localSheetId="2">'4to Año'!$Y$50</definedName>
+    <definedName name="inst_period" localSheetId="3">'5to Año'!$M$3</definedName>
+    <definedName name="inst_eval_type" localSheetId="3">'5to Año'!$N$4</definedName>
+    <definedName name="inst_code" localSheetId="3">'5to Año'!$E$7</definedName>
+    <definedName name="inst_name" localSheetId="3">'5to Año'!$J$7</definedName>
+    <definedName name="inst_address" localSheetId="3">'5to Año'!$C$8</definedName>
+    <definedName name="inst_phone" localSheetId="3">'5to Año'!$U$8</definedName>
+    <definedName name="inst_municipality" localSheetId="3">'5to Año'!$C$9</definedName>
+    <definedName name="inst_state" localSheetId="3">'5to Año'!$G$9</definedName>
+    <definedName name="inst_cdcee" localSheetId="3">'5to Año'!$N$9</definedName>
+    <definedName name="inst_director" localSheetId="3">'5to Año'!$C$10</definedName>
+    <definedName name="inst_director_doc" localSheetId="3">'5to Año'!$N$10</definedName>
+    <definedName name="subj_1" localSheetId="3">'5to Año'!$N$15</definedName>
+    <definedName name="subj_2" localSheetId="3">'5to Año'!$O$15</definedName>
+    <definedName name="subj_3" localSheetId="3">'5to Año'!$P$15</definedName>
+    <definedName name="subj_4" localSheetId="3">'5to Año'!$Q$15</definedName>
+    <definedName name="subj_5" localSheetId="3">'5to Año'!$R$15</definedName>
+    <definedName name="subj_6" localSheetId="3">'5to Año'!$S$15</definedName>
+    <definedName name="subj_7" localSheetId="3">'5to Año'!$T$15</definedName>
+    <definedName name="subj_8" localSheetId="3">'5to Año'!$U$15</definedName>
+    <definedName name="subj_9" localSheetId="3">'5to Año'!$V$15</definedName>
+    <definedName name="subj_10" localSheetId="3">'5to Año'!$W$15</definedName>
+    <definedName name="subj_11" localSheetId="3">'5to Año'!$X$15</definedName>
+    <definedName name="subj_12" localSheetId="3">'5to Año'!$Y$15</definedName>
+    <definedName name="std_num_1" localSheetId="3">'5to Año'!$A$16</definedName>
+    <definedName name="std_doc_1" localSheetId="3">'5to Año'!$B$16</definedName>
+    <definedName name="std_ln_1" localSheetId="3">'5to Año'!$D$16</definedName>
+    <definedName name="std_fn_1" localSheetId="3">'5to Año'!$F$16</definedName>
+    <definedName name="std_bp_1" localSheetId="3">'5to Año'!$H$16</definedName>
+    <definedName name="std_ef_1" localSheetId="3">'5to Año'!$I$16</definedName>
+    <definedName name="std_sx_1" localSheetId="3">'5to Año'!$J$16</definedName>
+    <definedName name="std_bd_1" localSheetId="3">'5to Año'!$K$16</definedName>
+    <definedName name="std_bm_1" localSheetId="3">'5to Año'!$L$16</definedName>
+    <definedName name="std_by_1" localSheetId="3">'5to Año'!$M$16</definedName>
+    <definedName name="grade_1_1" localSheetId="3">'5to Año'!$N$16</definedName>
+    <definedName name="grade_2_1" localSheetId="3">'5to Año'!$O$16</definedName>
+    <definedName name="grade_3_1" localSheetId="3">'5to Año'!$P$16</definedName>
+    <definedName name="grade_4_1" localSheetId="3">'5to Año'!$Q$16</definedName>
+    <definedName name="grade_5_1" localSheetId="3">'5to Año'!$R$16</definedName>
+    <definedName name="grade_6_1" localSheetId="3">'5to Año'!$S$16</definedName>
+    <definedName name="grade_7_1" localSheetId="3">'5to Año'!$T$16</definedName>
+    <definedName name="grade_8_1" localSheetId="3">'5to Año'!$U$16</definedName>
+    <definedName name="grade_9_1" localSheetId="3">'5to Año'!$V$16</definedName>
+    <definedName name="grade_10_1" localSheetId="3">'5to Año'!$W$16</definedName>
+    <definedName name="grade_11_1" localSheetId="3">'5to Año'!$X$16</definedName>
+    <definedName name="grade_12_1" localSheetId="3">'5to Año'!$Y$16</definedName>
+    <definedName name="std_part_1" localSheetId="3">'5to Año'!$Z$16</definedName>
+    <definedName name="std_num_2" localSheetId="3">'5to Año'!$A$17</definedName>
+    <definedName name="std_doc_2" localSheetId="3">'5to Año'!$B$17</definedName>
+    <definedName name="std_ln_2" localSheetId="3">'5to Año'!$D$17</definedName>
+    <definedName name="std_fn_2" localSheetId="3">'5to Año'!$F$17</definedName>
+    <definedName name="std_bp_2" localSheetId="3">'5to Año'!$H$17</definedName>
+    <definedName name="std_ef_2" localSheetId="3">'5to Año'!$I$17</definedName>
+    <definedName name="std_sx_2" localSheetId="3">'5to Año'!$J$17</definedName>
+    <definedName name="std_bd_2" localSheetId="3">'5to Año'!$K$17</definedName>
+    <definedName name="std_bm_2" localSheetId="3">'5to Año'!$L$17</definedName>
+    <definedName name="std_by_2" localSheetId="3">'5to Año'!$M$17</definedName>
+    <definedName name="grade_1_2" localSheetId="3">'5to Año'!$N$17</definedName>
+    <definedName name="grade_2_2" localSheetId="3">'5to Año'!$O$17</definedName>
+    <definedName name="grade_3_2" localSheetId="3">'5to Año'!$P$17</definedName>
+    <definedName name="grade_4_2" localSheetId="3">'5to Año'!$Q$17</definedName>
+    <definedName name="grade_5_2" localSheetId="3">'5to Año'!$R$17</definedName>
+    <definedName name="grade_6_2" localSheetId="3">'5to Año'!$S$17</definedName>
+    <definedName name="grade_7_2" localSheetId="3">'5to Año'!$T$17</definedName>
+    <definedName name="grade_8_2" localSheetId="3">'5to Año'!$U$17</definedName>
+    <definedName name="grade_9_2" localSheetId="3">'5to Año'!$V$17</definedName>
+    <definedName name="grade_10_2" localSheetId="3">'5to Año'!$W$17</definedName>
+    <definedName name="grade_11_2" localSheetId="3">'5to Año'!$X$17</definedName>
+    <definedName name="grade_12_2" localSheetId="3">'5to Año'!$Y$17</definedName>
+    <definedName name="std_part_2" localSheetId="3">'5to Año'!$Z$17</definedName>
+    <definedName name="std_num_3" localSheetId="3">'5to Año'!$A$18</definedName>
+    <definedName name="std_doc_3" localSheetId="3">'5to Año'!$B$18</definedName>
+    <definedName name="std_ln_3" localSheetId="3">'5to Año'!$D$18</definedName>
+    <definedName name="std_fn_3" localSheetId="3">'5to Año'!$F$18</definedName>
+    <definedName name="std_bp_3" localSheetId="3">'5to Año'!$H$18</definedName>
+    <definedName name="std_ef_3" localSheetId="3">'5to Año'!$I$18</definedName>
+    <definedName name="std_sx_3" localSheetId="3">'5to Año'!$J$18</definedName>
+    <definedName name="std_bd_3" localSheetId="3">'5to Año'!$K$18</definedName>
+    <definedName name="std_bm_3" localSheetId="3">'5to Año'!$L$18</definedName>
+    <definedName name="std_by_3" localSheetId="3">'5to Año'!$M$18</definedName>
+    <definedName name="grade_1_3" localSheetId="3">'5to Año'!$N$18</definedName>
+    <definedName name="grade_2_3" localSheetId="3">'5to Año'!$O$18</definedName>
+    <definedName name="grade_3_3" localSheetId="3">'5to Año'!$P$18</definedName>
+    <definedName name="grade_4_3" localSheetId="3">'5to Año'!$Q$18</definedName>
+    <definedName name="grade_5_3" localSheetId="3">'5to Año'!$R$18</definedName>
+    <definedName name="grade_6_3" localSheetId="3">'5to Año'!$S$18</definedName>
+    <definedName name="grade_7_3" localSheetId="3">'5to Año'!$T$18</definedName>
+    <definedName name="grade_8_3" localSheetId="3">'5to Año'!$U$18</definedName>
+    <definedName name="grade_9_3" localSheetId="3">'5to Año'!$V$18</definedName>
+    <definedName name="grade_10_3" localSheetId="3">'5to Año'!$W$18</definedName>
+    <definedName name="grade_11_3" localSheetId="3">'5to Año'!$X$18</definedName>
+    <definedName name="grade_12_3" localSheetId="3">'5to Año'!$Y$18</definedName>
+    <definedName name="std_part_3" localSheetId="3">'5to Año'!$Z$18</definedName>
+    <definedName name="std_num_4" localSheetId="3">'5to Año'!$A$19</definedName>
+    <definedName name="std_doc_4" localSheetId="3">'5to Año'!$B$19</definedName>
+    <definedName name="std_ln_4" localSheetId="3">'5to Año'!$D$19</definedName>
+    <definedName name="std_fn_4" localSheetId="3">'5to Año'!$F$19</definedName>
+    <definedName name="std_bp_4" localSheetId="3">'5to Año'!$H$19</definedName>
+    <definedName name="std_ef_4" localSheetId="3">'5to Año'!$I$19</definedName>
+    <definedName name="std_sx_4" localSheetId="3">'5to Año'!$J$19</definedName>
+    <definedName name="std_bd_4" localSheetId="3">'5to Año'!$K$19</definedName>
+    <definedName name="std_bm_4" localSheetId="3">'5to Año'!$L$19</definedName>
+    <definedName name="std_by_4" localSheetId="3">'5to Año'!$M$19</definedName>
+    <definedName name="grade_1_4" localSheetId="3">'5to Año'!$N$19</definedName>
+    <definedName name="grade_2_4" localSheetId="3">'5to Año'!$O$19</definedName>
+    <definedName name="grade_3_4" localSheetId="3">'5to Año'!$P$19</definedName>
+    <definedName name="grade_4_4" localSheetId="3">'5to Año'!$Q$19</definedName>
+    <definedName name="grade_5_4" localSheetId="3">'5to Año'!$R$19</definedName>
+    <definedName name="grade_6_4" localSheetId="3">'5to Año'!$S$19</definedName>
+    <definedName name="grade_7_4" localSheetId="3">'5to Año'!$T$19</definedName>
+    <definedName name="grade_8_4" localSheetId="3">'5to Año'!$U$19</definedName>
+    <definedName name="grade_9_4" localSheetId="3">'5to Año'!$V$19</definedName>
+    <definedName name="grade_10_4" localSheetId="3">'5to Año'!$W$19</definedName>
+    <definedName name="grade_11_4" localSheetId="3">'5to Año'!$X$19</definedName>
+    <definedName name="grade_12_4" localSheetId="3">'5to Año'!$Y$19</definedName>
+    <definedName name="std_part_4" localSheetId="3">'5to Año'!$Z$19</definedName>
+    <definedName name="std_num_5" localSheetId="3">'5to Año'!$A$20</definedName>
+    <definedName name="std_doc_5" localSheetId="3">'5to Año'!$B$20</definedName>
+    <definedName name="std_ln_5" localSheetId="3">'5to Año'!$D$20</definedName>
+    <definedName name="std_fn_5" localSheetId="3">'5to Año'!$F$20</definedName>
+    <definedName name="std_bp_5" localSheetId="3">'5to Año'!$H$20</definedName>
+    <definedName name="std_ef_5" localSheetId="3">'5to Año'!$I$20</definedName>
+    <definedName name="std_sx_5" localSheetId="3">'5to Año'!$J$20</definedName>
+    <definedName name="std_bd_5" localSheetId="3">'5to Año'!$K$20</definedName>
+    <definedName name="std_bm_5" localSheetId="3">'5to Año'!$L$20</definedName>
+    <definedName name="std_by_5" localSheetId="3">'5to Año'!$M$20</definedName>
+    <definedName name="grade_1_5" localSheetId="3">'5to Año'!$N$20</definedName>
+    <definedName name="grade_2_5" localSheetId="3">'5to Año'!$O$20</definedName>
+    <definedName name="grade_3_5" localSheetId="3">'5to Año'!$P$20</definedName>
+    <definedName name="grade_4_5" localSheetId="3">'5to Año'!$Q$20</definedName>
+    <definedName name="grade_5_5" localSheetId="3">'5to Año'!$R$20</definedName>
+    <definedName name="grade_6_5" localSheetId="3">'5to Año'!$S$20</definedName>
+    <definedName name="grade_7_5" localSheetId="3">'5to Año'!$T$20</definedName>
+    <definedName name="grade_8_5" localSheetId="3">'5to Año'!$U$20</definedName>
+    <definedName name="grade_9_5" localSheetId="3">'5to Año'!$V$20</definedName>
+    <definedName name="grade_10_5" localSheetId="3">'5to Año'!$W$20</definedName>
+    <definedName name="grade_11_5" localSheetId="3">'5to Año'!$X$20</definedName>
+    <definedName name="grade_12_5" localSheetId="3">'5to Año'!$Y$20</definedName>
+    <definedName name="std_part_5" localSheetId="3">'5to Año'!$Z$20</definedName>
+    <definedName name="std_num_6" localSheetId="3">'5to Año'!$A$21</definedName>
+    <definedName name="std_doc_6" localSheetId="3">'5to Año'!$B$21</definedName>
+    <definedName name="std_ln_6" localSheetId="3">'5to Año'!$D$21</definedName>
+    <definedName name="std_fn_6" localSheetId="3">'5to Año'!$F$21</definedName>
+    <definedName name="std_bp_6" localSheetId="3">'5to Año'!$H$21</definedName>
+    <definedName name="std_ef_6" localSheetId="3">'5to Año'!$I$21</definedName>
+    <definedName name="std_sx_6" localSheetId="3">'5to Año'!$J$21</definedName>
+    <definedName name="std_bd_6" localSheetId="3">'5to Año'!$K$21</definedName>
+    <definedName name="std_bm_6" localSheetId="3">'5to Año'!$L$21</definedName>
+    <definedName name="std_by_6" localSheetId="3">'5to Año'!$M$21</definedName>
+    <definedName name="grade_1_6" localSheetId="3">'5to Año'!$N$21</definedName>
+    <definedName name="grade_2_6" localSheetId="3">'5to Año'!$O$21</definedName>
+    <definedName name="grade_3_6" localSheetId="3">'5to Año'!$P$21</definedName>
+    <definedName name="grade_4_6" localSheetId="3">'5to Año'!$Q$21</definedName>
+    <definedName name="grade_5_6" localSheetId="3">'5to Año'!$R$21</definedName>
+    <definedName name="grade_6_6" localSheetId="3">'5to Año'!$S$21</definedName>
+    <definedName name="grade_7_6" localSheetId="3">'5to Año'!$T$21</definedName>
+    <definedName name="grade_8_6" localSheetId="3">'5to Año'!$U$21</definedName>
+    <definedName name="grade_9_6" localSheetId="3">'5to Año'!$V$21</definedName>
+    <definedName name="grade_10_6" localSheetId="3">'5to Año'!$W$21</definedName>
+    <definedName name="grade_11_6" localSheetId="3">'5to Año'!$X$21</definedName>
+    <definedName name="grade_12_6" localSheetId="3">'5to Año'!$Y$21</definedName>
+    <definedName name="std_part_6" localSheetId="3">'5to Año'!$Z$21</definedName>
+    <definedName name="std_num_7" localSheetId="3">'5to Año'!$A$22</definedName>
+    <definedName name="std_doc_7" localSheetId="3">'5to Año'!$B$22</definedName>
+    <definedName name="std_ln_7" localSheetId="3">'5to Año'!$D$22</definedName>
+    <definedName name="std_fn_7" localSheetId="3">'5to Año'!$F$22</definedName>
+    <definedName name="std_bp_7" localSheetId="3">'5to Año'!$H$22</definedName>
+    <definedName name="std_ef_7" localSheetId="3">'5to Año'!$I$22</definedName>
+    <definedName name="std_sx_7" localSheetId="3">'5to Año'!$J$22</definedName>
+    <definedName name="std_bd_7" localSheetId="3">'5to Año'!$K$22</definedName>
+    <definedName name="std_bm_7" localSheetId="3">'5to Año'!$L$22</definedName>
+    <definedName name="std_by_7" localSheetId="3">'5to Año'!$M$22</definedName>
+    <definedName name="grade_1_7" localSheetId="3">'5to Año'!$N$22</definedName>
+    <definedName name="grade_2_7" localSheetId="3">'5to Año'!$O$22</definedName>
+    <definedName name="grade_3_7" localSheetId="3">'5to Año'!$P$22</definedName>
+    <definedName name="grade_4_7" localSheetId="3">'5to Año'!$Q$22</definedName>
+    <definedName name="grade_5_7" localSheetId="3">'5to Año'!$R$22</definedName>
+    <definedName name="grade_6_7" localSheetId="3">'5to Año'!$S$22</definedName>
+    <definedName name="grade_7_7" localSheetId="3">'5to Año'!$T$22</definedName>
+    <definedName name="grade_8_7" localSheetId="3">'5to Año'!$U$22</definedName>
+    <definedName name="grade_9_7" localSheetId="3">'5to Año'!$V$22</definedName>
+    <definedName name="grade_10_7" localSheetId="3">'5to Año'!$W$22</definedName>
+    <definedName name="grade_11_7" localSheetId="3">'5to Año'!$X$22</definedName>
+    <definedName name="grade_12_7" localSheetId="3">'5to Año'!$Y$22</definedName>
+    <definedName name="std_part_7" localSheetId="3">'5to Año'!$Z$22</definedName>
+    <definedName name="std_num_8" localSheetId="3">'5to Año'!$A$23</definedName>
+    <definedName name="std_doc_8" localSheetId="3">'5to Año'!$B$23</definedName>
+    <definedName name="std_ln_8" localSheetId="3">'5to Año'!$D$23</definedName>
+    <definedName name="std_fn_8" localSheetId="3">'5to Año'!$F$23</definedName>
+    <definedName name="std_bp_8" localSheetId="3">'5to Año'!$H$23</definedName>
+    <definedName name="std_ef_8" localSheetId="3">'5to Año'!$I$23</definedName>
+    <definedName name="std_sx_8" localSheetId="3">'5to Año'!$J$23</definedName>
+    <definedName name="std_bd_8" localSheetId="3">'5to Año'!$K$23</definedName>
+    <definedName name="std_bm_8" localSheetId="3">'5to Año'!$L$23</definedName>
+    <definedName name="std_by_8" localSheetId="3">'5to Año'!$M$23</definedName>
+    <definedName name="grade_1_8" localSheetId="3">'5to Año'!$N$23</definedName>
+    <definedName name="grade_2_8" localSheetId="3">'5to Año'!$O$23</definedName>
+    <definedName name="grade_3_8" localSheetId="3">'5to Año'!$P$23</definedName>
+    <definedName name="grade_4_8" localSheetId="3">'5to Año'!$Q$23</definedName>
+    <definedName name="grade_5_8" localSheetId="3">'5to Año'!$R$23</definedName>
+    <definedName name="grade_6_8" localSheetId="3">'5to Año'!$S$23</definedName>
+    <definedName name="grade_7_8" localSheetId="3">'5to Año'!$T$23</definedName>
+    <definedName name="grade_8_8" localSheetId="3">'5to Año'!$U$23</definedName>
+    <definedName name="grade_9_8" localSheetId="3">'5to Año'!$V$23</definedName>
+    <definedName name="grade_10_8" localSheetId="3">'5to Año'!$W$23</definedName>
+    <definedName name="grade_11_8" localSheetId="3">'5to Año'!$X$23</definedName>
+    <definedName name="grade_12_8" localSheetId="3">'5to Año'!$Y$23</definedName>
+    <definedName name="std_part_8" localSheetId="3">'5to Año'!$Z$23</definedName>
+    <definedName name="std_num_9" localSheetId="3">'5to Año'!$A$24</definedName>
+    <definedName name="std_doc_9" localSheetId="3">'5to Año'!$B$24</definedName>
+    <definedName name="std_ln_9" localSheetId="3">'5to Año'!$D$24</definedName>
+    <definedName name="std_fn_9" localSheetId="3">'5to Año'!$F$24</definedName>
+    <definedName name="std_bp_9" localSheetId="3">'5to Año'!$H$24</definedName>
+    <definedName name="std_ef_9" localSheetId="3">'5to Año'!$I$24</definedName>
+    <definedName name="std_sx_9" localSheetId="3">'5to Año'!$J$24</definedName>
+    <definedName name="std_bd_9" localSheetId="3">'5to Año'!$K$24</definedName>
+    <definedName name="std_bm_9" localSheetId="3">'5to Año'!$L$24</definedName>
+    <definedName name="std_by_9" localSheetId="3">'5to Año'!$M$24</definedName>
+    <definedName name="grade_1_9" localSheetId="3">'5to Año'!$N$24</definedName>
+    <definedName name="grade_2_9" localSheetId="3">'5to Año'!$O$24</definedName>
+    <definedName name="grade_3_9" localSheetId="3">'5to Año'!$P$24</definedName>
+    <definedName name="grade_4_9" localSheetId="3">'5to Año'!$Q$24</definedName>
+    <definedName name="grade_5_9" localSheetId="3">'5to Año'!$R$24</definedName>
+    <definedName name="grade_6_9" localSheetId="3">'5to Año'!$S$24</definedName>
+    <definedName name="grade_7_9" localSheetId="3">'5to Año'!$T$24</definedName>
+    <definedName name="grade_8_9" localSheetId="3">'5to Año'!$U$24</definedName>
+    <definedName name="grade_9_9" localSheetId="3">'5to Año'!$V$24</definedName>
+    <definedName name="grade_10_9" localSheetId="3">'5to Año'!$W$24</definedName>
+    <definedName name="grade_11_9" localSheetId="3">'5to Año'!$X$24</definedName>
+    <definedName name="grade_12_9" localSheetId="3">'5to Año'!$Y$24</definedName>
+    <definedName name="std_part_9" localSheetId="3">'5to Año'!$Z$24</definedName>
+    <definedName name="std_num_10" localSheetId="3">'5to Año'!$A$25</definedName>
+    <definedName name="std_doc_10" localSheetId="3">'5to Año'!$B$25</definedName>
+    <definedName name="std_ln_10" localSheetId="3">'5to Año'!$D$25</definedName>
+    <definedName name="std_fn_10" localSheetId="3">'5to Año'!$F$25</definedName>
+    <definedName name="std_bp_10" localSheetId="3">'5to Año'!$H$25</definedName>
+    <definedName name="std_ef_10" localSheetId="3">'5to Año'!$I$25</definedName>
+    <definedName name="std_sx_10" localSheetId="3">'5to Año'!$J$25</definedName>
+    <definedName name="std_bd_10" localSheetId="3">'5to Año'!$K$25</definedName>
+    <definedName name="std_bm_10" localSheetId="3">'5to Año'!$L$25</definedName>
+    <definedName name="std_by_10" localSheetId="3">'5to Año'!$M$25</definedName>
+    <definedName name="grade_1_10" localSheetId="3">'5to Año'!$N$25</definedName>
+    <definedName name="grade_2_10" localSheetId="3">'5to Año'!$O$25</definedName>
+    <definedName name="grade_3_10" localSheetId="3">'5to Año'!$P$25</definedName>
+    <definedName name="grade_4_10" localSheetId="3">'5to Año'!$Q$25</definedName>
+    <definedName name="grade_5_10" localSheetId="3">'5to Año'!$R$25</definedName>
+    <definedName name="grade_6_10" localSheetId="3">'5to Año'!$S$25</definedName>
+    <definedName name="grade_7_10" localSheetId="3">'5to Año'!$T$25</definedName>
+    <definedName name="grade_8_10" localSheetId="3">'5to Año'!$U$25</definedName>
+    <definedName name="grade_9_10" localSheetId="3">'5to Año'!$V$25</definedName>
+    <definedName name="grade_10_10" localSheetId="3">'5to Año'!$W$25</definedName>
+    <definedName name="grade_11_10" localSheetId="3">'5to Año'!$X$25</definedName>
+    <definedName name="grade_12_10" localSheetId="3">'5to Año'!$Y$25</definedName>
+    <definedName name="std_part_10" localSheetId="3">'5to Año'!$Z$25</definedName>
+    <definedName name="std_num_11" localSheetId="3">'5to Año'!$A$26</definedName>
+    <definedName name="std_doc_11" localSheetId="3">'5to Año'!$B$26</definedName>
+    <definedName name="std_ln_11" localSheetId="3">'5to Año'!$D$26</definedName>
+    <definedName name="std_fn_11" localSheetId="3">'5to Año'!$F$26</definedName>
+    <definedName name="std_bp_11" localSheetId="3">'5to Año'!$H$26</definedName>
+    <definedName name="std_ef_11" localSheetId="3">'5to Año'!$I$26</definedName>
+    <definedName name="std_sx_11" localSheetId="3">'5to Año'!$J$26</definedName>
+    <definedName name="std_bd_11" localSheetId="3">'5to Año'!$K$26</definedName>
+    <definedName name="std_bm_11" localSheetId="3">'5to Año'!$L$26</definedName>
+    <definedName name="std_by_11" localSheetId="3">'5to Año'!$M$26</definedName>
+    <definedName name="grade_1_11" localSheetId="3">'5to Año'!$N$26</definedName>
+    <definedName name="grade_2_11" localSheetId="3">'5to Año'!$O$26</definedName>
+    <definedName name="grade_3_11" localSheetId="3">'5to Año'!$P$26</definedName>
+    <definedName name="grade_4_11" localSheetId="3">'5to Año'!$Q$26</definedName>
+    <definedName name="grade_5_11" localSheetId="3">'5to Año'!$R$26</definedName>
+    <definedName name="grade_6_11" localSheetId="3">'5to Año'!$S$26</definedName>
+    <definedName name="grade_7_11" localSheetId="3">'5to Año'!$T$26</definedName>
+    <definedName name="grade_8_11" localSheetId="3">'5to Año'!$U$26</definedName>
+    <definedName name="grade_9_11" localSheetId="3">'5to Año'!$V$26</definedName>
+    <definedName name="grade_10_11" localSheetId="3">'5to Año'!$W$26</definedName>
+    <definedName name="grade_11_11" localSheetId="3">'5to Año'!$X$26</definedName>
+    <definedName name="grade_12_11" localSheetId="3">'5to Año'!$Y$26</definedName>
+    <definedName name="std_part_11" localSheetId="3">'5to Año'!$Z$26</definedName>
+    <definedName name="std_num_12" localSheetId="3">'5to Año'!$A$27</definedName>
+    <definedName name="std_doc_12" localSheetId="3">'5to Año'!$B$27</definedName>
+    <definedName name="std_ln_12" localSheetId="3">'5to Año'!$D$27</definedName>
+    <definedName name="std_fn_12" localSheetId="3">'5to Año'!$F$27</definedName>
+    <definedName name="std_bp_12" localSheetId="3">'5to Año'!$H$27</definedName>
+    <definedName name="std_ef_12" localSheetId="3">'5to Año'!$I$27</definedName>
+    <definedName name="std_sx_12" localSheetId="3">'5to Año'!$J$27</definedName>
+    <definedName name="std_bd_12" localSheetId="3">'5to Año'!$K$27</definedName>
+    <definedName name="std_bm_12" localSheetId="3">'5to Año'!$L$27</definedName>
+    <definedName name="std_by_12" localSheetId="3">'5to Año'!$M$27</definedName>
+    <definedName name="grade_1_12" localSheetId="3">'5to Año'!$N$27</definedName>
+    <definedName name="grade_2_12" localSheetId="3">'5to Año'!$O$27</definedName>
+    <definedName name="grade_3_12" localSheetId="3">'5to Año'!$P$27</definedName>
+    <definedName name="grade_4_12" localSheetId="3">'5to Año'!$Q$27</definedName>
+    <definedName name="grade_5_12" localSheetId="3">'5to Año'!$R$27</definedName>
+    <definedName name="grade_6_12" localSheetId="3">'5to Año'!$S$27</definedName>
+    <definedName name="grade_7_12" localSheetId="3">'5to Año'!$T$27</definedName>
+    <definedName name="grade_8_12" localSheetId="3">'5to Año'!$U$27</definedName>
+    <definedName name="grade_9_12" localSheetId="3">'5to Año'!$V$27</definedName>
+    <definedName name="grade_10_12" localSheetId="3">'5to Año'!$W$27</definedName>
+    <definedName name="grade_11_12" localSheetId="3">'5to Año'!$X$27</definedName>
+    <definedName name="grade_12_12" localSheetId="3">'5to Año'!$Y$27</definedName>
+    <definedName name="std_part_12" localSheetId="3">'5to Año'!$Z$27</definedName>
+    <definedName name="std_num_13" localSheetId="3">'5to Año'!$A$28</definedName>
+    <definedName name="std_doc_13" localSheetId="3">'5to Año'!$B$28</definedName>
+    <definedName name="std_ln_13" localSheetId="3">'5to Año'!$D$28</definedName>
+    <definedName name="std_fn_13" localSheetId="3">'5to Año'!$F$28</definedName>
+    <definedName name="std_bp_13" localSheetId="3">'5to Año'!$H$28</definedName>
+    <definedName name="std_ef_13" localSheetId="3">'5to Año'!$I$28</definedName>
+    <definedName name="std_sx_13" localSheetId="3">'5to Año'!$J$28</definedName>
+    <definedName name="std_bd_13" localSheetId="3">'5to Año'!$K$28</definedName>
+    <definedName name="std_bm_13" localSheetId="3">'5to Año'!$L$28</definedName>
+    <definedName name="std_by_13" localSheetId="3">'5to Año'!$M$28</definedName>
+    <definedName name="grade_1_13" localSheetId="3">'5to Año'!$N$28</definedName>
+    <definedName name="grade_2_13" localSheetId="3">'5to Año'!$O$28</definedName>
+    <definedName name="grade_3_13" localSheetId="3">'5to Año'!$P$28</definedName>
+    <definedName name="grade_4_13" localSheetId="3">'5to Año'!$Q$28</definedName>
+    <definedName name="grade_5_13" localSheetId="3">'5to Año'!$R$28</definedName>
+    <definedName name="grade_6_13" localSheetId="3">'5to Año'!$S$28</definedName>
+    <definedName name="grade_7_13" localSheetId="3">'5to Año'!$T$28</definedName>
+    <definedName name="grade_8_13" localSheetId="3">'5to Año'!$U$28</definedName>
+    <definedName name="grade_9_13" localSheetId="3">'5to Año'!$V$28</definedName>
+    <definedName name="grade_10_13" localSheetId="3">'5to Año'!$W$28</definedName>
+    <definedName name="grade_11_13" localSheetId="3">'5to Año'!$X$28</definedName>
+    <definedName name="grade_12_13" localSheetId="3">'5to Año'!$Y$28</definedName>
+    <definedName name="std_part_13" localSheetId="3">'5to Año'!$Z$28</definedName>
+    <definedName name="std_num_14" localSheetId="3">'5to Año'!$A$29</definedName>
+    <definedName name="std_doc_14" localSheetId="3">'5to Año'!$B$29</definedName>
+    <definedName name="std_ln_14" localSheetId="3">'5to Año'!$D$29</definedName>
+    <definedName name="std_fn_14" localSheetId="3">'5to Año'!$F$29</definedName>
+    <definedName name="std_bp_14" localSheetId="3">'5to Año'!$H$29</definedName>
+    <definedName name="std_ef_14" localSheetId="3">'5to Año'!$I$29</definedName>
+    <definedName name="std_sx_14" localSheetId="3">'5to Año'!$J$29</definedName>
+    <definedName name="std_bd_14" localSheetId="3">'5to Año'!$K$29</definedName>
+    <definedName name="std_bm_14" localSheetId="3">'5to Año'!$L$29</definedName>
+    <definedName name="std_by_14" localSheetId="3">'5to Año'!$M$29</definedName>
+    <definedName name="grade_1_14" localSheetId="3">'5to Año'!$N$29</definedName>
+    <definedName name="grade_2_14" localSheetId="3">'5to Año'!$O$29</definedName>
+    <definedName name="grade_3_14" localSheetId="3">'5to Año'!$P$29</definedName>
+    <definedName name="grade_4_14" localSheetId="3">'5to Año'!$Q$29</definedName>
+    <definedName name="grade_5_14" localSheetId="3">'5to Año'!$R$29</definedName>
+    <definedName name="grade_6_14" localSheetId="3">'5to Año'!$S$29</definedName>
+    <definedName name="grade_7_14" localSheetId="3">'5to Año'!$T$29</definedName>
+    <definedName name="grade_8_14" localSheetId="3">'5to Año'!$U$29</definedName>
+    <definedName name="grade_9_14" localSheetId="3">'5to Año'!$V$29</definedName>
+    <definedName name="grade_10_14" localSheetId="3">'5to Año'!$W$29</definedName>
+    <definedName name="grade_11_14" localSheetId="3">'5to Año'!$X$29</definedName>
+    <definedName name="grade_12_14" localSheetId="3">'5to Año'!$Y$29</definedName>
+    <definedName name="std_part_14" localSheetId="3">'5to Año'!$Z$29</definedName>
+    <definedName name="std_num_15" localSheetId="3">'5to Año'!$A$30</definedName>
+    <definedName name="std_doc_15" localSheetId="3">'5to Año'!$B$30</definedName>
+    <definedName name="std_ln_15" localSheetId="3">'5to Año'!$D$30</definedName>
+    <definedName name="std_fn_15" localSheetId="3">'5to Año'!$F$30</definedName>
+    <definedName name="std_bp_15" localSheetId="3">'5to Año'!$H$30</definedName>
+    <definedName name="std_ef_15" localSheetId="3">'5to Año'!$I$30</definedName>
+    <definedName name="std_sx_15" localSheetId="3">'5to Año'!$J$30</definedName>
+    <definedName name="std_bd_15" localSheetId="3">'5to Año'!$K$30</definedName>
+    <definedName name="std_bm_15" localSheetId="3">'5to Año'!$L$30</definedName>
+    <definedName name="std_by_15" localSheetId="3">'5to Año'!$M$30</definedName>
+    <definedName name="grade_1_15" localSheetId="3">'5to Año'!$N$30</definedName>
+    <definedName name="grade_2_15" localSheetId="3">'5to Año'!$O$30</definedName>
+    <definedName name="grade_3_15" localSheetId="3">'5to Año'!$P$30</definedName>
+    <definedName name="grade_4_15" localSheetId="3">'5to Año'!$Q$30</definedName>
+    <definedName name="grade_5_15" localSheetId="3">'5to Año'!$R$30</definedName>
+    <definedName name="grade_6_15" localSheetId="3">'5to Año'!$S$30</definedName>
+    <definedName name="grade_7_15" localSheetId="3">'5to Año'!$T$30</definedName>
+    <definedName name="grade_8_15" localSheetId="3">'5to Año'!$U$30</definedName>
+    <definedName name="grade_9_15" localSheetId="3">'5to Año'!$V$30</definedName>
+    <definedName name="grade_10_15" localSheetId="3">'5to Año'!$W$30</definedName>
+    <definedName name="grade_11_15" localSheetId="3">'5to Año'!$X$30</definedName>
+    <definedName name="grade_12_15" localSheetId="3">'5to Año'!$Y$30</definedName>
+    <definedName name="std_part_15" localSheetId="3">'5to Año'!$Z$30</definedName>
+    <definedName name="std_num_16" localSheetId="3">'5to Año'!$A$31</definedName>
+    <definedName name="std_doc_16" localSheetId="3">'5to Año'!$B$31</definedName>
+    <definedName name="std_ln_16" localSheetId="3">'5to Año'!$D$31</definedName>
+    <definedName name="std_fn_16" localSheetId="3">'5to Año'!$F$31</definedName>
+    <definedName name="std_bp_16" localSheetId="3">'5to Año'!$H$31</definedName>
+    <definedName name="std_ef_16" localSheetId="3">'5to Año'!$I$31</definedName>
+    <definedName name="std_sx_16" localSheetId="3">'5to Año'!$J$31</definedName>
+    <definedName name="std_bd_16" localSheetId="3">'5to Año'!$K$31</definedName>
+    <definedName name="std_bm_16" localSheetId="3">'5to Año'!$L$31</definedName>
+    <definedName name="std_by_16" localSheetId="3">'5to Año'!$M$31</definedName>
+    <definedName name="grade_1_16" localSheetId="3">'5to Año'!$N$31</definedName>
+    <definedName name="grade_2_16" localSheetId="3">'5to Año'!$O$31</definedName>
+    <definedName name="grade_3_16" localSheetId="3">'5to Año'!$P$31</definedName>
+    <definedName name="grade_4_16" localSheetId="3">'5to Año'!$Q$31</definedName>
+    <definedName name="grade_5_16" localSheetId="3">'5to Año'!$R$31</definedName>
+    <definedName name="grade_6_16" localSheetId="3">'5to Año'!$S$31</definedName>
+    <definedName name="grade_7_16" localSheetId="3">'5to Año'!$T$31</definedName>
+    <definedName name="grade_8_16" localSheetId="3">'5to Año'!$U$31</definedName>
+    <definedName name="grade_9_16" localSheetId="3">'5to Año'!$V$31</definedName>
+    <definedName name="grade_10_16" localSheetId="3">'5to Año'!$W$31</definedName>
+    <definedName name="grade_11_16" localSheetId="3">'5to Año'!$X$31</definedName>
+    <definedName name="grade_12_16" localSheetId="3">'5to Año'!$Y$31</definedName>
+    <definedName name="std_part_16" localSheetId="3">'5to Año'!$Z$31</definedName>
+    <definedName name="std_num_17" localSheetId="3">'5to Año'!$A$32</definedName>
+    <definedName name="std_doc_17" localSheetId="3">'5to Año'!$B$32</definedName>
+    <definedName name="std_ln_17" localSheetId="3">'5to Año'!$D$32</definedName>
+    <definedName name="std_fn_17" localSheetId="3">'5to Año'!$F$32</definedName>
+    <definedName name="std_bp_17" localSheetId="3">'5to Año'!$H$32</definedName>
+    <definedName name="std_ef_17" localSheetId="3">'5to Año'!$I$32</definedName>
+    <definedName name="std_sx_17" localSheetId="3">'5to Año'!$J$32</definedName>
+    <definedName name="std_bd_17" localSheetId="3">'5to Año'!$K$32</definedName>
+    <definedName name="std_bm_17" localSheetId="3">'5to Año'!$L$32</definedName>
+    <definedName name="std_by_17" localSheetId="3">'5to Año'!$M$32</definedName>
+    <definedName name="grade_1_17" localSheetId="3">'5to Año'!$N$32</definedName>
+    <definedName name="grade_2_17" localSheetId="3">'5to Año'!$O$32</definedName>
+    <definedName name="grade_3_17" localSheetId="3">'5to Año'!$P$32</definedName>
+    <definedName name="grade_4_17" localSheetId="3">'5to Año'!$Q$32</definedName>
+    <definedName name="grade_5_17" localSheetId="3">'5to Año'!$R$32</definedName>
+    <definedName name="grade_6_17" localSheetId="3">'5to Año'!$S$32</definedName>
+    <definedName name="grade_7_17" localSheetId="3">'5to Año'!$T$32</definedName>
+    <definedName name="grade_8_17" localSheetId="3">'5to Año'!$U$32</definedName>
+    <definedName name="grade_9_17" localSheetId="3">'5to Año'!$V$32</definedName>
+    <definedName name="grade_10_17" localSheetId="3">'5to Año'!$W$32</definedName>
+    <definedName name="grade_11_17" localSheetId="3">'5to Año'!$X$32</definedName>
+    <definedName name="grade_12_17" localSheetId="3">'5to Año'!$Y$32</definedName>
+    <definedName name="std_part_17" localSheetId="3">'5to Año'!$Z$32</definedName>
+    <definedName name="std_num_18" localSheetId="3">'5to Año'!$A$33</definedName>
+    <definedName name="std_doc_18" localSheetId="3">'5to Año'!$B$33</definedName>
+    <definedName name="std_ln_18" localSheetId="3">'5to Año'!$D$33</definedName>
+    <definedName name="std_fn_18" localSheetId="3">'5to Año'!$F$33</definedName>
+    <definedName name="std_bp_18" localSheetId="3">'5to Año'!$H$33</definedName>
+    <definedName name="std_ef_18" localSheetId="3">'5to Año'!$I$33</definedName>
+    <definedName name="std_sx_18" localSheetId="3">'5to Año'!$J$33</definedName>
+    <definedName name="std_bd_18" localSheetId="3">'5to Año'!$K$33</definedName>
+    <definedName name="std_bm_18" localSheetId="3">'5to Año'!$L$33</definedName>
+    <definedName name="std_by_18" localSheetId="3">'5to Año'!$M$33</definedName>
+    <definedName name="grade_1_18" localSheetId="3">'5to Año'!$N$33</definedName>
+    <definedName name="grade_2_18" localSheetId="3">'5to Año'!$O$33</definedName>
+    <definedName name="grade_3_18" localSheetId="3">'5to Año'!$P$33</definedName>
+    <definedName name="grade_4_18" localSheetId="3">'5to Año'!$Q$33</definedName>
+    <definedName name="grade_5_18" localSheetId="3">'5to Año'!$R$33</definedName>
+    <definedName name="grade_6_18" localSheetId="3">'5to Año'!$S$33</definedName>
+    <definedName name="grade_7_18" localSheetId="3">'5to Año'!$T$33</definedName>
+    <definedName name="grade_8_18" localSheetId="3">'5to Año'!$U$33</definedName>
+    <definedName name="grade_9_18" localSheetId="3">'5to Año'!$V$33</definedName>
+    <definedName name="grade_10_18" localSheetId="3">'5to Año'!$W$33</definedName>
+    <definedName name="grade_11_18" localSheetId="3">'5to Año'!$X$33</definedName>
+    <definedName name="grade_12_18" localSheetId="3">'5to Año'!$Y$33</definedName>
+    <definedName name="std_part_18" localSheetId="3">'5to Año'!$Z$33</definedName>
+    <definedName name="std_num_19" localSheetId="3">'5to Año'!$A$34</definedName>
+    <definedName name="std_doc_19" localSheetId="3">'5to Año'!$B$34</definedName>
+    <definedName name="std_ln_19" localSheetId="3">'5to Año'!$D$34</definedName>
+    <definedName name="std_fn_19" localSheetId="3">'5to Año'!$F$34</definedName>
+    <definedName name="std_bp_19" localSheetId="3">'5to Año'!$H$34</definedName>
+    <definedName name="std_ef_19" localSheetId="3">'5to Año'!$I$34</definedName>
+    <definedName name="std_sx_19" localSheetId="3">'5to Año'!$J$34</definedName>
+    <definedName name="std_bd_19" localSheetId="3">'5to Año'!$K$34</definedName>
+    <definedName name="std_bm_19" localSheetId="3">'5to Año'!$L$34</definedName>
+    <definedName name="std_by_19" localSheetId="3">'5to Año'!$M$34</definedName>
+    <definedName name="grade_1_19" localSheetId="3">'5to Año'!$N$34</definedName>
+    <definedName name="grade_2_19" localSheetId="3">'5to Año'!$O$34</definedName>
+    <definedName name="grade_3_19" localSheetId="3">'5to Año'!$P$34</definedName>
+    <definedName name="grade_4_19" localSheetId="3">'5to Año'!$Q$34</definedName>
+    <definedName name="grade_5_19" localSheetId="3">'5to Año'!$R$34</definedName>
+    <definedName name="grade_6_19" localSheetId="3">'5to Año'!$S$34</definedName>
+    <definedName name="grade_7_19" localSheetId="3">'5to Año'!$T$34</definedName>
+    <definedName name="grade_8_19" localSheetId="3">'5to Año'!$U$34</definedName>
+    <definedName name="grade_9_19" localSheetId="3">'5to Año'!$V$34</definedName>
+    <definedName name="grade_10_19" localSheetId="3">'5to Año'!$W$34</definedName>
+    <definedName name="grade_11_19" localSheetId="3">'5to Año'!$X$34</definedName>
+    <definedName name="grade_12_19" localSheetId="3">'5to Año'!$Y$34</definedName>
+    <definedName name="std_part_19" localSheetId="3">'5to Año'!$Z$34</definedName>
+    <definedName name="std_num_20" localSheetId="3">'5to Año'!$A$35</definedName>
+    <definedName name="std_doc_20" localSheetId="3">'5to Año'!$B$35</definedName>
+    <definedName name="std_ln_20" localSheetId="3">'5to Año'!$D$35</definedName>
+    <definedName name="std_fn_20" localSheetId="3">'5to Año'!$F$35</definedName>
+    <definedName name="std_bp_20" localSheetId="3">'5to Año'!$H$35</definedName>
+    <definedName name="std_ef_20" localSheetId="3">'5to Año'!$I$35</definedName>
+    <definedName name="std_sx_20" localSheetId="3">'5to Año'!$J$35</definedName>
+    <definedName name="std_bd_20" localSheetId="3">'5to Año'!$K$35</definedName>
+    <definedName name="std_bm_20" localSheetId="3">'5to Año'!$L$35</definedName>
+    <definedName name="std_by_20" localSheetId="3">'5to Año'!$M$35</definedName>
+    <definedName name="grade_1_20" localSheetId="3">'5to Año'!$N$35</definedName>
+    <definedName name="grade_2_20" localSheetId="3">'5to Año'!$O$35</definedName>
+    <definedName name="grade_3_20" localSheetId="3">'5to Año'!$P$35</definedName>
+    <definedName name="grade_4_20" localSheetId="3">'5to Año'!$Q$35</definedName>
+    <definedName name="grade_5_20" localSheetId="3">'5to Año'!$R$35</definedName>
+    <definedName name="grade_6_20" localSheetId="3">'5to Año'!$S$35</definedName>
+    <definedName name="grade_7_20" localSheetId="3">'5to Año'!$T$35</definedName>
+    <definedName name="grade_8_20" localSheetId="3">'5to Año'!$U$35</definedName>
+    <definedName name="grade_9_20" localSheetId="3">'5to Año'!$V$35</definedName>
+    <definedName name="grade_10_20" localSheetId="3">'5to Año'!$W$35</definedName>
+    <definedName name="grade_11_20" localSheetId="3">'5to Año'!$X$35</definedName>
+    <definedName name="grade_12_20" localSheetId="3">'5to Año'!$Y$35</definedName>
+    <definedName name="std_part_20" localSheetId="3">'5to Año'!$Z$35</definedName>
+    <definedName name="std_num_21" localSheetId="3">'5to Año'!$A$36</definedName>
+    <definedName name="std_doc_21" localSheetId="3">'5to Año'!$B$36</definedName>
+    <definedName name="std_ln_21" localSheetId="3">'5to Año'!$D$36</definedName>
+    <definedName name="std_fn_21" localSheetId="3">'5to Año'!$F$36</definedName>
+    <definedName name="std_bp_21" localSheetId="3">'5to Año'!$H$36</definedName>
+    <definedName name="std_ef_21" localSheetId="3">'5to Año'!$I$36</definedName>
+    <definedName name="std_sx_21" localSheetId="3">'5to Año'!$J$36</definedName>
+    <definedName name="std_bd_21" localSheetId="3">'5to Año'!$K$36</definedName>
+    <definedName name="std_bm_21" localSheetId="3">'5to Año'!$L$36</definedName>
+    <definedName name="std_by_21" localSheetId="3">'5to Año'!$M$36</definedName>
+    <definedName name="grade_1_21" localSheetId="3">'5to Año'!$N$36</definedName>
+    <definedName name="grade_2_21" localSheetId="3">'5to Año'!$O$36</definedName>
+    <definedName name="grade_3_21" localSheetId="3">'5to Año'!$P$36</definedName>
+    <definedName name="grade_4_21" localSheetId="3">'5to Año'!$Q$36</definedName>
+    <definedName name="grade_5_21" localSheetId="3">'5to Año'!$R$36</definedName>
+    <definedName name="grade_6_21" localSheetId="3">'5to Año'!$S$36</definedName>
+    <definedName name="grade_7_21" localSheetId="3">'5to Año'!$T$36</definedName>
+    <definedName name="grade_8_21" localSheetId="3">'5to Año'!$U$36</definedName>
+    <definedName name="grade_9_21" localSheetId="3">'5to Año'!$V$36</definedName>
+    <definedName name="grade_10_21" localSheetId="3">'5to Año'!$W$36</definedName>
+    <definedName name="grade_11_21" localSheetId="3">'5to Año'!$X$36</definedName>
+    <definedName name="grade_12_21" localSheetId="3">'5to Año'!$Y$36</definedName>
+    <definedName name="std_part_21" localSheetId="3">'5to Año'!$Z$36</definedName>
+    <definedName name="std_num_22" localSheetId="3">'5to Año'!$A$37</definedName>
+    <definedName name="std_doc_22" localSheetId="3">'5to Año'!$B$37</definedName>
+    <definedName name="std_ln_22" localSheetId="3">'5to Año'!$D$37</definedName>
+    <definedName name="std_fn_22" localSheetId="3">'5to Año'!$F$37</definedName>
+    <definedName name="std_bp_22" localSheetId="3">'5to Año'!$H$37</definedName>
+    <definedName name="std_ef_22" localSheetId="3">'5to Año'!$I$37</definedName>
+    <definedName name="std_sx_22" localSheetId="3">'5to Año'!$J$37</definedName>
+    <definedName name="std_bd_22" localSheetId="3">'5to Año'!$K$37</definedName>
+    <definedName name="std_bm_22" localSheetId="3">'5to Año'!$L$37</definedName>
+    <definedName name="std_by_22" localSheetId="3">'5to Año'!$M$37</definedName>
+    <definedName name="grade_1_22" localSheetId="3">'5to Año'!$N$37</definedName>
+    <definedName name="grade_2_22" localSheetId="3">'5to Año'!$O$37</definedName>
+    <definedName name="grade_3_22" localSheetId="3">'5to Año'!$P$37</definedName>
+    <definedName name="grade_4_22" localSheetId="3">'5to Año'!$Q$37</definedName>
+    <definedName name="grade_5_22" localSheetId="3">'5to Año'!$R$37</definedName>
+    <definedName name="grade_6_22" localSheetId="3">'5to Año'!$S$37</definedName>
+    <definedName name="grade_7_22" localSheetId="3">'5to Año'!$T$37</definedName>
+    <definedName name="grade_8_22" localSheetId="3">'5to Año'!$U$37</definedName>
+    <definedName name="grade_9_22" localSheetId="3">'5to Año'!$V$37</definedName>
+    <definedName name="grade_10_22" localSheetId="3">'5to Año'!$W$37</definedName>
+    <definedName name="grade_11_22" localSheetId="3">'5to Año'!$X$37</definedName>
+    <definedName name="grade_12_22" localSheetId="3">'5to Año'!$Y$37</definedName>
+    <definedName name="std_part_22" localSheetId="3">'5to Año'!$Z$37</definedName>
+    <definedName name="std_num_23" localSheetId="3">'5to Año'!$A$38</definedName>
+    <definedName name="std_doc_23" localSheetId="3">'5to Año'!$B$38</definedName>
+    <definedName name="std_ln_23" localSheetId="3">'5to Año'!$D$38</definedName>
+    <definedName name="std_fn_23" localSheetId="3">'5to Año'!$F$38</definedName>
+    <definedName name="std_bp_23" localSheetId="3">'5to Año'!$H$38</definedName>
+    <definedName name="std_ef_23" localSheetId="3">'5to Año'!$I$38</definedName>
+    <definedName name="std_sx_23" localSheetId="3">'5to Año'!$J$38</definedName>
+    <definedName name="std_bd_23" localSheetId="3">'5to Año'!$K$38</definedName>
+    <definedName name="std_bm_23" localSheetId="3">'5to Año'!$L$38</definedName>
+    <definedName name="std_by_23" localSheetId="3">'5to Año'!$M$38</definedName>
+    <definedName name="grade_1_23" localSheetId="3">'5to Año'!$N$38</definedName>
+    <definedName name="grade_2_23" localSheetId="3">'5to Año'!$O$38</definedName>
+    <definedName name="grade_3_23" localSheetId="3">'5to Año'!$P$38</definedName>
+    <definedName name="grade_4_23" localSheetId="3">'5to Año'!$Q$38</definedName>
+    <definedName name="grade_5_23" localSheetId="3">'5to Año'!$R$38</definedName>
+    <definedName name="grade_6_23" localSheetId="3">'5to Año'!$S$38</definedName>
+    <definedName name="grade_7_23" localSheetId="3">'5to Año'!$T$38</definedName>
+    <definedName name="grade_8_23" localSheetId="3">'5to Año'!$U$38</definedName>
+    <definedName name="grade_9_23" localSheetId="3">'5to Año'!$V$38</definedName>
+    <definedName name="grade_10_23" localSheetId="3">'5to Año'!$W$38</definedName>
+    <definedName name="grade_11_23" localSheetId="3">'5to Año'!$X$38</definedName>
+    <definedName name="grade_12_23" localSheetId="3">'5to Año'!$Y$38</definedName>
+    <definedName name="std_part_23" localSheetId="3">'5to Año'!$Z$38</definedName>
+    <definedName name="std_num_24" localSheetId="3">'5to Año'!$A$39</definedName>
+    <definedName name="std_doc_24" localSheetId="3">'5to Año'!$B$39</definedName>
+    <definedName name="std_ln_24" localSheetId="3">'5to Año'!$D$39</definedName>
+    <definedName name="std_fn_24" localSheetId="3">'5to Año'!$F$39</definedName>
+    <definedName name="std_bp_24" localSheetId="3">'5to Año'!$H$39</definedName>
+    <definedName name="std_ef_24" localSheetId="3">'5to Año'!$I$39</definedName>
+    <definedName name="std_sx_24" localSheetId="3">'5to Año'!$J$39</definedName>
+    <definedName name="std_bd_24" localSheetId="3">'5to Año'!$K$39</definedName>
+    <definedName name="std_bm_24" localSheetId="3">'5to Año'!$L$39</definedName>
+    <definedName name="std_by_24" localSheetId="3">'5to Año'!$M$39</definedName>
+    <definedName name="grade_1_24" localSheetId="3">'5to Año'!$N$39</definedName>
+    <definedName name="grade_2_24" localSheetId="3">'5to Año'!$O$39</definedName>
+    <definedName name="grade_3_24" localSheetId="3">'5to Año'!$P$39</definedName>
+    <definedName name="grade_4_24" localSheetId="3">'5to Año'!$Q$39</definedName>
+    <definedName name="grade_5_24" localSheetId="3">'5to Año'!$R$39</definedName>
+    <definedName name="grade_6_24" localSheetId="3">'5to Año'!$S$39</definedName>
+    <definedName name="grade_7_24" localSheetId="3">'5to Año'!$T$39</definedName>
+    <definedName name="grade_8_24" localSheetId="3">'5to Año'!$U$39</definedName>
+    <definedName name="grade_9_24" localSheetId="3">'5to Año'!$V$39</definedName>
+    <definedName name="grade_10_24" localSheetId="3">'5to Año'!$W$39</definedName>
+    <definedName name="grade_11_24" localSheetId="3">'5to Año'!$X$39</definedName>
+    <definedName name="grade_12_24" localSheetId="3">'5to Año'!$Y$39</definedName>
+    <definedName name="std_part_24" localSheetId="3">'5to Año'!$Z$39</definedName>
+    <definedName name="std_num_25" localSheetId="3">'5to Año'!$A$40</definedName>
+    <definedName name="std_doc_25" localSheetId="3">'5to Año'!$B$40</definedName>
+    <definedName name="std_ln_25" localSheetId="3">'5to Año'!$D$40</definedName>
+    <definedName name="std_fn_25" localSheetId="3">'5to Año'!$F$40</definedName>
+    <definedName name="std_bp_25" localSheetId="3">'5to Año'!$H$40</definedName>
+    <definedName name="std_ef_25" localSheetId="3">'5to Año'!$I$40</definedName>
+    <definedName name="std_sx_25" localSheetId="3">'5to Año'!$J$40</definedName>
+    <definedName name="std_bd_25" localSheetId="3">'5to Año'!$K$40</definedName>
+    <definedName name="std_bm_25" localSheetId="3">'5to Año'!$L$40</definedName>
+    <definedName name="std_by_25" localSheetId="3">'5to Año'!$M$40</definedName>
+    <definedName name="grade_1_25" localSheetId="3">'5to Año'!$N$40</definedName>
+    <definedName name="grade_2_25" localSheetId="3">'5to Año'!$O$40</definedName>
+    <definedName name="grade_3_25" localSheetId="3">'5to Año'!$P$40</definedName>
+    <definedName name="grade_4_25" localSheetId="3">'5to Año'!$Q$40</definedName>
+    <definedName name="grade_5_25" localSheetId="3">'5to Año'!$R$40</definedName>
+    <definedName name="grade_6_25" localSheetId="3">'5to Año'!$S$40</definedName>
+    <definedName name="grade_7_25" localSheetId="3">'5to Año'!$T$40</definedName>
+    <definedName name="grade_8_25" localSheetId="3">'5to Año'!$U$40</definedName>
+    <definedName name="grade_9_25" localSheetId="3">'5to Año'!$V$40</definedName>
+    <definedName name="grade_10_25" localSheetId="3">'5to Año'!$W$40</definedName>
+    <definedName name="grade_11_25" localSheetId="3">'5to Año'!$X$40</definedName>
+    <definedName name="grade_12_25" localSheetId="3">'5to Año'!$Y$40</definedName>
+    <definedName name="std_part_25" localSheetId="3">'5to Año'!$Z$40</definedName>
+    <definedName name="std_num_26" localSheetId="3">'5to Año'!$A$41</definedName>
+    <definedName name="std_doc_26" localSheetId="3">'5to Año'!$B$41</definedName>
+    <definedName name="std_ln_26" localSheetId="3">'5to Año'!$D$41</definedName>
+    <definedName name="std_fn_26" localSheetId="3">'5to Año'!$F$41</definedName>
+    <definedName name="std_bp_26" localSheetId="3">'5to Año'!$H$41</definedName>
+    <definedName name="std_ef_26" localSheetId="3">'5to Año'!$I$41</definedName>
+    <definedName name="std_sx_26" localSheetId="3">'5to Año'!$J$41</definedName>
+    <definedName name="std_bd_26" localSheetId="3">'5to Año'!$K$41</definedName>
+    <definedName name="std_bm_26" localSheetId="3">'5to Año'!$L$41</definedName>
+    <definedName name="std_by_26" localSheetId="3">'5to Año'!$M$41</definedName>
+    <definedName name="grade_1_26" localSheetId="3">'5to Año'!$N$41</definedName>
+    <definedName name="grade_2_26" localSheetId="3">'5to Año'!$O$41</definedName>
+    <definedName name="grade_3_26" localSheetId="3">'5to Año'!$P$41</definedName>
+    <definedName name="grade_4_26" localSheetId="3">'5to Año'!$Q$41</definedName>
+    <definedName name="grade_5_26" localSheetId="3">'5to Año'!$R$41</definedName>
+    <definedName name="grade_6_26" localSheetId="3">'5to Año'!$S$41</definedName>
+    <definedName name="grade_7_26" localSheetId="3">'5to Año'!$T$41</definedName>
+    <definedName name="grade_8_26" localSheetId="3">'5to Año'!$U$41</definedName>
+    <definedName name="grade_9_26" localSheetId="3">'5to Año'!$V$41</definedName>
+    <definedName name="grade_10_26" localSheetId="3">'5to Año'!$W$41</definedName>
+    <definedName name="grade_11_26" localSheetId="3">'5to Año'!$X$41</definedName>
+    <definedName name="grade_12_26" localSheetId="3">'5to Año'!$Y$41</definedName>
+    <definedName name="std_part_26" localSheetId="3">'5to Año'!$Z$41</definedName>
+    <definedName name="std_num_27" localSheetId="3">'5to Año'!$A$42</definedName>
+    <definedName name="std_doc_27" localSheetId="3">'5to Año'!$B$42</definedName>
+    <definedName name="std_ln_27" localSheetId="3">'5to Año'!$D$42</definedName>
+    <definedName name="std_fn_27" localSheetId="3">'5to Año'!$F$42</definedName>
+    <definedName name="std_bp_27" localSheetId="3">'5to Año'!$H$42</definedName>
+    <definedName name="std_ef_27" localSheetId="3">'5to Año'!$I$42</definedName>
+    <definedName name="std_sx_27" localSheetId="3">'5to Año'!$J$42</definedName>
+    <definedName name="std_bd_27" localSheetId="3">'5to Año'!$K$42</definedName>
+    <definedName name="std_bm_27" localSheetId="3">'5to Año'!$L$42</definedName>
+    <definedName name="std_by_27" localSheetId="3">'5to Año'!$M$42</definedName>
+    <definedName name="grade_1_27" localSheetId="3">'5to Año'!$N$42</definedName>
+    <definedName name="grade_2_27" localSheetId="3">'5to Año'!$O$42</definedName>
+    <definedName name="grade_3_27" localSheetId="3">'5to Año'!$P$42</definedName>
+    <definedName name="grade_4_27" localSheetId="3">'5to Año'!$Q$42</definedName>
+    <definedName name="grade_5_27" localSheetId="3">'5to Año'!$R$42</definedName>
+    <definedName name="grade_6_27" localSheetId="3">'5to Año'!$S$42</definedName>
+    <definedName name="grade_7_27" localSheetId="3">'5to Año'!$T$42</definedName>
+    <definedName name="grade_8_27" localSheetId="3">'5to Año'!$U$42</definedName>
+    <definedName name="grade_9_27" localSheetId="3">'5to Año'!$V$42</definedName>
+    <definedName name="grade_10_27" localSheetId="3">'5to Año'!$W$42</definedName>
+    <definedName name="grade_11_27" localSheetId="3">'5to Año'!$X$42</definedName>
+    <definedName name="grade_12_27" localSheetId="3">'5to Año'!$Y$42</definedName>
+    <definedName name="std_part_27" localSheetId="3">'5to Año'!$Z$42</definedName>
+    <definedName name="std_num_28" localSheetId="3">'5to Año'!$A$43</definedName>
+    <definedName name="std_doc_28" localSheetId="3">'5to Año'!$B$43</definedName>
+    <definedName name="std_ln_28" localSheetId="3">'5to Año'!$D$43</definedName>
+    <definedName name="std_fn_28" localSheetId="3">'5to Año'!$F$43</definedName>
+    <definedName name="std_bp_28" localSheetId="3">'5to Año'!$H$43</definedName>
+    <definedName name="std_ef_28" localSheetId="3">'5to Año'!$I$43</definedName>
+    <definedName name="std_sx_28" localSheetId="3">'5to Año'!$J$43</definedName>
+    <definedName name="std_bd_28" localSheetId="3">'5to Año'!$K$43</definedName>
+    <definedName name="std_bm_28" localSheetId="3">'5to Año'!$L$43</definedName>
+    <definedName name="std_by_28" localSheetId="3">'5to Año'!$M$43</definedName>
+    <definedName name="grade_1_28" localSheetId="3">'5to Año'!$N$43</definedName>
+    <definedName name="grade_2_28" localSheetId="3">'5to Año'!$O$43</definedName>
+    <definedName name="grade_3_28" localSheetId="3">'5to Año'!$P$43</definedName>
+    <definedName name="grade_4_28" localSheetId="3">'5to Año'!$Q$43</definedName>
+    <definedName name="grade_5_28" localSheetId="3">'5to Año'!$R$43</definedName>
+    <definedName name="grade_6_28" localSheetId="3">'5to Año'!$S$43</definedName>
+    <definedName name="grade_7_28" localSheetId="3">'5to Año'!$T$43</definedName>
+    <definedName name="grade_8_28" localSheetId="3">'5to Año'!$U$43</definedName>
+    <definedName name="grade_9_28" localSheetId="3">'5to Año'!$V$43</definedName>
+    <definedName name="grade_10_28" localSheetId="3">'5to Año'!$W$43</definedName>
+    <definedName name="grade_11_28" localSheetId="3">'5to Año'!$X$43</definedName>
+    <definedName name="grade_12_28" localSheetId="3">'5to Año'!$Y$43</definedName>
+    <definedName name="std_part_28" localSheetId="3">'5to Año'!$Z$43</definedName>
+    <definedName name="std_num_29" localSheetId="3">'5to Año'!$A$44</definedName>
+    <definedName name="std_doc_29" localSheetId="3">'5to Año'!$B$44</definedName>
+    <definedName name="std_ln_29" localSheetId="3">'5to Año'!$D$44</definedName>
+    <definedName name="std_fn_29" localSheetId="3">'5to Año'!$F$44</definedName>
+    <definedName name="std_bp_29" localSheetId="3">'5to Año'!$H$44</definedName>
+    <definedName name="std_ef_29" localSheetId="3">'5to Año'!$I$44</definedName>
+    <definedName name="std_sx_29" localSheetId="3">'5to Año'!$J$44</definedName>
+    <definedName name="std_bd_29" localSheetId="3">'5to Año'!$K$44</definedName>
+    <definedName name="std_bm_29" localSheetId="3">'5to Año'!$L$44</definedName>
+    <definedName name="std_by_29" localSheetId="3">'5to Año'!$M$44</definedName>
+    <definedName name="grade_1_29" localSheetId="3">'5to Año'!$N$44</definedName>
+    <definedName name="grade_2_29" localSheetId="3">'5to Año'!$O$44</definedName>
+    <definedName name="grade_3_29" localSheetId="3">'5to Año'!$P$44</definedName>
+    <definedName name="grade_4_29" localSheetId="3">'5to Año'!$Q$44</definedName>
+    <definedName name="grade_5_29" localSheetId="3">'5to Año'!$R$44</definedName>
+    <definedName name="grade_6_29" localSheetId="3">'5to Año'!$S$44</definedName>
+    <definedName name="grade_7_29" localSheetId="3">'5to Año'!$T$44</definedName>
+    <definedName name="grade_8_29" localSheetId="3">'5to Año'!$U$44</definedName>
+    <definedName name="grade_9_29" localSheetId="3">'5to Año'!$V$44</definedName>
+    <definedName name="grade_10_29" localSheetId="3">'5to Año'!$W$44</definedName>
+    <definedName name="grade_11_29" localSheetId="3">'5to Año'!$X$44</definedName>
+    <definedName name="grade_12_29" localSheetId="3">'5to Año'!$Y$44</definedName>
+    <definedName name="std_part_29" localSheetId="3">'5to Año'!$Z$44</definedName>
+    <definedName name="std_num_30" localSheetId="3">'5to Año'!$A$45</definedName>
+    <definedName name="std_doc_30" localSheetId="3">'5to Año'!$B$45</definedName>
+    <definedName name="std_ln_30" localSheetId="3">'5to Año'!$D$45</definedName>
+    <definedName name="std_fn_30" localSheetId="3">'5to Año'!$F$45</definedName>
+    <definedName name="std_bp_30" localSheetId="3">'5to Año'!$H$45</definedName>
+    <definedName name="std_ef_30" localSheetId="3">'5to Año'!$I$45</definedName>
+    <definedName name="std_sx_30" localSheetId="3">'5to Año'!$J$45</definedName>
+    <definedName name="std_bd_30" localSheetId="3">'5to Año'!$K$45</definedName>
+    <definedName name="std_bm_30" localSheetId="3">'5to Año'!$L$45</definedName>
+    <definedName name="std_by_30" localSheetId="3">'5to Año'!$M$45</definedName>
+    <definedName name="grade_1_30" localSheetId="3">'5to Año'!$N$45</definedName>
+    <definedName name="grade_2_30" localSheetId="3">'5to Año'!$O$45</definedName>
+    <definedName name="grade_3_30" localSheetId="3">'5to Año'!$P$45</definedName>
+    <definedName name="grade_4_30" localSheetId="3">'5to Año'!$Q$45</definedName>
+    <definedName name="grade_5_30" localSheetId="3">'5to Año'!$R$45</definedName>
+    <definedName name="grade_6_30" localSheetId="3">'5to Año'!$S$45</definedName>
+    <definedName name="grade_7_30" localSheetId="3">'5to Año'!$T$45</definedName>
+    <definedName name="grade_8_30" localSheetId="3">'5to Año'!$U$45</definedName>
+    <definedName name="grade_9_30" localSheetId="3">'5to Año'!$V$45</definedName>
+    <definedName name="grade_10_30" localSheetId="3">'5to Año'!$W$45</definedName>
+    <definedName name="grade_11_30" localSheetId="3">'5to Año'!$X$45</definedName>
+    <definedName name="grade_12_30" localSheetId="3">'5to Año'!$Y$45</definedName>
+    <definedName name="std_part_30" localSheetId="3">'5to Año'!$Z$45</definedName>
+    <definedName name="std_num_31" localSheetId="3">'5to Año'!$A$46</definedName>
+    <definedName name="std_doc_31" localSheetId="3">'5to Año'!$B$46</definedName>
+    <definedName name="std_ln_31" localSheetId="3">'5to Año'!$D$46</definedName>
+    <definedName name="std_fn_31" localSheetId="3">'5to Año'!$F$46</definedName>
+    <definedName name="std_bp_31" localSheetId="3">'5to Año'!$H$46</definedName>
+    <definedName name="std_ef_31" localSheetId="3">'5to Año'!$I$46</definedName>
+    <definedName name="std_sx_31" localSheetId="3">'5to Año'!$J$46</definedName>
+    <definedName name="std_bd_31" localSheetId="3">'5to Año'!$K$46</definedName>
+    <definedName name="std_bm_31" localSheetId="3">'5to Año'!$L$46</definedName>
+    <definedName name="std_by_31" localSheetId="3">'5to Año'!$M$46</definedName>
+    <definedName name="grade_1_31" localSheetId="3">'5to Año'!$N$46</definedName>
+    <definedName name="grade_2_31" localSheetId="3">'5to Año'!$O$46</definedName>
+    <definedName name="grade_3_31" localSheetId="3">'5to Año'!$P$46</definedName>
+    <definedName name="grade_4_31" localSheetId="3">'5to Año'!$Q$46</definedName>
+    <definedName name="grade_5_31" localSheetId="3">'5to Año'!$R$46</definedName>
+    <definedName name="grade_6_31" localSheetId="3">'5to Año'!$S$46</definedName>
+    <definedName name="grade_7_31" localSheetId="3">'5to Año'!$T$46</definedName>
+    <definedName name="grade_8_31" localSheetId="3">'5to Año'!$U$46</definedName>
+    <definedName name="grade_9_31" localSheetId="3">'5to Año'!$V$46</definedName>
+    <definedName name="grade_10_31" localSheetId="3">'5to Año'!$W$46</definedName>
+    <definedName name="grade_11_31" localSheetId="3">'5to Año'!$X$46</definedName>
+    <definedName name="grade_12_31" localSheetId="3">'5to Año'!$Y$46</definedName>
+    <definedName name="std_part_31" localSheetId="3">'5to Año'!$Z$46</definedName>
+    <definedName name="std_num_32" localSheetId="3">'5to Año'!$A$47</definedName>
+    <definedName name="std_doc_32" localSheetId="3">'5to Año'!$B$47</definedName>
+    <definedName name="std_ln_32" localSheetId="3">'5to Año'!$D$47</definedName>
+    <definedName name="std_fn_32" localSheetId="3">'5to Año'!$F$47</definedName>
+    <definedName name="std_bp_32" localSheetId="3">'5to Año'!$H$47</definedName>
+    <definedName name="std_ef_32" localSheetId="3">'5to Año'!$I$47</definedName>
+    <definedName name="std_sx_32" localSheetId="3">'5to Año'!$J$47</definedName>
+    <definedName name="std_bd_32" localSheetId="3">'5to Año'!$K$47</definedName>
+    <definedName name="std_bm_32" localSheetId="3">'5to Año'!$L$47</definedName>
+    <definedName name="std_by_32" localSheetId="3">'5to Año'!$M$47</definedName>
+    <definedName name="grade_1_32" localSheetId="3">'5to Año'!$N$47</definedName>
+    <definedName name="grade_2_32" localSheetId="3">'5to Año'!$O$47</definedName>
+    <definedName name="grade_3_32" localSheetId="3">'5to Año'!$P$47</definedName>
+    <definedName name="grade_4_32" localSheetId="3">'5to Año'!$Q$47</definedName>
+    <definedName name="grade_5_32" localSheetId="3">'5to Año'!$R$47</definedName>
+    <definedName name="grade_6_32" localSheetId="3">'5to Año'!$S$47</definedName>
+    <definedName name="grade_7_32" localSheetId="3">'5to Año'!$T$47</definedName>
+    <definedName name="grade_8_32" localSheetId="3">'5to Año'!$U$47</definedName>
+    <definedName name="grade_9_32" localSheetId="3">'5to Año'!$V$47</definedName>
+    <definedName name="grade_10_32" localSheetId="3">'5to Año'!$W$47</definedName>
+    <definedName name="grade_11_32" localSheetId="3">'5to Año'!$X$47</definedName>
+    <definedName name="grade_12_32" localSheetId="3">'5to Año'!$Y$47</definedName>
+    <definedName name="std_part_32" localSheetId="3">'5to Año'!$Z$47</definedName>
+    <definedName name="std_num_33" localSheetId="3">'5to Año'!$A$48</definedName>
+    <definedName name="std_doc_33" localSheetId="3">'5to Año'!$B$48</definedName>
+    <definedName name="std_ln_33" localSheetId="3">'5to Año'!$D$48</definedName>
+    <definedName name="std_fn_33" localSheetId="3">'5to Año'!$F$48</definedName>
+    <definedName name="std_bp_33" localSheetId="3">'5to Año'!$H$48</definedName>
+    <definedName name="std_ef_33" localSheetId="3">'5to Año'!$I$48</definedName>
+    <definedName name="std_sx_33" localSheetId="3">'5to Año'!$J$48</definedName>
+    <definedName name="std_bd_33" localSheetId="3">'5to Año'!$K$48</definedName>
+    <definedName name="std_bm_33" localSheetId="3">'5to Año'!$L$48</definedName>
+    <definedName name="std_by_33" localSheetId="3">'5to Año'!$M$48</definedName>
+    <definedName name="grade_1_33" localSheetId="3">'5to Año'!$N$48</definedName>
+    <definedName name="grade_2_33" localSheetId="3">'5to Año'!$O$48</definedName>
+    <definedName name="grade_3_33" localSheetId="3">'5to Año'!$P$48</definedName>
+    <definedName name="grade_4_33" localSheetId="3">'5to Año'!$Q$48</definedName>
+    <definedName name="grade_5_33" localSheetId="3">'5to Año'!$R$48</definedName>
+    <definedName name="grade_6_33" localSheetId="3">'5to Año'!$S$48</definedName>
+    <definedName name="grade_7_33" localSheetId="3">'5to Año'!$T$48</definedName>
+    <definedName name="grade_8_33" localSheetId="3">'5to Año'!$U$48</definedName>
+    <definedName name="grade_9_33" localSheetId="3">'5to Año'!$V$48</definedName>
+    <definedName name="grade_10_33" localSheetId="3">'5to Año'!$W$48</definedName>
+    <definedName name="grade_11_33" localSheetId="3">'5to Año'!$X$48</definedName>
+    <definedName name="grade_12_33" localSheetId="3">'5to Año'!$Y$48</definedName>
+    <definedName name="std_part_33" localSheetId="3">'5to Año'!$Z$48</definedName>
+    <definedName name="std_num_34" localSheetId="3">'5to Año'!$A$49</definedName>
+    <definedName name="std_doc_34" localSheetId="3">'5to Año'!$B$49</definedName>
+    <definedName name="std_ln_34" localSheetId="3">'5to Año'!$D$49</definedName>
+    <definedName name="std_fn_34" localSheetId="3">'5to Año'!$F$49</definedName>
+    <definedName name="std_bp_34" localSheetId="3">'5to Año'!$H$49</definedName>
+    <definedName name="std_ef_34" localSheetId="3">'5to Año'!$I$49</definedName>
+    <definedName name="std_sx_34" localSheetId="3">'5to Año'!$J$49</definedName>
+    <definedName name="std_bd_34" localSheetId="3">'5to Año'!$K$49</definedName>
+    <definedName name="std_bm_34" localSheetId="3">'5to Año'!$L$49</definedName>
+    <definedName name="std_by_34" localSheetId="3">'5to Año'!$M$49</definedName>
+    <definedName name="grade_1_34" localSheetId="3">'5to Año'!$N$49</definedName>
+    <definedName name="grade_2_34" localSheetId="3">'5to Año'!$O$49</definedName>
+    <definedName name="grade_3_34" localSheetId="3">'5to Año'!$P$49</definedName>
+    <definedName name="grade_4_34" localSheetId="3">'5to Año'!$Q$49</definedName>
+    <definedName name="grade_5_34" localSheetId="3">'5to Año'!$R$49</definedName>
+    <definedName name="grade_6_34" localSheetId="3">'5to Año'!$S$49</definedName>
+    <definedName name="grade_7_34" localSheetId="3">'5to Año'!$T$49</definedName>
+    <definedName name="grade_8_34" localSheetId="3">'5to Año'!$U$49</definedName>
+    <definedName name="grade_9_34" localSheetId="3">'5to Año'!$V$49</definedName>
+    <definedName name="grade_10_34" localSheetId="3">'5to Año'!$W$49</definedName>
+    <definedName name="grade_11_34" localSheetId="3">'5to Año'!$X$49</definedName>
+    <definedName name="grade_12_34" localSheetId="3">'5to Año'!$Y$49</definedName>
+    <definedName name="std_part_34" localSheetId="3">'5to Año'!$Z$49</definedName>
+    <definedName name="std_num_35" localSheetId="3">'5to Año'!$A$50</definedName>
+    <definedName name="std_doc_35" localSheetId="3">'5to Año'!$B$50</definedName>
+    <definedName name="std_ln_35" localSheetId="3">'5to Año'!$D$50</definedName>
+    <definedName name="std_fn_35" localSheetId="3">'5to Año'!$F$50</definedName>
+    <definedName name="std_bp_35" localSheetId="3">'5to Año'!$H$50</definedName>
+    <definedName name="std_ef_35" localSheetId="3">'5to Año'!$I$50</definedName>
+    <definedName name="std_sx_35" localSheetId="3">'5to Año'!$J$50</definedName>
+    <definedName name="std_bd_35" localSheetId="3">'5to Año'!$K$50</definedName>
+    <definedName name="std_bm_35" localSheetId="3">'5to Año'!$L$50</definedName>
+    <definedName name="std_by_35" localSheetId="3">'5to Año'!$M$50</definedName>
+    <definedName name="grade_1_35" localSheetId="3">'5to Año'!$N$50</definedName>
+    <definedName name="grade_2_35" localSheetId="3">'5to Año'!$O$50</definedName>
+    <definedName name="grade_3_35" localSheetId="3">'5to Año'!$P$50</definedName>
+    <definedName name="grade_4_35" localSheetId="3">'5to Año'!$Q$50</definedName>
+    <definedName name="grade_5_35" localSheetId="3">'5to Año'!$R$50</definedName>
+    <definedName name="grade_6_35" localSheetId="3">'5to Año'!$S$50</definedName>
+    <definedName name="grade_7_35" localSheetId="3">'5to Año'!$T$50</definedName>
+    <definedName name="grade_8_35" localSheetId="3">'5to Año'!$U$50</definedName>
+    <definedName name="grade_9_35" localSheetId="3">'5to Año'!$V$50</definedName>
+    <definedName name="grade_10_35" localSheetId="3">'5to Año'!$W$50</definedName>
+    <definedName name="grade_11_35" localSheetId="3">'5to Año'!$X$50</definedName>
+    <definedName name="grade_12_35" localSheetId="3">'5to Año'!$Y$50</definedName>
+    <definedName name="std_part_35" localSheetId="3">'5to Año'!$Z$50</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
